--- a/data/3.R_pakh.xlsx
+++ b/data/3.R_pakh.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC50"/>
+  <dimension ref="A1:AC48"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="25" max="25" width="20.7109375" style="2" customWidth="1"/>
@@ -511,1804 +511,2077 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>KV3</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>CMU</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>DVKT</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Home Service</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Bảo dưỡng Điều hòa treo tường (9.000BTU ÷ 12.000 BTU)</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>VCC_HS_CMU_1774325231892</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>B2C</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Member</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Khách hàng cá nhân</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Viết Đông</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0902575123</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Long điền ,đông hải,bạc liêu, Phường Bạc Liêu, Tỉnh Cà Mau</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Sau bán</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Phàn nàn, Góp Ý</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Chất lượng, dịch vụ, Giá cả</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>KT ko vệ sinh cục nóng mà vẫn thu tiền đủ, KH càm thấy ko hài lòng.</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>13:30 27/03/2026</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>09:00 30/03/2026</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Chưa thực hiện</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Nguyễn Trí Đạt</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>437699</t>
+        </is>
+      </c>
+      <c r="Y2" s="2">
+        <v>46108</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>HS</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>KV1</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>LCI</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>GPTH</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NLMT</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Hệ thống NLMT</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>KHCN_TT.GPTH_LCI_1631825</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>B2C</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Diamond</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Khách hàng cá nhân</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Hoàng Thị Khuyên</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0915964280</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Phường Duyên Hải, Thành phố Lào Cai, Tỉnh Lào Cai</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Hotline</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Sau bán</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Sự cố</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>Chất lượng, hiệu suất của sản phẩm/hệ thống thấp</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>1. KH đã báo CN nhưng chưa được hỗ trợ
+2. KH phản ánh: Điện chỉ ăn vào điện lưới quốc gia mất 1,6-2tr tiền điện và khi mất điện ko tự động nhảy sang điện nlmt mà mất điện hết toàn bộ. KH lắp 3 pha nhưng thấy chỉ hỗ trợ điện 1 pha.
+3. KH yêu cầu: KT qua kiểm tra, khắc phục tình trạng này cho KH.
+***SĐT phản ánh: 0359247000</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>13:30 27/03/2026</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>09:00 30/03/2026</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Đang tiến hành</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Trần Hữu Tuân</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>431016</t>
+        </is>
+      </c>
+      <c r="Y3" s="2">
+        <v>46108</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>AIO</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
           <t>KV2</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>QTI</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>DVKT</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Home Service</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Gói hỗ trợ kỹ thuật - Dịch vụ kiểm tra</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>VCC_HS_QTI_1774347935114</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>B2C</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Khách hàng cá nhân</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Anhh Bảo</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0387766616</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>TDP7 xã Minh Hoá, Quảng Trị, Xã Minh Hóa, Tỉnh Quảng Trị</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Trước bán</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Khiếu nại</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>Liên hệ chậm</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>KH hẹn 25/3 mà ko thấy ai liên hệ yêu cầu KT liên hệ trao đổi với KH.</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>13:30 27/03/2026</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>09:00 30/03/2026</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Chưa thực hiện</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Nguyễn Bá Huy</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>069300</t>
+        </is>
+      </c>
+      <c r="Y4" s="2">
+        <v>46108</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>HS</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>KV1</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>QNH</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>DVKT</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Home Service</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Chi phí đến nhà kiểm tra DV Home Services (trong trường hợp KH không phát sinh đơn dịch vụ hoặc vật tư)</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>VCC_HS_QNH_1773466348941</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>B2C</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Khách hàng cá nhân</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Nguyễn Văn Thiết</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0912811551</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Nhà máy fanstech khu công nghiệp Bắc Tiền Phong phường Phong Cốc Quảng Ninh, Phường Phong Cốc, Tỉnh Quảng Ninh</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Trước bán</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Khiếu nại</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>Liên hệ chậm</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>KH hẹn vào 15/3 mà ko thấy ai liên hệ.</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>13:30 27/03/2026</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>09:00 30/03/2026</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Chưa thực hiện</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Nguyễn Việt An</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>419449</t>
+        </is>
+      </c>
+      <c r="Y5" s="2">
+        <v>46108</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>HS</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>KV2</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
         <is>
           <t>GLI</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>KHCN_TMNLMT_BDH_0297148</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>Lê Đình Khánh</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>0388773033</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>Cát Minh, Xã Cát Minh, Huyện Phù Cát, Tỉnh Bình Định</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>Sản phẩm bị ngắt quãng/ Không theo dõi và không nghe được</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>1. KH đã báo cn:  
 2. KH phản ánh:Hệ thống nlmt ko chạy ra kw, cứ đang chạy đỏ rồi lại đứng lại. Sản lượng ra thì thấp,  
 3. KH yêu cầu: Qua hỗ trợ, xử lý, hướng dẫn cho KH hiểu. KH sẽ sẵn sàng trả thêm phí nếu phát sinh thêm và cũng sẵn sàng hỗ trợ nếu xử lý dứt điểm được cho KH.</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>16:28 26/03/2026</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>16:28 27/03/2026</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>Chưa thực hiện</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>Trong hạn</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Đang tiến hành</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Sắp quá hạn</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
         <is>
           <t>Nguyễn Quang Toàn</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>293989</t>
         </is>
       </c>
-      <c r="Y2" s="2">
+      <c r="Y6" s="2">
         <v>46107</v>
       </c>
-      <c r="Z2">
+      <c r="Z6">
         <v>1</v>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>KV3</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>HCM</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>KHDN_TT.GPTH_BDG_1495422</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>B2B</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>Diamond</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>Khách hàng doanh nghiệp</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>CÔNG TY TNHH THƯƠNG MẠI VẬN TẢI BẢO LONG PHÁT</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>0918236379</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>Số 617, đường ĐT 743B, khu phố Đông Tân</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>Zalo</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>Hỗ trợ</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>Cài đặt hệ thống (APP/Mật khẩu)</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>1. KH báo cn người hỗ trợ trước nhưng ko liên hệ được
 2. KH phản ánh: KH kết nối được app báo lỗi ngoại tuyến
 3. KH yêu cầu: Hỗ trợ, hướng dẫn KH sử dụng, KH hay bị gặp vấn đề này nhiều hỗ trợ KH dứt điểm giúp.</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>16:08 26/03/2026</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>16:08 27/03/2026</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>Chưa thực hiện</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>09:00 05/04/2026</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Đang tiến hành</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
         <is>
           <t>Trong hạn</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>Nguyễn Thành Long</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>282101</t>
-        </is>
-      </c>
-      <c r="Y3" s="2">
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Trần Văn Thắng</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>470289</t>
+        </is>
+      </c>
+      <c r="Y7" s="2">
         <v>46107</v>
       </c>
-      <c r="Z3">
+      <c r="Z7">
         <v>1</v>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>KV2</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>DNG</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>GPTH</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>CNTT</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Camera</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>KHCN_TT.GPTH_DNG_1240036</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>B2C</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Khách hàng cá nhân</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Nguyễn Văn Thiên</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0935302100</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>48 nguyễn đình chiểu, Phường Khuê Mỹ, Quận Ngũ Hành Sơn, Thành phố Đà Nẵng</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Hotline</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Sau bán</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Hỗ trợ</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>Cài đặt hệ thống (APP/Mật khẩu)</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>1. KH phản ánh: Camera bị rớt không kết nối được, và cả mật khẩu wifi
+2. KH yêu cầu: Hỗ trợ KH cài đặt lại camera.</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>10:11 27/03/2026</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>09:00 30/03/2026</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Đang tiến hành</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Trần Xuân Bách</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>071337</t>
+        </is>
+      </c>
+      <c r="Y8" s="2">
+        <v>46108</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>AIO</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>P.Triển khai</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Sonln15</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>KV3</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>HCM</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>TNH</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>KHCN_TT.GPTH_HCM_1647671</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>0901/NLMT/VCCTNH</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Diamond</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Bùi Châu Thùy Linh</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>0852842882</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>Phường Bình Hưng Hòa, Thành phố Hồ Chí Minh</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>Nhân viên nội bộ VCC</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Nguyễn Hải Lương</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0983730342</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Thị trấn Tân Châu,Huyện Tân Châu,Tỉnh Tây Ninh</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Hotline</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>Chất lượng, hiệu suất của sản phẩm/hệ thống thấp</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>CN báo sự cố hộ KH
-1. KH phản ánh: Ivt thông số bị chênh lệch khoảng 40-50 số điện so với đồng hồ điện lực
-2. KH yêu cầu: Xử lý càng nhanh càng tốt vì nhà KH cho thuê.</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>14:14 26/03/2026</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>14:14 27/03/2026</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Chưa thực hiện</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>Sắp quá hạn</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>Lê Khánh Toàn</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>475483</t>
-        </is>
-      </c>
-      <c r="Y4" s="2">
-        <v>46107</v>
-      </c>
-      <c r="Z4">
-        <v>1</v>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>AIO</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>KV3</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>TNH</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>GPTH</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>NLMT</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Hệ thống NLMT</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>0901/NLMT/VCCTNH</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>B2C</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Khách hàng cá nhân</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Nguyễn Hải Lương</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>0983730342</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>Thị trấn Tân Châu,Huyện Tân Châu,Tỉnh Tây Ninh</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>Hotline</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>Bình thường</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>Sau bán</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>Sự cố</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>Chất lượng, hiệu suất của sản phẩm/hệ thống thấp</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>1. KH đã báo cn
 2. KH phản ánh: Hệ của KH sản lượng rất thấp, hqua nắng to cả ngày 39 độ mà ko được nổi 200kw trên hệ 52kw của KH.
 3. KH yêu cầu: Kiểm tra đo đạc lại thiết bị, và xem thiết kế lại đường đi dòng điện 3 pha, và xem có phương án để tối ưu sản lượng cho KH ko tư vấn, hướng dẫn cho KH.</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>08:00 27/03/2026</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>09:00 30/03/2026</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>Chưa thực hiện</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>Chưa tính KPI</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>Trần Văn Quy</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>470911</t>
-        </is>
-      </c>
-      <c r="Y5" s="2">
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Đang tiến hành</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Nguyễn Quốc Hưng</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>467401</t>
+        </is>
+      </c>
+      <c r="Y9" s="2">
         <v>46108</v>
       </c>
-      <c r="Z5">
+      <c r="Z9">
         <v>0</v>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AA9" t="inlineStr">
         <is>
           <t>IOC</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AB9" t="inlineStr">
         <is>
           <t>P.Triển khai</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>truongdv17</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>KV3</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>TNH</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_TNH_1639818</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>Diamond</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>Lý Đức Huy</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>0903101647</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>khu phố An Thới</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>Nhân viên nội bộ VCC</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>CN báo sự cố hộ KH
 1. KH phản ánh: Pin lưu trữ đang bị hỏng và mất luôn nguồn pin lưu trữ.
 2. KH yêu cầu: Qua kiểm tra, khắc phục tình trạng này cho KH.</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>14:47 26/03/2026</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>14:47 27/03/2026</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>08:55 04/04/2026</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>Sắp quá hạn</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
         <is>
           <t>Nguyễn Quốc Hưng</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>467401</t>
         </is>
       </c>
-      <c r="Y6" s="2">
+      <c r="Y10" s="2">
         <v>46107</v>
       </c>
-      <c r="Z6">
+      <c r="Z10">
         <v>1</v>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AA10" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AB10" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
+      <c r="AC10" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>KV2</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>DNG</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>GLI</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Tấm pin NLMT</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>VCC_YCTX_DNG_38420986565488944</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Hệ thống NLMT</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>KHCN_TT.GPTH_GLI_1676729</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Diamond</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Member</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Huỳnh Thanh Vũ</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>0905337005</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>Sơn Trà Đà Nẵng</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Rơ Ô WÊ</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0396081566</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Thôn Ia Prông</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>Trước bán</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>Hỗ trợ</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>Tư vấn sản phẩm/dịch vụ</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>KH cần NV tư vấn liên hệ lại</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>14:08 26/03/2026</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>14:08 27/03/2026</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>Chưa thực hiện</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>Sắp quá hạn</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>Lê Quốc Nguyên</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>411194</t>
-        </is>
-      </c>
-      <c r="Y7" s="2">
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Trong bán</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Khiếu nại</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>Tiến độ triển khai chậm</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>KH phản ánh đã đặt cọc lắp đặt hệ thống điện năng lượng mặt trời 20 ngày rồi nhưng chưa co KT nào qua lắp cho KH. Yêu cầu xử lý gấp</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>10:43 26/03/2026</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>08:35 31/03/2026</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Đang tiến hành</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Nguyễn Hà Nguyên</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>060709</t>
+        </is>
+      </c>
+      <c r="Y11" s="2">
         <v>46107</v>
       </c>
-      <c r="Z7">
+      <c r="Z11">
         <v>1</v>
       </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>IOC</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>P.KDNLMT</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>P.KDNLMT</t>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>AIO</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>P.Triển khai</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Sonln15</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>KV2</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>GLI</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>KHA</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>KHCN_TT.GPTH_GLI_1676729</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>KHCN_NLMT_NTN_0241352</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Member</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Rơ Ô WÊ</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>0396081566</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>Thôn Ia Prông</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Nguyễn Văn Sanh</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0913785605</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>KP2, Thị trấn Phước Dân, Huyện Ninh Phước, Tỉnh Ninh Thuận</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>Trong bán</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Khiếu nại</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>Tiến độ triển khai chậm</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>KH phản ánh đã đặt cọc lắp đặt hệ thống điện năng lượng mặt trời 20 ngày rồi nhưng chưa co KT nào qua lắp cho KH. Yêu cầu xử lý gấp</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>10:43 26/03/2026</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>10:43 27/03/2026</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>Chưa thực hiện</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>Sắp quá hạn</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>Nguyễn Hà Nguyên</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>060709</t>
-        </is>
-      </c>
-      <c r="Y8" s="2">
-        <v>46107</v>
-      </c>
-      <c r="Z8">
-        <v>1</v>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>AIO</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>P.Triển khai</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Sonln15</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>KV2</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>KHA</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>GPTH</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>NLMT</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Hệ thống NLMT</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>KHCN_NLMT_NTN_0241352</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>B2C</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Khách hàng cá nhân</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>Nguyễn Văn Sanh</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>0913785605</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>KP2, Thị trấn Phước Dân, Huyện Ninh Phước, Tỉnh Ninh Thuận</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>Hotline</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>Bình thường</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>1. KH đã báo cn
 2. KH phản ánh: Ivt bị lỗi ko hoạt động, KH ktra thấy còn ko chạy
 3. KH yêu cầu: Qua hỗ trợ, kiểm tra, khắc phục tình trạng này cho KH</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>08:25 26/03/2026</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>08:25 27/03/2026</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>14:00 27/03/2026</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>Sắp quá hạn</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>Vũ Đình Minh</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>006275</t>
-        </is>
-      </c>
-      <c r="Y9" s="2">
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Quá hạn</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Nguyễn Văn Vương</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>069846</t>
+        </is>
+      </c>
+      <c r="Y12" s="2">
         <v>46107</v>
       </c>
-      <c r="Z9">
+      <c r="Z12">
         <v>1</v>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="AA12" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AB12" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
+      <c r="AC12" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>KV1</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>HNI</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>DVKT</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Home Service</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Hỗ trợ kiểm tra</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>DH_B2C_HNI_1772685977872</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>HYN</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>GPTH</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NLMT</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Hệ thống NLMT</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>KHCN_TT.GPTH_HDG_1304417</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Silver</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Diamond</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>Đào Thị Bích Nga</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>0332262246</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>56B ngõ 31 Nguyễn Cao</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Nguyễn Thị Hồng Khánh</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0377883716</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Thôn Ngọc Loan,Xã Tân Quang,Huyện Văn Lâm,Tỉnh Hưng Yên</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>VIP</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>Trước bán</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>Sự cố</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>Sau bảo dưỡng thiết bị bị hỏng</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>bảo dưỡng điều hòa xong máy kêu ù ù</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>10:33 26/03/2026</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>10:33 27/03/2026</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>Chưa thực hiện</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>Sắp quá hạn</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>Lê Duy Tuấn</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>293859</t>
-        </is>
-      </c>
-      <c r="Y10" s="2">
-        <v>46107</v>
-      </c>
-      <c r="Z10">
-        <v>1</v>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>IOC</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>KV1</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>HYN</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>GPTH</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>NLMT</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Hệ thống NLMT</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>KHCN_TT.GPTH_HDG_1304433</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>B2C</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Diamond</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>Khách hàng cá nhân</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>Nguyễn Thị Hồng Khánh</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>0377883716</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>Thôn Ngọc Loan,Xã Tân Quang,Huyện Văn Lâm,Tỉnh Hưng Yên</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>Hotline</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="P13" t="inlineStr">
         <is>
           <t>Hỗ trợ</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>Hướng dẫn, hỗ trợ sử dụng sản phẩm</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="R13" t="inlineStr">
         <is>
           <t>KH chưa báo CN
 KH yêu cầu NVKT qua lại thiết bị inverter của KH 
 Số liên hệ:</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>08:00 26/03/2026</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>09:00 27/03/2026</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>17:25 02/04/2026</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>Sắp quá hạn</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
         <is>
           <t>Hoàng Văn Phong</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="X13" t="inlineStr">
         <is>
           <t>291011</t>
         </is>
       </c>
-      <c r="Y11" s="2">
+      <c r="Y13" s="2">
         <v>46107</v>
       </c>
-      <c r="Z11">
+      <c r="Z13">
         <v>1</v>
       </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AA13" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AB13" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
+      <c r="AC13" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>KV3</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>HCM</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_HCM_1169983</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>Đường Quyền Hồng</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>0907395121</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>Ấp 4, Xã Phước Kiển, Huyện Nhà Bè, Thành phố Hồ Chí Minh</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="O14" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="P14" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="Q14" t="inlineStr">
         <is>
           <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="R14" t="inlineStr">
         <is>
           <t>1. KH chưa báo CN
 2. KH phản ánh: Lỗi CP bị cúp điện dưới nhà, hiện tại điện ko sử dụng được.
 3. KH yêu cầu: Qua kiểm tra, hỗ trợ, khắc phục gấp cho KH giờ nhà KH đang ko có điện để sử dụng.</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>09:32 26/03/2026</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>09:32 27/03/2026</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>Chưa thực hiện</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>Sắp quá hạn</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>Đoàn Văn Lượng</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>410048</t>
-        </is>
-      </c>
-      <c r="Y12" s="2">
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>16:05 31/03/2026</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Đang tiến hành</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Điểu Ngọc Lâm</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>432612</t>
+        </is>
+      </c>
+      <c r="Y14" s="2">
         <v>46107</v>
       </c>
-      <c r="Z12">
+      <c r="Z14">
         <v>1</v>
       </c>
-      <c r="AA12" t="inlineStr">
+      <c r="AA14" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
+      <c r="AB14" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
+      <c r="AC14" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+    <row r="15">
+      <c r="A15" t="inlineStr">
         <is>
           <t>KV2</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>KHA</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_KHA_1631515</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>Diamond</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>Phạm Hải Triều</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>0903576559</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>Phường Nha Trang, Tỉnh Khánh Hòa</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>Nhân viên nội bộ VCC</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="O15" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="P15" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="Q15" t="inlineStr">
         <is>
           <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="R15" t="inlineStr">
         <is>
           <t>CN báo sự cố hộ KH
 1. KH phản ánh: Ắc quy, pin gần như ko hoạt động. Chỉ có bám tải, ivt hoạt động
 2. KH yêu cầu: Qua hỗ trợ, kiểm tra, xử lý sớm cho KH.</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>08:00 26/03/2026</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>09:00 27/03/2026</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>Chưa thực hiện</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>17:35 27/03/2026</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Đang tiến hành</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
         <is>
           <t>Sắp quá hạn</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>Phan Trọng Nghĩa</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
+      <c r="X15" t="inlineStr">
         <is>
           <t>234935</t>
         </is>
       </c>
-      <c r="Y13" s="2">
+      <c r="Y15" s="2">
         <v>46107</v>
       </c>
-      <c r="Z13">
+      <c r="Z15">
         <v>1</v>
       </c>
-      <c r="AA13" t="inlineStr">
+      <c r="AA15" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
+      <c r="AB15" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
+      <c r="AC15" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>KV1</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>HNI</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>KHDN_TT.GPTH_HNI_1646163</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>B2B</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>Diamond</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>Khách hàng doanh nghiệp</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>Công Ty Tnhh Đầu Tư Xây Dựng Và Thương Mại Triệu Phúc</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>0973721368</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>Triệu Xuyên, Long xuyên</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
+      <c r="O16" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
+      <c r="P16" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr">
+      <c r="Q16" t="inlineStr">
         <is>
           <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="R16" t="inlineStr">
         <is>
           <t>1. KH đã báo cn a Long gđ kỹ thuật, a Dương Đăng Minh chủ ký HĐ, a Vương lắp đặt.
 2. KH phản ánh: Bị nhảy áp liên tục 1 tháng phải nhảy 20 ngày rơi vào khoảng 2h đêm và 12h trưa ban ngày, và chập tối lúc GĐ đang vào sinh hoạt. CN nhiều lần xuống ktra và kiến nghị nhưng có câu trả lời KH ko được hài lòng lắm. Đặc biệt là a Long GĐ KT có thái độ là đổ cho GĐ tắt áp, KH bức xúc vì KH bỏ đồng tiền ra mà lại đổ lỗi cho nhà KH. KH cũng báo với a Dương Đăng Minh, a Minh cũng bảo là để cháu bảo ae xuống thế nọ thế kia khất để ra giêng để sửa mà giờ hết tháng rồi vẫn ko thấy đâu.
@@ -2316,430 +2589,430 @@
 ***SĐT liên hệ: 0945268772, chú Bồng</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>14:58 25/03/2026</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>23:00 06/04/2026</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>Trong hạn</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>Lê Duy Tuấn</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
+      <c r="X16" t="inlineStr">
         <is>
           <t>293859</t>
         </is>
       </c>
-      <c r="Y14" s="2">
+      <c r="Y16" s="2">
         <v>46106</v>
       </c>
-      <c r="Z14">
+      <c r="Z16">
         <v>2</v>
       </c>
-      <c r="AA14" t="inlineStr">
+      <c r="AA16" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
+      <c r="AB16" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
+      <c r="AC16" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>KV1</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>BNH</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_BNH_1600729</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>Nguyễn Khương</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>0977113014</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="L17" t="inlineStr">
         <is>
           <t>Xã Tân Chi, Tỉnh Bắc Ninh</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr">
+      <c r="O17" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr">
+      <c r="P17" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr">
+      <c r="Q17" t="inlineStr">
         <is>
           <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="R17" t="inlineStr">
         <is>
           <t>1. KH đã báo cn nhưng bạn nv kinh doanh a Vượng chuyển công tác nên chuyển cho a Phong, a Phong lại chuyển công tác cho số người mới nhưng chưa thấy.
 2. KH phản ánh: Biểu đồ biến tần tăng giảm đột biến, sụt pin về 0,pv về 0, tất cả đều về 0, thi thoảng còn bị mất điện. Hôm vừa rồi đầu xuân vào app báo thấy mất kết nối điện lưới trong khi nhà xung quanh vẫn có, sau khi xem tbao ở trên app lại ko có bất kỳ tbao nào về biến tần bị ngắt hay gì cả. KH Kbt có ai can thiệp vào app không
 3. KH yêu cầu: Kiểm tra biến tần cho KH, đã yêu cầu hãng xử lý rất nhiều lần rồi, nhưng giờ vẫn có tình trạng gặp lỗi. Ngoài ra KH yêu cầu là xử lý triệt để cho KH vì sắp tới mùa hè nó lên 3,4kw bị nhảy mà giờ còn kh thấy có tbao trên app.</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>09:20 25/03/2026</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="T17" t="inlineStr">
         <is>
           <t>17:25 27/03/2026</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="U17" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr">
+      <c r="V17" t="inlineStr">
         <is>
           <t>Sắp quá hạn</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>Phạm Khắc Việt</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
+      <c r="X17" t="inlineStr">
         <is>
           <t>048379</t>
         </is>
       </c>
-      <c r="Y15" s="2">
+      <c r="Y17" s="2">
         <v>46106</v>
       </c>
-      <c r="Z15">
+      <c r="Z17">
         <v>2</v>
       </c>
-      <c r="AA15" t="inlineStr">
+      <c r="AA17" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
+      <c r="AB17" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
+      <c r="AC17" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>KV2</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>KHA</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>Tấm pin NLMT</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>KHCN_PINNLMT_NTN_0470662</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>Lê Anh Tuấn</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>0949186789</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t>Phường Phan Rang ,Tỉnh Ninh Thuận</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t>Nhân viên nội bộ VCC</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr">
+      <c r="O18" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr">
+      <c r="P18" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr">
+      <c r="Q18" t="inlineStr">
         <is>
           <t>Inverter không hoạt động</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="R18" t="inlineStr">
         <is>
           <t>CN 0962600057 báo sự cố hộ KH, trước lắp đặt cho KH giờ chuyển công tác.
 1. KH phản ánh: Lỗi ivt ko hoạt động, ko nạp và xả ra được
 2. KH yêu cầu: Qua kiểm tra, khắc phục tình trạng này cho KH</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>08:25 25/03/2026</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
+      <c r="T18" t="inlineStr">
         <is>
           <t>19:50 28/03/2026</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="U18" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
+      <c r="V18" t="inlineStr">
         <is>
           <t>Trong hạn</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>Nguyễn Văn Vương</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
+      <c r="X18" t="inlineStr">
         <is>
           <t>069846</t>
         </is>
       </c>
-      <c r="Y16" s="2">
+      <c r="Y18" s="2">
         <v>46106</v>
       </c>
-      <c r="Z16">
+      <c r="Z18">
         <v>2</v>
       </c>
-      <c r="AA16" t="inlineStr">
+      <c r="AA18" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
+      <c r="AB18" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
+      <c r="AC18" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>KV1</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>PTO</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_VPC_1503902</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>Diamond</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>Nguyễn Việt Hùng</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>0966547344</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="L19" t="inlineStr">
         <is>
           <t>Tự lập Mê Linh,Phường Hùng Vương,Thành phố Phúc Yên,Tỉnh Vĩnh Phúc</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
+      <c r="N19" t="inlineStr">
         <is>
           <t>Hot</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr">
+      <c r="O19" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr">
+      <c r="P19" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr">
+      <c r="Q19" t="inlineStr">
         <is>
           <t>Không kết nối được app/Wifi và không theo dõi được hiệu suất</t>
         </is>
       </c>
-      <c r="R17" t="inlineStr">
+      <c r="R19" t="inlineStr">
         <is>
           <t>KH đã báo CN
 KH đang dùng NLMT hiện tại bị lỗi biến tần, ko kết nối được app
@@ -2747,321 +3020,34 @@
 NOTE: địa chỉ hiện tại của KH: thôn phú mỹ, xã tiến thắng, Hà Nội</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t>15:34 24/03/2026</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
+      <c r="T19" t="inlineStr">
         <is>
           <t>17:30 01/04/2026</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr">
+      <c r="V19" t="inlineStr">
         <is>
           <t>Trong hạn</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>Phạm Văn Nghĩa</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
+      <c r="X19" t="inlineStr">
         <is>
           <t>023020</t>
-        </is>
-      </c>
-      <c r="Y17" s="2">
-        <v>46105</v>
-      </c>
-      <c r="Z17">
-        <v>3</v>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>AIO</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>KV3</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>HCM</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>GPTH</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>NLMT</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Inverter</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>KHCN_TT.GPTH_BDG_1352264</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>B2C</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>Khách hàng cá nhân</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>Nguyễn Liễu Thông</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>0362126000</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>ph</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>Hotline</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>Bình thường</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>Sau bán</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>Sự cố</t>
-        </is>
-      </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
-        </is>
-      </c>
-      <c r="R18" t="inlineStr">
-        <is>
-          <t>không hoạt động</t>
-        </is>
-      </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>09:29 26/03/2026</t>
-        </is>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>17:30 31/03/2026</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>Đang tiến hành</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>Trong hạn</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>Nguyễn Văn Toản</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>427880</t>
-        </is>
-      </c>
-      <c r="Y18" s="2">
-        <v>46107</v>
-      </c>
-      <c r="Z18">
-        <v>1</v>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>AIO</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>KV2</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>KHA</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>GPTH</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>NLMT</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Hệ thống NLMT</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>KHCN_TT.GPTH_NTN_1595255</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>B2C</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Silver</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>Khách hàng cá nhân</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>Nguyễn Thị Mỹ Linh</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>0976685068</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>1/19 Hàm Nghi, Phước Mỹ, Phan Rang, Ninh Thuận</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>Happycall</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>Bình thường</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>Sau bán</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>Hỗ trợ</t>
-        </is>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>Cài đặt hệ thống (APP/Mật khẩu)</t>
-        </is>
-      </c>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>1. KH phản ánh: ko tải được app về được và ko xem được mức điện tiêu thụ.
-2. KH yêu cầu: Hỗ trợ cho KH tải app và đăng nhập để xem hiệu suất nlmt.</t>
-        </is>
-      </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>16:44 24/03/2026</t>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>17:30 29/03/2026</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>Đang tiến hành</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>Trong hạn</t>
-        </is>
-      </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>Bùi Khắc Hoàng Linh</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>454887</t>
         </is>
       </c>
       <c r="Y19" s="2">
@@ -3089,520 +3075,807 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>KV3</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>HCM</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>GPTH</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NLMT</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Inverter</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>KHCN_TT.GPTH_BDG_1352264</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>B2C</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Khách hàng cá nhân</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Nguyễn Liễu Thông</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>0362126000</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>ph</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>Hotline</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Sau bán</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Sự cố</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>không hoạt động</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>09:29 26/03/2026</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>17:30 31/03/2026</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Đang tiến hành</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Nguyễn Văn Toản</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>427880</t>
+        </is>
+      </c>
+      <c r="Y20" s="2">
+        <v>46107</v>
+      </c>
+      <c r="Z20">
+        <v>1</v>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>AIO</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>KV2</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>KHA</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>GPTH</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NLMT</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Hệ thống NLMT</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>KHCN_TT.GPTH_NTN_1595255</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>B2C</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Khách hàng cá nhân</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Nguyễn Thị Mỹ Linh</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>0976685068</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>1/19 Hàm Nghi, Phước Mỹ, Phan Rang, Ninh Thuận</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>Happycall</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>Sau bán</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Hỗ trợ</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>Cài đặt hệ thống (APP/Mật khẩu)</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>1. KH phản ánh: ko tải được app về được và ko xem được mức điện tiêu thụ.
+2. KH yêu cầu: Hỗ trợ cho KH tải app và đăng nhập để xem hiệu suất nlmt.</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>16:44 24/03/2026</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>17:30 29/03/2026</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Đang tiến hành</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Bùi Khắc Hoàng Linh</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>454887</t>
+        </is>
+      </c>
+      <c r="Y21" s="2">
+        <v>46105</v>
+      </c>
+      <c r="Z21">
+        <v>3</v>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>AIO</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>KV1</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>PTO</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_PTO_1620637</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>Diamond</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>Nguyễn Đình Mạnh</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t>0988308581</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="L22" t="inlineStr">
         <is>
           <t>Xã Thanh Cao, Huyện Lương Sơn, Tỉnh Hòa Bình</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr">
+      <c r="N22" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr">
+      <c r="O22" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr">
+      <c r="P22" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr">
+      <c r="Q22" t="inlineStr">
         <is>
           <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
-      <c r="R20" t="inlineStr">
+      <c r="R22" t="inlineStr">
         <is>
           <t>KH chưa báo CN
 KH phản ánh: hệ thống bị lỗi, điện bật 10 -15s chớp 1 lần
 KH yêu cầu chuyển KT xuống xử lý gấp</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="S22" t="inlineStr">
         <is>
           <t>15:09 24/03/2026</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
+      <c r="T22" t="inlineStr">
         <is>
           <t>09:10 29/03/2026</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="U22" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr">
+      <c r="V22" t="inlineStr">
         <is>
           <t>Trong hạn</t>
         </is>
       </c>
-      <c r="W20" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>Bùi Anh Nguyễn</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr">
+      <c r="X22" t="inlineStr">
         <is>
           <t>414445</t>
         </is>
       </c>
-      <c r="Y20" s="2">
+      <c r="Y22" s="2">
         <v>46105</v>
       </c>
-      <c r="Z20">
+      <c r="Z22">
         <v>3</v>
       </c>
-      <c r="AA20" t="inlineStr">
+      <c r="AA22" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
+      <c r="AB22" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
+      <c r="AC22" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
+    <row r="23">
+      <c r="A23" t="inlineStr">
         <is>
           <t>KV1</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>NAN</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_NAN_1653908</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>Diamond</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t>Nguyễn Văn Tài</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="K23" t="inlineStr">
         <is>
           <t>0916371137</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="L23" t="inlineStr">
         <is>
           <t>xóm 5 hưng Thịnh Cũ</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr">
+      <c r="N23" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr">
+      <c r="O23" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr">
+      <c r="P23" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q21" t="inlineStr">
+      <c r="Q23" t="inlineStr">
         <is>
           <t>Không kết nối được app/Wifi và không theo dõi được hiệu suất</t>
         </is>
       </c>
-      <c r="R21" t="inlineStr">
+      <c r="R23" t="inlineStr">
         <is>
           <t>1. KH đã báo cn
 2. KH phản ánh: Ivt vẫn hoạt động bthg nhưng vào app chỉ thấy dừng ở 20% và ko kiểm tra được lượng điện vào bao nhiêu.
 3. KH yêu cầu: Kiểm tra xem thiết bị có vấn đề gì không và hướng dẫn KH theo dõi hiệu suất.</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="S23" t="inlineStr">
         <is>
           <t>08:32 24/03/2026</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
+      <c r="T23" t="inlineStr">
         <is>
           <t>20:05 27/03/2026</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="U23" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
+      <c r="V23" t="inlineStr">
         <is>
           <t>Sắp quá hạn</t>
         </is>
       </c>
-      <c r="W21" t="inlineStr">
+      <c r="W23" t="inlineStr">
         <is>
           <t>Phan Bùi Nam</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
+      <c r="X23" t="inlineStr">
         <is>
           <t>119107</t>
         </is>
       </c>
-      <c r="Y21" s="2">
+      <c r="Y23" s="2">
         <v>46105</v>
       </c>
-      <c r="Z21">
+      <c r="Z23">
         <v>3</v>
       </c>
-      <c r="AA21" t="inlineStr">
+      <c r="AA23" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
+      <c r="AB23" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
+      <c r="AC23" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
+    <row r="24">
+      <c r="A24" t="inlineStr">
         <is>
           <t>KV2</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>DLK</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_DLK_1648454</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t>Diamond</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>Huỳnh Chí Băng</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
+      <c r="K24" t="inlineStr">
         <is>
           <t>0366448992</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="L24" t="inlineStr">
         <is>
           <t>Xã Ea Khăl, Tỉnh Đắk Lắk</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr">
+      <c r="N24" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr">
+      <c r="O24" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr">
+      <c r="P24" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q22" t="inlineStr">
+      <c r="Q24" t="inlineStr">
         <is>
           <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
-      <c r="R22" t="inlineStr">
+      <c r="R24" t="inlineStr">
         <is>
           <t>KH đã báo CN: a Nguyễn Văn Hà	nửa thasg nhưng chưa có ai đến hỗ trợ
 KH phản ánh hệ thống điện năng lượng mặt trời ko hoạt động
 KH yêu cầu xử lý gấp</t>
         </is>
       </c>
-      <c r="S22" t="inlineStr">
+      <c r="S24" t="inlineStr">
         <is>
           <t>15:19 24/03/2026</t>
         </is>
       </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>08:45 28/03/2026</t>
-        </is>
-      </c>
-      <c r="U22" t="inlineStr">
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>10:50 31/03/2026</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>Sắp quá hạn</t>
-        </is>
-      </c>
-      <c r="W22" t="inlineStr">
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
         <is>
           <t>Nguyễn Văn Hà</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr">
+      <c r="X24" t="inlineStr">
         <is>
           <t>008244</t>
         </is>
       </c>
-      <c r="Y22" s="2">
+      <c r="Y24" s="2">
         <v>46105</v>
       </c>
-      <c r="Z22">
+      <c r="Z24">
         <v>3</v>
       </c>
-      <c r="AA22" t="inlineStr">
+      <c r="AA24" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
+      <c r="AB24" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
+      <c r="AC24" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>KV1</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>NAN</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>CNTT</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>Camera 360 độ</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>299/2025/HĐKT</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>B2B</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>Khách hàng doanh nghiệp</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>Ban Quản Lý Rừng Phòng Hộ Bắc Nghệ An</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t>0869217169</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="L25" t="inlineStr">
         <is>
           <t>Khối 11, Xã Quỳnh Lưu, Tỉnh Nghệ An</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr">
+      <c r="N25" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr">
+      <c r="O25" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P23" t="inlineStr">
+      <c r="P25" t="inlineStr">
         <is>
           <t>Hỗ trợ</t>
         </is>
       </c>
-      <c r="Q23" t="inlineStr">
+      <c r="Q25" t="inlineStr">
         <is>
           <t>Hướng dẫn, hỗ trợ sử dụng sản phẩm</t>
         </is>
       </c>
-      <c r="R23" t="inlineStr">
+      <c r="R25" t="inlineStr">
         <is>
           <t>1. KH đã báo cn
 2. KH phản ánh: camera 360 chưa kết nối được hệ thống điều khiển, chưa lên được tivi để xem và cũng như pccc rừng mùa khô.
@@ -3610,324 +3883,41 @@
 ***SĐT liên hệ: 0988867428, Anh Thức</t>
         </is>
       </c>
-      <c r="S23" t="inlineStr">
+      <c r="S25" t="inlineStr">
         <is>
           <t>08:45 24/03/2026</t>
         </is>
       </c>
-      <c r="T23" t="inlineStr">
+      <c r="T25" t="inlineStr">
         <is>
           <t>23:05 30/03/2026</t>
         </is>
       </c>
-      <c r="U23" t="inlineStr">
+      <c r="U25" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V23" t="inlineStr">
+      <c r="V25" t="inlineStr">
         <is>
           <t>Trong hạn</t>
         </is>
       </c>
-      <c r="W23" t="inlineStr">
+      <c r="W25" t="inlineStr">
         <is>
           <t>Võ Trọng Đức</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
+      <c r="X25" t="inlineStr">
         <is>
           <t>293804</t>
         </is>
       </c>
-      <c r="Y23" s="2">
+      <c r="Y25" s="2">
         <v>46105</v>
       </c>
-      <c r="Z23">
+      <c r="Z25">
         <v>3</v>
-      </c>
-      <c r="AA23" t="inlineStr">
-        <is>
-          <t>IOC</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>P.Triển khai</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>tietvt16</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>KV3</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>CMU</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>GPTH</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>M&amp;E</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Nồi áp suất</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>KHCN_TT.GPTH_CMU_1265325</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>B2C</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Member</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>Khách hàng cá nhân</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>Bích Loan</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>0946842984</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>Bích Loan Cống Hội Đồng Nguyên</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>Hotline</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>Bình thường</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>Trước bán</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>Sự cố</t>
-        </is>
-      </c>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>Hiệu suất thấp</t>
-        </is>
-      </c>
-      <c r="R24" t="inlineStr">
-        <is>
-          <t>cammera bị off 1 cai</t>
-        </is>
-      </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>10:28 26/03/2026</t>
-        </is>
-      </c>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>10:28 27/03/2026</t>
-        </is>
-      </c>
-      <c r="U24" t="inlineStr">
-        <is>
-          <t>Chưa thực hiện</t>
-        </is>
-      </c>
-      <c r="V24" t="inlineStr">
-        <is>
-          <t>Sắp quá hạn</t>
-        </is>
-      </c>
-      <c r="W24" t="inlineStr">
-        <is>
-          <t>Vũ Thái Sơn</t>
-        </is>
-      </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>284625</t>
-        </is>
-      </c>
-      <c r="Y24" s="2">
-        <v>46107</v>
-      </c>
-      <c r="Z24">
-        <v>1</v>
-      </c>
-      <c r="AA24" t="inlineStr">
-        <is>
-          <t>AIO</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>P.KD Cơ điện</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>P.KD Cơ điện</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>KV3</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>HCM</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>GPTH</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>NLMT</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Hệ thống NLMT</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>1808-2969/BBBG/CNCTHCM-STRIDESOLAR</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>B2B</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>Khách hàng cá nhân</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>CÔNG TY TNHH STRIDE SOLAR</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>0369030903</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>90/52A Đỗ Tuấn Phong, phường Tân Đông Hiệp, Thành phố Hồ Chí Minh</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>Hotline</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>VIP</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>Sau bán</t>
-        </is>
-      </c>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>Hỗ trợ</t>
-        </is>
-      </c>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t>Thủ tục/giấy tờ/ Hóa đơn/ Hồ sơ lắp đặt</t>
-        </is>
-      </c>
-      <c r="R25" t="inlineStr">
-        <is>
-          <t>HĐ NLMT với STRIDE
-1. KH đã báo cn: a Nhân, qua zalo
-2. KH yêu cầu: Hỗ trợ KH hồ sơ để đăng ký nlmt để báo cáo cho bên điện lực.</t>
-        </is>
-      </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>16:17 23/03/2026</t>
-        </is>
-      </c>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>15:45 27/03/2026</t>
-        </is>
-      </c>
-      <c r="U25" t="inlineStr">
-        <is>
-          <t>Đang tiến hành</t>
-        </is>
-      </c>
-      <c r="V25" t="inlineStr">
-        <is>
-          <t>Sắp quá hạn</t>
-        </is>
-      </c>
-      <c r="W25" t="inlineStr">
-        <is>
-          <t>Lê Trương Văn Trọng Nhân</t>
-        </is>
-      </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>200577</t>
-        </is>
-      </c>
-      <c r="Y25" s="2">
-        <v>46104</v>
-      </c>
-      <c r="Z25">
-        <v>4</v>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
@@ -3948,380 +3938,523 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>KV3</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>CMU</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>GPTH</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>CNTT</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Camera</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>KHCN_TT.GPTH_CMU_1265325</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>B2C</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Member</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Khách hàng cá nhân</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Bích Loan</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>0946842984</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>Bích Loan Cống Hội Đồng Nguyên</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Nhân viên nội bộ VCC</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>Sau bán</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Sự cố</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>cammera bị off 1 cai</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>10:28 26/03/2026</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>17:30 28/03/2026</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Đang tiến hành</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Lý Hoài Bảo</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>433302</t>
+        </is>
+      </c>
+      <c r="Y26" s="2">
+        <v>46107</v>
+      </c>
+      <c r="Z26">
+        <v>1</v>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>AIO</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>P.Triển khai</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Tuyendv</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
           <t>KV1</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>HYN</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_HYN_1630850</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>B2B</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t>Diamond</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t>Khách hàng doanh nghiệp</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
+      <c r="J27" t="inlineStr">
         <is>
           <t>CÔNG TY TNHH THƯƠNG MẠI ĐẦU TƯ PHÁT TRIỂN MINH GIA</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
+      <c r="K27" t="inlineStr">
         <is>
           <t>0965326111</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="L27" t="inlineStr">
         <is>
           <t>Số 93 Chu Mạnh Trinh,Phường Hiến Nam,Thành phố Hưng Yên,Tỉnh Hưng Yên</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr">
+      <c r="N27" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr">
+      <c r="O27" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P26" t="inlineStr">
+      <c r="P27" t="inlineStr">
         <is>
           <t>Hỗ trợ</t>
         </is>
       </c>
-      <c r="Q26" t="inlineStr">
+      <c r="Q27" t="inlineStr">
         <is>
           <t>Hỗ trợ lắp đặt</t>
         </is>
       </c>
-      <c r="R26" t="inlineStr">
+      <c r="R27" t="inlineStr">
         <is>
           <t>KH cần hỗ trợ chuyển đường dây điện 1 phòng trong nhà vào hệ thống điện NLMT 
 Quán cf góc kdt 379 Hưng Hà Thái Bình 
 Số liên hệ: chị Hường</t>
         </is>
       </c>
-      <c r="S26" t="inlineStr">
+      <c r="S27" t="inlineStr">
         <is>
           <t>15:02 23/03/2026</t>
         </is>
       </c>
-      <c r="T26" t="inlineStr">
+      <c r="T27" t="inlineStr">
         <is>
           <t>17:45 29/03/2026</t>
         </is>
       </c>
-      <c r="U26" t="inlineStr">
+      <c r="U27" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V26" t="inlineStr">
+      <c r="V27" t="inlineStr">
         <is>
           <t>Trong hạn</t>
         </is>
       </c>
-      <c r="W26" t="inlineStr">
+      <c r="W27" t="inlineStr">
         <is>
           <t>Nguyễn Duy Đức</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr">
+      <c r="X27" t="inlineStr">
         <is>
           <t>282796</t>
         </is>
       </c>
-      <c r="Y26" s="2">
+      <c r="Y27" s="2">
         <v>46104</v>
       </c>
-      <c r="Z26">
+      <c r="Z27">
         <v>4</v>
       </c>
-      <c r="AA26" t="inlineStr">
+      <c r="AA27" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr">
+      <c r="AB27" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
+      <c r="AC27" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
+    <row r="28">
+      <c r="A28" t="inlineStr">
         <is>
           <t>KV3</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>DNI</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_BPC_1427400</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="H28" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
+      <c r="J28" t="inlineStr">
         <is>
           <t>Công Ty Tnhh Phúc An Solutions</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
+      <c r="K28" t="inlineStr">
         <is>
           <t>0972342939</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
+      <c r="L28" t="inlineStr">
         <is>
           <t>abc,Phường An Lộc,Thị xã Bình Long,Tỉnh Bình Phước</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr">
+      <c r="M28" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr">
+      <c r="N28" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O27" t="inlineStr">
+      <c r="O28" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P27" t="inlineStr">
+      <c r="P28" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q27" t="inlineStr">
+      <c r="Q28" t="inlineStr">
         <is>
           <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
-      <c r="R27" t="inlineStr">
+      <c r="R28" t="inlineStr">
         <is>
           <t>1. KH chưa báo cn
 2. KH phản ánh: Cục pin lưu trữ đang ko hoạt động, ko sử dụng được.
 3. KH yêu cầu: Có KT qua kiểm tra, khắc phục tình trạng này cho KH.</t>
         </is>
       </c>
-      <c r="S27" t="inlineStr">
+      <c r="S28" t="inlineStr">
         <is>
           <t>14:29 23/03/2026</t>
         </is>
       </c>
-      <c r="T27" t="inlineStr">
-        <is>
-          <t>16:35 30/03/2026</t>
-        </is>
-      </c>
-      <c r="U27" t="inlineStr">
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>07:20 02/04/2026</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V27" t="inlineStr">
+      <c r="V28" t="inlineStr">
         <is>
           <t>Trong hạn</t>
         </is>
       </c>
-      <c r="W27" t="inlineStr">
+      <c r="W28" t="inlineStr">
         <is>
           <t>Phạm Trung Hiếu</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr">
+      <c r="X28" t="inlineStr">
         <is>
           <t>264250</t>
         </is>
       </c>
-      <c r="Y27" s="2">
+      <c r="Y28" s="2">
         <v>46104</v>
       </c>
-      <c r="Z27">
+      <c r="Z28">
         <v>4</v>
       </c>
-      <c r="AA27" t="inlineStr">
+      <c r="AA28" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
+      <c r="AB28" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
+      <c r="AC28" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
+    <row r="29">
+      <c r="A29" t="inlineStr">
         <is>
           <t>KV2</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>GLI</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>Inverter</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>100901-KD/HDMB-2021/GLI-TT</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>B2B</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t>Member</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t>Khách hàng doanh nghiệp</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
+      <c r="J29" t="inlineStr">
         <is>
           <t>Đồn Biên Phòng 723</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
+      <c r="K29" t="inlineStr">
         <is>
           <t>0862000202</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
+      <c r="L29" t="inlineStr">
         <is>
           <t>Đồn Biên Phòng 723</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr">
+      <c r="M29" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr">
+      <c r="N29" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr">
+      <c r="O29" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P28" t="inlineStr">
+      <c r="P29" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q28" t="inlineStr">
+      <c r="Q29" t="inlineStr">
         <is>
           <t>Inverter không hoạt động</t>
         </is>
       </c>
-      <c r="R28" t="inlineStr">
+      <c r="R29" t="inlineStr">
         <is>
           <t>1.Đã báo chi nhánh chưa: chưa báo 
 2.Đã báo qua đâu: KH gọi TĐ
@@ -4329,290 +4462,290 @@
 4. KH yêu cầu KT qua kiểm tra xử lý cho KH.</t>
         </is>
       </c>
-      <c r="S28" t="inlineStr">
+      <c r="S29" t="inlineStr">
         <is>
           <t>08:00 23/03/2026</t>
         </is>
       </c>
-      <c r="T28" t="inlineStr">
+      <c r="T29" t="inlineStr">
         <is>
           <t>12:45 31/03/2026</t>
         </is>
       </c>
-      <c r="U28" t="inlineStr">
+      <c r="U29" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V28" t="inlineStr">
+      <c r="V29" t="inlineStr">
         <is>
           <t>Trong hạn</t>
         </is>
       </c>
-      <c r="W28" t="inlineStr">
+      <c r="W29" t="inlineStr">
         <is>
           <t>Nguyễn Hà Nguyên</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr">
+      <c r="X29" t="inlineStr">
         <is>
           <t>060709</t>
         </is>
       </c>
-      <c r="Y28" s="2">
+      <c r="Y29" s="2">
         <v>46104</v>
       </c>
-      <c r="Z28">
+      <c r="Z29">
         <v>4</v>
       </c>
-      <c r="AA28" t="inlineStr">
+      <c r="AA29" t="inlineStr">
         <is>
           <t>IOC</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
+      <c r="AB29" t="inlineStr">
         <is>
           <t>P.Triển khai</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
+      <c r="AC29" t="inlineStr">
         <is>
           <t>truongdv17</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
+    <row r="30">
+      <c r="A30" t="inlineStr">
         <is>
           <t>KV2</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>DNG</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>SS</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>Công tắc thông minh</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_DNG_1416913</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t>Member</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
+      <c r="J30" t="inlineStr">
         <is>
           <t>Lê Đắc Quỳ</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
+      <c r="K30" t="inlineStr">
         <is>
           <t>0915313915</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
+      <c r="L30" t="inlineStr">
         <is>
           <t>Phường Hòa Xuân, Thành phố Đà Nẵng</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr">
+      <c r="M30" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr">
+      <c r="N30" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O29" t="inlineStr">
+      <c r="O30" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P29" t="inlineStr">
+      <c r="P30" t="inlineStr">
         <is>
           <t>Hỗ trợ</t>
         </is>
       </c>
-      <c r="Q29" t="inlineStr">
+      <c r="Q30" t="inlineStr">
         <is>
           <t>Hướng dẫn, hỗ trợ sử dụng sản phẩm</t>
         </is>
       </c>
-      <c r="R29" t="inlineStr">
+      <c r="R30" t="inlineStr">
         <is>
           <t>1. KH đã báo cn
 2. KH phản ánh: Vào được aio app smart home nhưng ko thấy có công tắc.
 3. KH yêu cầu: Qua hỗ trợ, kiểm tra thiết bị cho KH, KH sẵn sàng trả phí.</t>
         </is>
       </c>
-      <c r="S29" t="inlineStr">
+      <c r="S30" t="inlineStr">
         <is>
           <t>08:00 23/03/2026</t>
         </is>
       </c>
-      <c r="T29" t="inlineStr">
+      <c r="T30" t="inlineStr">
         <is>
           <t>08:55 30/03/2026</t>
         </is>
       </c>
-      <c r="U29" t="inlineStr">
+      <c r="U30" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V29" t="inlineStr">
+      <c r="V30" t="inlineStr">
         <is>
           <t>Trong hạn</t>
         </is>
       </c>
-      <c r="W29" t="inlineStr">
+      <c r="W30" t="inlineStr">
         <is>
           <t>Ngô Văn Minh</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr">
+      <c r="X30" t="inlineStr">
         <is>
           <t>083585</t>
         </is>
       </c>
-      <c r="Y29" s="2">
+      <c r="Y30" s="2">
         <v>46104</v>
       </c>
-      <c r="Z29">
+      <c r="Z30">
         <v>4</v>
       </c>
-      <c r="AA29" t="inlineStr">
+      <c r="AA30" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB29" t="inlineStr">
+      <c r="AB30" t="inlineStr">
         <is>
           <t>P.Triển khai</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
+      <c r="AC30" t="inlineStr">
         <is>
           <t>Sonln15</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
+    <row r="31">
+      <c r="A31" t="inlineStr">
         <is>
           <t>KV1</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>BNH</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_BGG_1597213</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="H31" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
+      <c r="J31" t="inlineStr">
         <is>
           <t>Dương Văn Quân</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
+      <c r="K31" t="inlineStr">
         <is>
           <t>0359999199</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
+      <c r="L31" t="inlineStr">
         <is>
           <t>xã Hoàng Vân</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr">
+      <c r="M31" t="inlineStr">
         <is>
           <t>Happycall</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr">
+      <c r="N31" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O30" t="inlineStr">
+      <c r="O31" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P30" t="inlineStr">
+      <c r="P31" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q30" t="inlineStr">
+      <c r="Q31" t="inlineStr">
         <is>
           <t>Chất lượng, hiệu suất của sản phẩm/hệ thống thấp</t>
         </is>
       </c>
-      <c r="R30" t="inlineStr">
+      <c r="R31" t="inlineStr">
         <is>
           <t>1.Đã báo chi nhánh chưa: chưa báo
 2.Đã báo qua đâu: DTV HPC
@@ -4620,145 +4753,145 @@
 4.KH yêu cầu KT qua kiểm tra cho KH</t>
         </is>
       </c>
-      <c r="S30" t="inlineStr">
+      <c r="S31" t="inlineStr">
         <is>
           <t>08:00 23/03/2026</t>
         </is>
       </c>
-      <c r="T30" t="inlineStr">
+      <c r="T31" t="inlineStr">
         <is>
           <t>18:00 26/03/2026</t>
         </is>
       </c>
-      <c r="U30" t="inlineStr">
+      <c r="U31" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V30" t="inlineStr">
+      <c r="V31" t="inlineStr">
         <is>
           <t>Quá hạn</t>
         </is>
       </c>
-      <c r="W30" t="inlineStr">
+      <c r="W31" t="inlineStr">
         <is>
           <t>Phạm Văn Huy</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr">
+      <c r="X31" t="inlineStr">
         <is>
           <t>408869</t>
         </is>
       </c>
-      <c r="Y30" s="2">
+      <c r="Y31" s="2">
         <v>46104</v>
       </c>
-      <c r="Z30">
+      <c r="Z31">
         <v>4</v>
       </c>
-      <c r="AA30" t="inlineStr">
+      <c r="AA31" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
+      <c r="AB31" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
+      <c r="AC31" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
+    <row r="32">
+      <c r="A32" t="inlineStr">
         <is>
           <t>KV3</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>CMU</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_CMU_1384534</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="H32" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
+      <c r="J32" t="inlineStr">
         <is>
           <t>Nguyễn Đức Hiếu</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
+      <c r="K32" t="inlineStr">
         <is>
           <t>0949001616</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr">
+      <c r="L32" t="inlineStr">
         <is>
           <t>Khóm 10</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr">
+      <c r="M32" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr">
+      <c r="N32" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O31" t="inlineStr">
+      <c r="O32" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P31" t="inlineStr">
+      <c r="P32" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q31" t="inlineStr">
+      <c r="Q32" t="inlineStr">
         <is>
           <t>Không kết nối được app/Wifi và không theo dõi được hiệu suất</t>
         </is>
       </c>
-      <c r="R31" t="inlineStr">
+      <c r="R32" t="inlineStr">
         <is>
           <t>1.Đã báo chi nhánh chưa: đã báo
 2.Đã báo cho ai:  KT Thái
@@ -4767,172 +4900,34 @@
 5.KH yêu cầu KT qua kiểm tra gấp cho KH.</t>
         </is>
       </c>
-      <c r="S31" t="inlineStr">
+      <c r="S32" t="inlineStr">
         <is>
           <t>09:44 20/03/2026</t>
         </is>
       </c>
-      <c r="T31" t="inlineStr">
+      <c r="T32" t="inlineStr">
         <is>
           <t>19:55 27/03/2026</t>
         </is>
       </c>
-      <c r="U31" t="inlineStr">
+      <c r="U32" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V31" t="inlineStr">
+      <c r="V32" t="inlineStr">
         <is>
           <t>Sắp quá hạn</t>
         </is>
       </c>
-      <c r="W31" t="inlineStr">
+      <c r="W32" t="inlineStr">
         <is>
           <t>Võ Duy Khang</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr">
+      <c r="X32" t="inlineStr">
         <is>
           <t>473069</t>
-        </is>
-      </c>
-      <c r="Y31" s="2">
-        <v>46101</v>
-      </c>
-      <c r="Z31">
-        <v>7</v>
-      </c>
-      <c r="AA31" t="inlineStr">
-        <is>
-          <t>AIO</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>KV1</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>GPTH</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>NLMT</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Hệ thống NLMT</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>VCC_YCTX_NAN_37485587203842849</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>B2C</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>Khách hàng cá nhân</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>Xuân Hương</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>0974371218</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>Xã Nhân Hòa, Tỉnh Nghệ An</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>Happycall</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>Bình thường</t>
-        </is>
-      </c>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>Trước bán</t>
-        </is>
-      </c>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>Hỗ trợ</t>
-        </is>
-      </c>
-      <c r="Q32" t="inlineStr">
-        <is>
-          <t>Tư vấn sản phẩm/dịch vụ</t>
-        </is>
-      </c>
-      <c r="R32" t="inlineStr">
-        <is>
-          <t>KH báo chưa thấy có nv liên hệ để tư vấn NLMT.</t>
-        </is>
-      </c>
-      <c r="S32" t="inlineStr">
-        <is>
-          <t>15:32 20/03/2026</t>
-        </is>
-      </c>
-      <c r="T32" t="inlineStr">
-        <is>
-          <t>17:15 02/04/2026</t>
-        </is>
-      </c>
-      <c r="U32" t="inlineStr">
-        <is>
-          <t>Đang tiến hành</t>
-        </is>
-      </c>
-      <c r="V32" t="inlineStr">
-        <is>
-          <t>Trong hạn</t>
-        </is>
-      </c>
-      <c r="W32" t="inlineStr">
-        <is>
-          <t>Trần Bình Thanh</t>
-        </is>
-      </c>
-      <c r="X32" t="inlineStr">
-        <is>
-          <t>069159</t>
         </is>
       </c>
       <c r="Y32" s="2">
@@ -4943,17 +4938,17 @@
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>IOC</t>
+          <t>AIO</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>P.KDNLMT</t>
+          <t>VHKT</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>P.KDNLMT</t>
+          <t>VHKT</t>
         </is>
       </c>
     </row>
@@ -4965,411 +4960,404 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
+          <t>NAN</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>GPTH</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NLMT</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Hệ thống NLMT</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>VCC_YCTX_NAN_37485587203842849</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>B2C</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Khách hàng cá nhân</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Xuân Hương</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>0974371218</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>Xã Nhân Hòa, Tỉnh Nghệ An</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>Happycall</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>Trước bán</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Hỗ trợ</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>Tư vấn sản phẩm/dịch vụ</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>KH báo chưa thấy có nv liên hệ để tư vấn NLMT.</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>15:32 20/03/2026</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>17:15 02/04/2026</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Đang tiến hành</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Trần Bình Thanh</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>069159</t>
+        </is>
+      </c>
+      <c r="Y33" s="2">
+        <v>46101</v>
+      </c>
+      <c r="Z33">
+        <v>7</v>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>IOC</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>P.KDNLMT</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>P.KDNLMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>KV1</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
           <t>HPG</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>CRP2501952</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t>B2B</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t>Khách hàng doanh nghiệp</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr">
+      <c r="J34" t="inlineStr">
         <is>
           <t>CÔNG TY TNHH UNIVERSAL SCIENTIFIC INDUSTRIAL VIỆT NAM</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
+      <c r="K34" t="inlineStr">
         <is>
           <t>0985479660</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
+      <c r="L34" t="inlineStr">
         <is>
           <t>Lô đất CN4.1H</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr">
+      <c r="M34" t="inlineStr">
         <is>
           <t>Nhân viên nội bộ VCC</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr">
+      <c r="N34" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O33" t="inlineStr">
+      <c r="O34" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P33" t="inlineStr">
+      <c r="P34" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q33" t="inlineStr">
+      <c r="Q34" t="inlineStr">
         <is>
           <t>Lỗi kết nối giữa thiết bị và hệ thống theo dõi</t>
         </is>
       </c>
-      <c r="R33" t="inlineStr">
+      <c r="R34" t="inlineStr">
         <is>
           <t>CN báo sự cố hộ KH
 1. KH phản ánh: Máy chủ scada mất tín hiệu và ko kết nối được với ivt
 2. KH yêu cầu: Qua triển khai, xử lý gấp cho KHDN</t>
         </is>
       </c>
-      <c r="S33" t="inlineStr">
+      <c r="S34" t="inlineStr">
         <is>
           <t>10:55 19/03/2026</t>
         </is>
       </c>
-      <c r="T33" t="inlineStr">
+      <c r="T34" t="inlineStr">
         <is>
           <t>18:00 30/03/2026</t>
         </is>
       </c>
-      <c r="U33" t="inlineStr">
+      <c r="U34" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>Trong hạn</t>
-        </is>
-      </c>
-      <c r="W33" t="inlineStr">
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Sắp quá hạn</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
         <is>
           <t>Lương Ngọc Hưng</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr">
+      <c r="X34" t="inlineStr">
         <is>
           <t>284060</t>
         </is>
       </c>
-      <c r="Y33" s="2">
+      <c r="Y34" s="2">
         <v>46100</v>
       </c>
-      <c r="Z33">
+      <c r="Z34">
         <v>8</v>
       </c>
-      <c r="AA33" t="inlineStr">
+      <c r="AA34" t="inlineStr">
         <is>
           <t>IOC</t>
         </is>
       </c>
-      <c r="AB33" t="inlineStr">
+      <c r="AB34" t="inlineStr">
         <is>
           <t>P.Triển khai</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
+      <c r="AC34" t="inlineStr">
         <is>
           <t>vinhvv4</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
+    <row r="35">
+      <c r="A35" t="inlineStr">
         <is>
           <t>KV3</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>HCM</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="E35" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="F35" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_HCM_1638575</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="H35" t="inlineStr">
         <is>
           <t>Diamond</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
+      <c r="I35" t="inlineStr">
         <is>
           <t>Khách hàng doanh nghiệp</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
+      <c r="J35" t="inlineStr">
         <is>
           <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ TAYOTO</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
+      <c r="K35" t="inlineStr">
         <is>
           <t>0911937779</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
+      <c r="L35" t="inlineStr">
         <is>
           <t>quốc lộ 55, Xã Hồ Tràm, Thành phố Hồ Chí Minh, Xã Hồ Tràm, Thành phố Hồ Chí Minh</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr">
+      <c r="M35" t="inlineStr">
         <is>
           <t>Happycall</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr">
+      <c r="N35" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O34" t="inlineStr">
+      <c r="O35" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P34" t="inlineStr">
+      <c r="P35" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q34" t="inlineStr">
+      <c r="Q35" t="inlineStr">
         <is>
           <t>Sản phẩm bị ngắt quãng/ Không theo dõi và không nghe được</t>
         </is>
       </c>
-      <c r="R34" t="inlineStr">
+      <c r="R35" t="inlineStr">
         <is>
           <t>1. KH chưa báo cn
 2. KH phản ánh: Sự cố từ TT_1772587360264 trước sau khi xử lý KH thấy hệ thống nlmt ko có ổn định, lâu lâu tự ngắt và phải bảo nv tắt 3 công tắc cp đi bật lại mãi mới được.
 3. KH yêu cầu: Kiểm tra lại hàng hóa xem có đúng với HĐ về chất lượng, hiệu suất không. Nếu có vấn đề thì thay mới tinh cho KH để hệ thống vận hành trơn tru.</t>
         </is>
       </c>
-      <c r="S34" t="inlineStr">
+      <c r="S35" t="inlineStr">
         <is>
           <t>09:25 19/03/2026</t>
         </is>
       </c>
-      <c r="T34" t="inlineStr">
+      <c r="T35" t="inlineStr">
         <is>
           <t>08:35 25/04/2026</t>
         </is>
       </c>
-      <c r="U34" t="inlineStr">
+      <c r="U35" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V34" t="inlineStr">
+      <c r="V35" t="inlineStr">
         <is>
           <t>Trong hạn</t>
         </is>
       </c>
-      <c r="W34" t="inlineStr">
+      <c r="W35" t="inlineStr">
         <is>
           <t>Lê Đức Cảnh</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr">
+      <c r="X35" t="inlineStr">
         <is>
           <t>291002</t>
         </is>
       </c>
-      <c r="Y34" s="2">
+      <c r="Y35" s="2">
         <v>46100</v>
       </c>
-      <c r="Z34">
+      <c r="Z35">
         <v>8</v>
-      </c>
-      <c r="AA34" t="inlineStr">
-        <is>
-          <t>AIO</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>KV1</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>BNH</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>GPTH</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>NLMT</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>Hệ thống NLMT</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>KHCN_TT.GPTH_BNH_1615873</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>B2C</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>Khách hàng cá nhân</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>Công Ty Tnhh Thương Mại Vận Tải Hùng Vĩ</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>0989558605</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>Phường Xương Giang,Thành phố Bắc Giang,Tỉnh Bắc Giang</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>Hotline</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>Bình thường</t>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>Sau bán</t>
-        </is>
-      </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>Sự cố</t>
-        </is>
-      </c>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>Thiết bị vỡ, hỏng, chập cháy</t>
-        </is>
-      </c>
-      <c r="R35" t="inlineStr">
-        <is>
-          <t>1. KH chưa báo cn
-2. KH phản ánh: Từ hqua tầm 10h tối, KH nghe thấy tiếng oạch 1 cái rồi mất điện xong 1 lúc sau lại thấy có ngay, KH ktra thì thấy biến tần ko chạy và thấy báo đỏ, ko hoạt động, theo dõi trên đt cũng thấy đang có vấn đề.
-3. KH yêu cầu: Qua hỗ trợ, kiểm tra nguyên nhân dẫn đến tình trạng và khắc phục cho KH.</t>
-        </is>
-      </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>09:25 18/03/2026</t>
-        </is>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>18:00 29/03/2026</t>
-        </is>
-      </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>Đang tiến hành</t>
-        </is>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>Sắp quá hạn</t>
-        </is>
-      </c>
-      <c r="W35" t="inlineStr">
-        <is>
-          <t>Hoàng Văn Chính</t>
-        </is>
-      </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>284663</t>
-        </is>
-      </c>
-      <c r="Y35" s="2">
-        <v>46099</v>
-      </c>
-      <c r="Z35">
-        <v>9</v>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
@@ -5395,223 +5383,85 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>NBH</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>DVKT</t>
+          <t>GPTH</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Home Service</t>
+          <t>NLMT</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Bảo dưỡng Điều hòa treo tường (9.000BTU ÷ 12.000 BTU)</t>
+          <t>Acquy lưu trữ</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>VCC_HS_HPG_1773463559534</t>
+          <t>KHDN_TT.GPTH_NBH_1627573</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>B2C</t>
+          <t>B2B</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Diamond</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Khách hàng cá nhân</t>
+          <t>Khách hàng doanh nghiệp</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Anh Nhuận</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ GIANG HOÀNG HẢI</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>0398685088</t>
+          <t>0836461111</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>493 đông hải hải an, Phường Hải An, Hải Phòng</t>
+          <t>Đường vĩnh lợi, phố mỹ lộ, p hoa lư, ninh bình</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Hotline</t>
+          <t>Nhân viên nội bộ VCC</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>Hot</t>
+          <t>Bình thường</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>Trong bán</t>
+          <t>Sau bán</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Khiếu nại</t>
+          <t>Bảo hành</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>Liên hệ chậm</t>
+          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
-        <is>
-          <t>KH gọi lên TĐ phản ánh KH đặt lịch bảo dưỡng từ ngày 14/3 nhưng ko có kỹ thuật liên hệ hẹn lịch, kh rất bức xúc yc kiểm tra lý do và yêu cầu VCC phản hồi thông tin cho kh qua email: hoanphihoan1987@gmail.com</t>
-        </is>
-      </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>13:31 16/03/2026</t>
-        </is>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>09:00 17/03/2026</t>
-        </is>
-      </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>Đang tiến hành</t>
-        </is>
-      </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>Trong hạn</t>
-        </is>
-      </c>
-      <c r="W36" t="inlineStr">
-        <is>
-          <t>Phạm Quang Toàn</t>
-        </is>
-      </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>048813</t>
-        </is>
-      </c>
-      <c r="Y36" s="2">
-        <v>46097</v>
-      </c>
-      <c r="Z36">
-        <v>11</v>
-      </c>
-      <c r="AA36" t="inlineStr">
-        <is>
-          <t>HS</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>KV1</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>NBH</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>GPTH</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>NLMT</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>Acquy lưu trữ</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>KHDN_TT.GPTH_NBH_1627573</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>B2B</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Diamond</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>Khách hàng doanh nghiệp</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ GIANG HOÀNG HẢI</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>0836461111</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>Đường vĩnh lợi, phố mỹ lộ, p hoa lư, ninh bình</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>Nhân viên nội bộ VCC</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>Bình thường</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>Sau bán</t>
-        </is>
-      </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>Bảo hành</t>
-        </is>
-      </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
-        </is>
-      </c>
-      <c r="R37" t="inlineStr">
         <is>
           <t>CN báo sự cố cho KH (0985951652)
 1.Đã báo chi nhánh chưa: có báo
@@ -5621,14 +5471,157 @@
 4. KH yêu cầu KT qua kiểm tra gấp cho KH</t>
         </is>
       </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>10:57 17/03/2026</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>11:46 10/04/2026</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Đang tiến hành</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Phạm Văn Đông</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>449553</t>
+        </is>
+      </c>
+      <c r="Y36" s="2">
+        <v>46098</v>
+      </c>
+      <c r="Z36">
+        <v>10</v>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>AIO</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>KV3</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>HCM</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>GPTH</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NLMT</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Hệ thống NLMT</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>KHCN_TT.GPTH_HCM_1646383</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>B2C</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Diamond</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Khách hàng cá nhân</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Nguyễn Hữu Nghĩa</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>0945919596</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>Phường Tam Thắng, Thành phố Hồ Chí Minh, Phường Tam Thắng, Thành phố Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>Happycall</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>Sau bán</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Hỗ trợ</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>Hướng dẫn, hỗ trợ sử dụng sản phẩm</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>KH yc ktra nguyên nhân xảy ra sự cố TT_1772849052506</t>
+        </is>
+      </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>10:57 17/03/2026</t>
+          <t>08:00 16/03/2026</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>11:46 10/04/2026</t>
+          <t>08:45 12/04/2026</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -5643,19 +5636,19 @@
       </c>
       <c r="W37" t="inlineStr">
         <is>
-          <t>Phạm Văn Đông</t>
+          <t>Lê Đức Cảnh</t>
         </is>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>449553</t>
+          <t>291002</t>
         </is>
       </c>
       <c r="Y37" s="2">
-        <v>46098</v>
+        <v>46097</v>
       </c>
       <c r="Z37">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
@@ -5676,12 +5669,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>KV3</t>
+          <t>KV1</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>BNH</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -5701,7 +5694,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>KHCN_TT.GPTH_HCM_1646383</t>
+          <t>KHCN_PINNLMT_BGG_0404930</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -5711,7 +5704,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Diamond</t>
+          <t>Member</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -5721,22 +5714,22 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Nguyễn Hữu Nghĩa</t>
+          <t>Lê Văn Mạnh</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>0945919596</t>
+          <t>0987567050</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>Phường Tam Thắng, Thành phố Hồ Chí Minh, Phường Tam Thắng, Thành phố Hồ Chí Minh</t>
+          <t>Xã Liên Chung,Huyện Tân Yên,Tỉnh Bắc Giang</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Happycall</t>
+          <t>Hotline</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -5751,158 +5744,15 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Hỗ trợ</t>
+          <t>Sự cố</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>Hướng dẫn, hỗ trợ sử dụng sản phẩm</t>
+          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
-        <is>
-          <t>KH yc ktra nguyên nhân xảy ra sự cố TT_1772849052506</t>
-        </is>
-      </c>
-      <c r="S38" t="inlineStr">
-        <is>
-          <t>08:00 16/03/2026</t>
-        </is>
-      </c>
-      <c r="T38" t="inlineStr">
-        <is>
-          <t>08:45 12/04/2026</t>
-        </is>
-      </c>
-      <c r="U38" t="inlineStr">
-        <is>
-          <t>Đang tiến hành</t>
-        </is>
-      </c>
-      <c r="V38" t="inlineStr">
-        <is>
-          <t>Trong hạn</t>
-        </is>
-      </c>
-      <c r="W38" t="inlineStr">
-        <is>
-          <t>Lê Đức Cảnh</t>
-        </is>
-      </c>
-      <c r="X38" t="inlineStr">
-        <is>
-          <t>291002</t>
-        </is>
-      </c>
-      <c r="Y38" s="2">
-        <v>46097</v>
-      </c>
-      <c r="Z38">
-        <v>11</v>
-      </c>
-      <c r="AA38" t="inlineStr">
-        <is>
-          <t>AIO</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>KV1</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>BNH</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>GPTH</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>NLMT</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>Hệ thống NLMT</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>KHCN_PINNLMT_BGG_0345907</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>B2C</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Member</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>Khách hàng cá nhân</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>Lê Văn Mạnh</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>0987567050</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>Xã Liên Chung,Huyện Tân Yên,Tỉnh Bắc Giang</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>Hotline</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>Bình thường</t>
-        </is>
-      </c>
-      <c r="O39" t="inlineStr">
-        <is>
-          <t>Sau bán</t>
-        </is>
-      </c>
-      <c r="P39" t="inlineStr">
-        <is>
-          <t>Sự cố</t>
-        </is>
-      </c>
-      <c r="Q39" t="inlineStr">
-        <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
-        </is>
-      </c>
-      <c r="R39" t="inlineStr">
         <is>
           <t>1.Đã báo chi nhánh chưa: đã báo
 2.KH báo cho GĐ Trường 
@@ -5911,14 +5761,154 @@
  5.KH yêu cầu KT qua kiểm tra gấp cho KH.</t>
         </is>
       </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>10:21 10/03/2026</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>09:00 30/03/2026</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Đang tiến hành</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Sắp quá hạn</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Thân Đức Giang</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>081984</t>
+        </is>
+      </c>
+      <c r="Y38" s="2">
+        <v>46091</v>
+      </c>
+      <c r="Z38">
+        <v>17</v>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>AIO</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>KV2</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>QTI</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>GPTH</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NLMT</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Hệ thống NLMT</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>KHCN_TT.GPTH_QTI_0991884</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>B2C</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Khách hàng cá nhân</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Nguyễn Thị Như Mỹ</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>0963369267</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>KP4, Thị trấn Cam Lộ, Huyện Cam Lộ, Tỉnh Quảng Trị</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>Hotline</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>Sau bán</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Bảo hành</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>1. KH đã báo cn: a Nguyễn Đình Bằng bên nlmt
+2. KH phản ánh: Hệ thống inverter báo lỗi mã lỗi 01.M011 và ko đẩy ra sản lượng điện nlmt.
+3. KH yêu cầu: Điều KT qua hỗ trợ giúp KH.</t>
+        </is>
+      </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>10:21 10/03/2026</t>
+          <t>08:00 09/03/2026</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>20:40 26/03/2026</t>
+          <t>11:45 10/04/2026</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -5928,24 +5918,24 @@
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="W39" t="inlineStr">
         <is>
-          <t>Thân Đức Giang</t>
+          <t>Trương Thành</t>
         </is>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>081984</t>
+          <t>462341</t>
         </is>
       </c>
       <c r="Y39" s="2">
-        <v>46091</v>
+        <v>46090</v>
       </c>
       <c r="Z39">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
@@ -5971,7 +5961,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>QTI</t>
+          <t>QNI</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -5986,12 +5976,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Hệ thống NLMT</t>
+          <t>Tấm pin NLMT</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>KHCN_TT.GPTH_QTI_0991884</t>
+          <t>KHCN_PINNLMT_KTM_0284233</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -6006,17 +5996,17 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Nguyễn Thị Như Mỹ</t>
+          <t>Nguyễn Xuân Quyết</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>0963369267</t>
+          <t>0981397050</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>KP4, Thị trấn Cam Lộ, Huyện Cam Lộ, Tỉnh Quảng Trị</t>
+          <t>Khối phố 6, Thị trấn Plei Kần, Huyện Ngọc Hồi, Tỉnh Kon Tum</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -6036,7 +6026,7 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Bảo hành</t>
+          <t>Sự cố</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
@@ -6045,146 +6035,6 @@
         </is>
       </c>
       <c r="R40" t="inlineStr">
-        <is>
-          <t>1. KH đã báo cn: a Nguyễn Đình Bằng bên nlmt
-2. KH phản ánh: Hệ thống inverter báo lỗi mã lỗi 01.M011 và ko đẩy ra sản lượng điện nlmt.
-3. KH yêu cầu: Điều KT qua hỗ trợ giúp KH.</t>
-        </is>
-      </c>
-      <c r="S40" t="inlineStr">
-        <is>
-          <t>08:00 09/03/2026</t>
-        </is>
-      </c>
-      <c r="T40" t="inlineStr">
-        <is>
-          <t>11:45 10/04/2026</t>
-        </is>
-      </c>
-      <c r="U40" t="inlineStr">
-        <is>
-          <t>Đang tiến hành</t>
-        </is>
-      </c>
-      <c r="V40" t="inlineStr">
-        <is>
-          <t>Trong hạn</t>
-        </is>
-      </c>
-      <c r="W40" t="inlineStr">
-        <is>
-          <t>Trương Thành</t>
-        </is>
-      </c>
-      <c r="X40" t="inlineStr">
-        <is>
-          <t>462341</t>
-        </is>
-      </c>
-      <c r="Y40" s="2">
-        <v>46090</v>
-      </c>
-      <c r="Z40">
-        <v>18</v>
-      </c>
-      <c r="AA40" t="inlineStr">
-        <is>
-          <t>AIO</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>KV2</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>QNI</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>GPTH</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>NLMT</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>Tấm pin NLMT</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>KHCN_PINNLMT_KTM_0284233</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>B2C</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>Khách hàng cá nhân</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>Nguyễn Xuân Quyết</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>0981397050</t>
-        </is>
-      </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>Khối phố 6, Thị trấn Plei Kần, Huyện Ngọc Hồi, Tỉnh Kon Tum</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>Hotline</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>Bình thường</t>
-        </is>
-      </c>
-      <c r="O41" t="inlineStr">
-        <is>
-          <t>Sau bán</t>
-        </is>
-      </c>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t>Sự cố</t>
-        </is>
-      </c>
-      <c r="Q41" t="inlineStr">
-        <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
-        </is>
-      </c>
-      <c r="R41" t="inlineStr">
         <is>
           <t>1.Đã báo chi nhánh chưa: đã báo 
 2.Đã báo cho ai:  NV Văn
@@ -6193,145 +6043,145 @@
 5.	 KH yêu cầu KT qua kiểm tra gấp cho KH</t>
         </is>
       </c>
-      <c r="S41" t="inlineStr">
+      <c r="S40" t="inlineStr">
         <is>
           <t>14:54 05/03/2026</t>
         </is>
       </c>
-      <c r="T41" t="inlineStr">
+      <c r="T40" t="inlineStr">
         <is>
           <t>17:00 31/03/2026</t>
         </is>
       </c>
-      <c r="U41" t="inlineStr">
+      <c r="U40" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V41" t="inlineStr">
+      <c r="V40" t="inlineStr">
         <is>
           <t>Sắp quá hạn</t>
         </is>
       </c>
-      <c r="W41" t="inlineStr">
+      <c r="W40" t="inlineStr">
         <is>
           <t>Đỗ Lê Thanh Dĩnh</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr">
+      <c r="X40" t="inlineStr">
         <is>
           <t>041111</t>
         </is>
       </c>
-      <c r="Y41" s="2">
+      <c r="Y40" s="2">
         <v>46086</v>
       </c>
-      <c r="Z41">
+      <c r="Z40">
         <v>22</v>
       </c>
-      <c r="AA41" t="inlineStr">
+      <c r="AA40" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB41" t="inlineStr">
+      <c r="AB40" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
+      <c r="AC40" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
+    <row r="41">
+      <c r="A41" t="inlineStr">
         <is>
           <t>KV3</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>HCM</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="D41" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="E41" t="inlineStr">
         <is>
           <t>Inverter</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="F41" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_VTU_1502475</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
+      <c r="H41" t="inlineStr">
         <is>
           <t>Diamond</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
+      <c r="I41" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr">
+      <c r="J41" t="inlineStr">
         <is>
           <t>Nguyễn Phú Quý</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr">
+      <c r="K41" t="inlineStr">
         <is>
           <t>0947110192</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr">
+      <c r="L41" t="inlineStr">
         <is>
           <t>120 Chu Mạnh Trinh,Phường 8,Thành phố Vũng Tàu,Tỉnh Bà Rịa - Vũng Tàu, Phường Tam Thắng, Thành phố Hồ Chí Minh</t>
         </is>
       </c>
-      <c r="M42" t="inlineStr">
+      <c r="M41" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N42" t="inlineStr">
+      <c r="N41" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O42" t="inlineStr">
+      <c r="O41" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P42" t="inlineStr">
+      <c r="P41" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q42" t="inlineStr">
+      <c r="Q41" t="inlineStr">
         <is>
           <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
-      <c r="R42" t="inlineStr">
+      <c r="R41" t="inlineStr">
         <is>
           <t>1. Đã báo chi nhánh chưa: chưa báo
 2.KH gọi điện lên TĐ
@@ -6339,14 +6189,154 @@
 4.KH yêu cầu Kt kiểm tra lại pin và CN đưa ra phương án xử lý vấn đề thiệt hại kinh tế cho KH khi sử dụng điện NLMT không hiệu quả.</t>
         </is>
       </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>15:09 03/03/2026</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>12:55 15/03/2026</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Đang tiến hành</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Lê Đức Cảnh</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>291002</t>
+        </is>
+      </c>
+      <c r="Y41" s="2">
+        <v>46084</v>
+      </c>
+      <c r="Z41">
+        <v>24</v>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>AIO</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>KV1</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>NAN</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>GPTH</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>CNTT</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Camera</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>081101/HĐMBLĐ-2024/THQUYNHHUNG-NAN</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>B2B</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Khách hàng doanh nghiệp</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Trường Tiểu Học Quỳnh Hưng</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>0963785576</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>Xóm 6,Xã Quỳnh Hưng,Huyện Quỳnh Lưu,Tỉnh Nghệ An</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>Hotline</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>Sau bán</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Sự cố</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>1. Kh chưa báo cn
+2. Kh phản ánh: Hiện tại ko có mắt cam nào xem đc, mạng thì vẫn bình thường
+3. Kh yc: Yc cn hỗ trợ</t>
+        </is>
+      </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>15:09 03/03/2026</t>
+          <t>16:54 26/02/2026</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>12:55 15/03/2026</t>
+          <t>18:00 31/03/2026</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -6356,50 +6346,50 @@
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>Trong hạn</t>
+          <t>Sắp quá hạn</t>
         </is>
       </c>
       <c r="W42" t="inlineStr">
         <is>
-          <t>Lê Đức Cảnh</t>
+          <t>Lê Văn Toán</t>
         </is>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>291002</t>
+          <t>119464</t>
         </is>
       </c>
       <c r="Y42" s="2">
-        <v>46084</v>
+        <v>46079</v>
       </c>
       <c r="Z42">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>AIO</t>
+          <t>IOC</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>VHKT</t>
+          <t>P.Triển khai</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>VHKT</t>
+          <t>tietvt16</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>KV1</t>
+          <t>KV3</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -6409,17 +6399,17 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>CNTT</t>
+          <t>NLMT</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Camera</t>
+          <t>Hệ thống NLMT</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>081101/HĐMBLĐ-2024/THQUYNHHUNG-NAN</t>
+          <t>KHDN_TT.GPTH_DNI_1659133</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -6427,6 +6417,11 @@
           <t>B2B</t>
         </is>
       </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Diamond</t>
+        </is>
+      </c>
       <c r="I43" t="inlineStr">
         <is>
           <t>Khách hàng doanh nghiệp</t>
@@ -6434,17 +6429,17 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Trường Tiểu Học Quỳnh Hưng</t>
+          <t>CÔNG TY TNHH KHOA HỌC KỸ THUẬT TOÀN CẦU</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>0963785576</t>
+          <t>0907002673</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>Xóm 6,Xã Quỳnh Hưng,Huyện Quỳnh Lưu,Tỉnh Nghệ An</t>
+          <t>Lầu 19, Khu A, Số 4 Nguyễn Đình Chiểu, Phường Tân Định, Thành phố Hồ Chí Minh</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -6454,7 +6449,7 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>Bình thường</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
@@ -6464,7 +6459,7 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Sự cố</t>
+          <t>Bảo hành</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
@@ -6474,19 +6469,19 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>1. Kh chưa báo cn
-2. Kh phản ánh: Hiện tại ko có mắt cam nào xem đc, mạng thì vẫn bình thường
-3. Kh yc: Yc cn hỗ trợ</t>
+          <t>1. Kh đã báo cn
+2. Kh phản ánh: Hệ của kh dạo này sd có hiện tượng liên tục bị sập. Kh đã báo kt và kt phản hồi do kh sd quá tải nhưng từ khi lắp đến nay kh báo chỉ dùng bằng đó thiết bị chứ ko hơn
+3. kh yc: YC cn hỗ trợ sớm</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>16:54 26/02/2026</t>
+          <t>13:30 23/02/2026</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>18:00 31/03/2026</t>
+          <t>18:30 21/03/2026</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -6496,50 +6491,50 @@
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>Sắp quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="W43" t="inlineStr">
         <is>
-          <t>Lê Văn Toán</t>
+          <t>Nguyễn Hữu Tâm Định</t>
         </is>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>119464</t>
+          <t>450471</t>
         </is>
       </c>
       <c r="Y43" s="2">
-        <v>46079</v>
+        <v>46076</v>
       </c>
       <c r="Z43">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>IOC</t>
+          <t>AIO</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>P.Triển khai</t>
+          <t>VHKT</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>tietvt16</t>
+          <t>VHKT</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>KV3</t>
+          <t>KV1</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>NAN</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -6554,42 +6549,37 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Hệ thống NLMT</t>
+          <t>Inverter</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>KHDN_TT.GPTH_DNI_1659133</t>
+          <t>KHCN_PINNLMT_NAN_0334667</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>B2B</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Diamond</t>
+          <t>B2C</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Khách hàng doanh nghiệp</t>
+          <t>Khách hàng cá nhân</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH KHOA HỌC KỸ THUẬT TOÀN CẦU</t>
+          <t>Lê Trung An</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>0907002673</t>
+          <t>0865878212</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>Lầu 19, Khu A, Số 4 Nguyễn Đình Chiểu, Phường Tân Định, Thành phố Hồ Chí Minh</t>
+          <t>xóm 9, Xã Đại Sơn, Huyện Đô Lương, Tỉnh Nghệ An</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -6609,7 +6599,7 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Bảo hành</t>
+          <t>Sự cố</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
@@ -6619,19 +6609,18 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>1. Kh đã báo cn
-2. Kh phản ánh: Hệ của kh dạo này sd có hiện tượng liên tục bị sập. Kh đã báo kt và kt phản hồi do kh sd quá tải nhưng từ khi lắp đến nay kh báo chỉ dùng bằng đó thiết bị chứ ko hơn
-3. kh yc: YC cn hỗ trợ sớm</t>
+          <t>- KH phản ánh ivt mới mang bảo hành về được mấy hôm lại lỗi không sử dụng được
+- KH Yc cho nv qua htro khắc phục triệt để</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>13:30 23/02/2026</t>
+          <t>16:02 26/01/2026</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>18:30 21/03/2026</t>
+          <t>10:00 30/03/2026</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
@@ -6646,19 +6635,19 @@
       </c>
       <c r="W44" t="inlineStr">
         <is>
-          <t>Nguyễn Hữu Tâm Định</t>
+          <t>Nguyễn Minh Linh</t>
         </is>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>450471</t>
+          <t>285776</t>
         </is>
       </c>
       <c r="Y44" s="2">
-        <v>46076</v>
+        <v>46048</v>
       </c>
       <c r="Z44">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
@@ -6704,7 +6693,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>KHCN_PINNLMT_NAN_0334667</t>
+          <t>KHCN_TT.GPTH_NAN_1364237</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -6712,6 +6701,11 @@
           <t>B2C</t>
         </is>
       </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="I45" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
@@ -6719,17 +6713,17 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Lê Trung An</t>
+          <t>Trương Công An</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>0865878212</t>
+          <t>0914531694</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>xóm 9, Xã Đại Sơn, Huyện Đô Lương, Tỉnh Nghệ An</t>
+          <t>khối 2</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -6749,7 +6743,7 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Sự cố</t>
+          <t>Bảo hành</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
@@ -6759,18 +6753,18 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>- KH phản ánh ivt mới mang bảo hành về được mấy hôm lại lỗi không sử dụng được
-- KH Yc cho nv qua htro khắc phục triệt để</t>
+          <t>- KH phản ánh nhân sự Lê Văn Anh mang thiết bị ivt đi bảo hành từ 8/12/2025  tới nay 16/1/2026 vẫn chưa có ivt gửi về cho KH. Đã rất lâu và thiệt hại rất nhiều, trước đấy có mang ắc quy đi BH cũng k được giờ mang ivt đi hơn tháng chưa thấy phản hồi 
+- KH Yc ktra lại và phản hồi mang thiết bị về lắp đặt  lại cho KH</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>16:02 26/01/2026</t>
+          <t>08:00 19/01/2026</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>10:00 30/03/2026</t>
+          <t>22:00 17/04/2026</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
@@ -6785,19 +6779,19 @@
       </c>
       <c r="W45" t="inlineStr">
         <is>
-          <t>Nguyễn Minh Linh</t>
+          <t>Lê Văn Anh</t>
         </is>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>285776</t>
+          <t>069170</t>
         </is>
       </c>
       <c r="Y45" s="2">
-        <v>46048</v>
+        <v>46041</v>
       </c>
       <c r="Z45">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
@@ -6823,7 +6817,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -6838,12 +6832,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Inverter</t>
+          <t>Hệ thống NLMT</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>KHCN_TT.GPTH_NAN_1364237</t>
+          <t>KHCN_TT.GPTH_TNN_0885867</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -6851,11 +6845,6 @@
           <t>B2C</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
       <c r="I46" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
@@ -6863,17 +6852,17 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Trương Công An</t>
+          <t>Nguyễn Đức Hùng</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>0914531694</t>
+          <t>0396264028</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>khối 2</t>
+          <t>Xóm Ấp Chè, Xã Văn Hán, Huyện Đồng Hỷ, Tỉnh Thái Nguyên</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -6883,7 +6872,7 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>Hot</t>
+          <t>Bình thường</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
@@ -6903,18 +6892,19 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>- KH phản ánh nhân sự Lê Văn Anh mang thiết bị ivt đi bảo hành từ 8/12/2025  tới nay 16/1/2026 vẫn chưa có ivt gửi về cho KH. Đã rất lâu và thiệt hại rất nhiều, trước đấy có mang ắc quy đi BH cũng k được giờ mang ivt đi hơn tháng chưa thấy phản hồi 
-- KH Yc ktra lại và phản hồi mang thiết bị về lắp đặt  lại cho KH</t>
+          <t>1. Đã báo CN: Chưa báo
+2. KH báo sự cố: 1 cục pin lưu trữ không vào điện và khi mất điện lưới hệ không tải điện vào để sử dụng.
+3. Kh yêu cầu: KT qua kiểm tra cho Kh</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>08:00 19/01/2026</t>
+          <t>08:00 14/01/2026</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>22:00 17/04/2026</t>
+          <t>17:00 25/02/2026</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
@@ -6929,19 +6919,19 @@
       </c>
       <c r="W46" t="inlineStr">
         <is>
-          <t>Lê Văn Anh</t>
+          <t>Trần Xuân Kương</t>
         </is>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>069170</t>
+          <t>289759</t>
         </is>
       </c>
       <c r="Y46" s="2">
-        <v>46041</v>
+        <v>46036</v>
       </c>
       <c r="Z46">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
@@ -6967,7 +6957,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>QNH</t>
+          <t>BNH</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -6977,52 +6967,57 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NLMT</t>
+          <t>M&amp;E</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Inverter</t>
+          <t>Bếp từ</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>KHDN_TT.GPTH_QNH_1468057</t>
+          <t>KHDN_TT.GPTH_HNI_2402026_CDV</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>B2B</t>
+          <t>B2C</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Silver</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Khách hàng doanh nghiệp</t>
+          <t>Khách hàng cá nhân</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN ĐẦU TƯ VÀ PHÁT TRIỂN BẤT ĐỘNG SẢN TOÀN CẦU</t>
+          <t>Nguyễn Quang Vũ</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>0989815656</t>
+          <t>0983034568</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>Phường Bãi Cháy,Thành phố Hạ Long,Tỉnh Quảng Ninh</t>
+          <t>CNCT Viettel Bắc Ninh</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Hotline</t>
+          <t>Nhân viên nội bộ VCC</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>Hot</t>
+          <t>Bình thường</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
@@ -7032,32 +7027,28 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Sự cố</t>
+          <t>Bảo hành</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>Chất lượng, hiệu suất của sản phẩm/hệ thống thấp</t>
+          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>1. Kh chưa báo cn
-2. Kh phản ánh:
-- Hiện tại kh làm mất bản hđ giấy của hệ nlmt 12A Triều Khúc (Hà Nội) (mã hđ 	KHDN_TT.GPTH_QNH_1426314) -&gt; cần cn hỗ trợ làm lại và gửi lại cho kh
-- Kh phản ánh hệ nlmt ở Quảng NInh KHDN_TT.GPTH_QNH_1468057 các tháng trước đó tiền điện đều đều từ 1tr5-2tr nhưng tháng vừa rồi lại vọt lên 5tr
-3. Kh yc: Yc cn hỗ trợ kh sớm
-*Ghi chú: sdt phản ánh 0981972868</t>
+          <t>KH nội bộ VCC T12/2025 quay số trúng thưởng bếp từ đơn AIO, bếp không hoạt động. Yêu cầu Kt qua bảo hành gấp. 
+Quà tặng trúng thưởng nên không có thông tin mã HĐ.</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>08:19 15/01/2026</t>
+          <t>08:00 05/01/2026</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>16:00 20/01/2026</t>
+          <t>10:25 03/04/2026</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
@@ -7067,24 +7058,24 @@
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="W47" t="inlineStr">
         <is>
-          <t>Lê Thanh Tú</t>
+          <t>Đinh Thị Ngọc</t>
         </is>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>113238</t>
+          <t>205029</t>
         </is>
       </c>
       <c r="Y47" s="2">
-        <v>46037</v>
+        <v>46027</v>
       </c>
       <c r="Z47">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
@@ -7093,12 +7084,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>VHKT</t>
+          <t>P.Triển khai</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>VHKT</t>
+          <t>Anhnt631</t>
         </is>
       </c>
     </row>
@@ -7110,52 +7101,52 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>QNH</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>GPTH</t>
+          <t>DVKT</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NLMT</t>
+          <t>Home Service</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Hệ thống NLMT</t>
+          <t>Dịch vụ khác</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>KHCN_TT.GPTH_TNN_0885867</t>
+          <t>23092025/HĐTP-SPT-VIETTEL</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>B2C</t>
+          <t>B2B</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Khách hàng cá nhân</t>
+          <t>Khách hàng doanh nghiệp</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Nguyễn Đức Hùng</t>
+          <t>CÔNG TY CỔ PHẦN SPT VIỆT NAM</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>0396264028</t>
+          <t>0962892720</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>Xóm Ấp Chè, Xã Văn Hán, Huyện Đồng Hỷ, Tỉnh Thái Nguyên</t>
+          <t>...</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -7165,309 +7156,25 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>Bình thường</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>Sau bán</t>
+          <t>Trong bán</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Bảo hành</t>
+          <t>Khiếu nại</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Tiến độ triển khai chậm</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
-        <is>
-          <t>1. Đã báo CN: Chưa báo
-2. KH báo sự cố: 1 cục pin lưu trữ không vào điện và khi mất điện lưới hệ không tải điện vào để sử dụng.
-3. Kh yêu cầu: KT qua kiểm tra cho Kh</t>
-        </is>
-      </c>
-      <c r="S48" t="inlineStr">
-        <is>
-          <t>08:00 14/01/2026</t>
-        </is>
-      </c>
-      <c r="T48" t="inlineStr">
-        <is>
-          <t>17:00 25/02/2026</t>
-        </is>
-      </c>
-      <c r="U48" t="inlineStr">
-        <is>
-          <t>Đang tiến hành</t>
-        </is>
-      </c>
-      <c r="V48" t="inlineStr">
-        <is>
-          <t>Trong hạn</t>
-        </is>
-      </c>
-      <c r="W48" t="inlineStr">
-        <is>
-          <t>Trần Xuân Kương</t>
-        </is>
-      </c>
-      <c r="X48" t="inlineStr">
-        <is>
-          <t>289759</t>
-        </is>
-      </c>
-      <c r="Y48" s="2">
-        <v>46036</v>
-      </c>
-      <c r="Z48">
-        <v>72</v>
-      </c>
-      <c r="AA48" t="inlineStr">
-        <is>
-          <t>AIO</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>KV1</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>BNH</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>GPTH</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>M&amp;E</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>Bếp từ</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>KHDN_TT.GPTH_HNI_2402026_CDV</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>B2C</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Silver</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>Khách hàng cá nhân</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>Nguyễn Quang Vũ</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>0983034568</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>CNCT Viettel Bắc Ninh</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>Nhân viên nội bộ VCC</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>Bình thường</t>
-        </is>
-      </c>
-      <c r="O49" t="inlineStr">
-        <is>
-          <t>Sau bán</t>
-        </is>
-      </c>
-      <c r="P49" t="inlineStr">
-        <is>
-          <t>Bảo hành</t>
-        </is>
-      </c>
-      <c r="Q49" t="inlineStr">
-        <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
-        </is>
-      </c>
-      <c r="R49" t="inlineStr">
-        <is>
-          <t>KH nội bộ VCC T12/2025 quay số trúng thưởng bếp từ đơn AIO, bếp không hoạt động. Yêu cầu Kt qua bảo hành gấp. 
-Quà tặng trúng thưởng nên không có thông tin mã HĐ.</t>
-        </is>
-      </c>
-      <c r="S49" t="inlineStr">
-        <is>
-          <t>08:00 05/01/2026</t>
-        </is>
-      </c>
-      <c r="T49" t="inlineStr">
-        <is>
-          <t>10:25 03/04/2026</t>
-        </is>
-      </c>
-      <c r="U49" t="inlineStr">
-        <is>
-          <t>Đang tiến hành</t>
-        </is>
-      </c>
-      <c r="V49" t="inlineStr">
-        <is>
-          <t>Trong hạn</t>
-        </is>
-      </c>
-      <c r="W49" t="inlineStr">
-        <is>
-          <t>Đinh Thị Ngọc</t>
-        </is>
-      </c>
-      <c r="X49" t="inlineStr">
-        <is>
-          <t>205029</t>
-        </is>
-      </c>
-      <c r="Y49" s="2">
-        <v>46027</v>
-      </c>
-      <c r="Z49">
-        <v>81</v>
-      </c>
-      <c r="AA49" t="inlineStr">
-        <is>
-          <t>AIO</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>P.Triển khai</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Anhnt631</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>KV1</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>QNH</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>DVKT</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>Home Service</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>Dịch vụ khác</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>23092025/HĐTP-SPT-VIETTEL</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>B2B</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>Khách hàng doanh nghiệp</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>CÔNG TY CỔ PHẦN SPT VIỆT NAM</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>0962892720</t>
-        </is>
-      </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>...</t>
-        </is>
-      </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>Hotline</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>Hot</t>
-        </is>
-      </c>
-      <c r="O50" t="inlineStr">
-        <is>
-          <t>Trong bán</t>
-        </is>
-      </c>
-      <c r="P50" t="inlineStr">
-        <is>
-          <t>Khiếu nại</t>
-        </is>
-      </c>
-      <c r="Q50" t="inlineStr">
-        <is>
-          <t>Tiến độ triển khai chậm</t>
-        </is>
-      </c>
-      <c r="R50" t="inlineStr">
         <is>
           <t>- Đối tác Công ty cổ phần SPT Việt Nam (sdt phản ánh 0975014010) tiếp tục gọi tđ phản ánh về vấn đề chậm trễ tiến độ và thiếu nhân lực thi công cho dự án Thi công lắp đặt hệ thống Chiller. 
 - Kh báo hiện tại vẫn chậm tiến độ, cn ko thay đổi hay tiến triển thêm gì
@@ -7475,53 +7182,53 @@
 - Kh yc: Yc TCT có biện pháp xử lý rõ ràng cho kh</t>
         </is>
       </c>
-      <c r="S50" t="inlineStr">
+      <c r="S48" t="inlineStr">
         <is>
           <t>08:00 10/12/2025</t>
         </is>
       </c>
-      <c r="T50" t="inlineStr">
+      <c r="T48" t="inlineStr">
         <is>
           <t>15:00 16/12/2025</t>
         </is>
       </c>
-      <c r="U50" t="inlineStr">
+      <c r="U48" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V50" t="inlineStr">
+      <c r="V48" t="inlineStr">
         <is>
           <t>Trong hạn</t>
         </is>
       </c>
-      <c r="W50" t="inlineStr">
+      <c r="W48" t="inlineStr">
         <is>
           <t>Đặng Việt Phú</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr">
+      <c r="X48" t="inlineStr">
         <is>
           <t>062146</t>
         </is>
       </c>
-      <c r="Y50" s="2">
+      <c r="Y48" s="2">
         <v>46001</v>
       </c>
-      <c r="Z50">
+      <c r="Z48">
         <v>107</v>
       </c>
-      <c r="AA50" t="inlineStr">
+      <c r="AA48" t="inlineStr">
         <is>
           <t>IOC</t>
         </is>
       </c>
-      <c r="AB50" t="inlineStr">
+      <c r="AB48" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
-      <c r="AC50" t="inlineStr">
+      <c r="AC48" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>

--- a/data/3.R_pakh.xlsx
+++ b/data/3.R_pakh.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC51"/>
+  <dimension ref="A1:AC52"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="25" max="25" width="20.7109375" style="2" customWidth="1"/>
@@ -516,7 +516,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>NBH</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -531,12 +531,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Gói hỗ trợ kỹ thuật - Dịch vụ kiểm tra</t>
+          <t>Thay lõi lọc máy lọc nước</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>VCC_HS_HPG_1774424390346</t>
+          <t>VCC_HS_NBH_1774573594561</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -551,22 +551,22 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Nguyen Dung</t>
+          <t>Ngô Anh Tuấn</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0948510404</t>
+          <t>0964982317</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>31 Cao thắng , Hạ lý , Hồng bàng , Hải phòng, Phường An Dương, Thành phố Hải Phòng</t>
+          <t>số nhà 11 tổ 10 phường phủ lý tỉnh ninh bình, Phường Phủ Lý, Tỉnh Ninh Bình</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Facebook</t>
+          <t>Hotline</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -576,7 +576,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Trước bán</t>
+          <t>Trong bán</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -586,22 +586,22 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>Liên hệ chậm</t>
+          <t>Không đúng lịch hẹn</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>KH báo chưa có KT liên hệ, ĐTV check log cuộc gọi ko thấy có.</t>
+          <t>KH báo KT hẹn ngày 28/03 qua hỗ trợ nhưng không đến. Yêu cầu kiểm tra lại thái độ làm việc của nhân viên</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>13:30 30/03/2026</t>
+          <t>08:00 31/03/2026</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>09:00 31/03/2026</t>
+          <t>14:00 31/03/2026</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -616,16 +616,16 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>Đào Văn Sơn</t>
+          <t>Trần Quốc Tài</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>079457</t>
+          <t>073753</t>
         </is>
       </c>
       <c r="Y2" s="2">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -654,7 +654,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>HNI</t>
+          <t>LCU</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -669,12 +669,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bảo dưỡng vệ sinh máy giặt lồng ngang</t>
+          <t>Bảo dưỡng, vệ sinh máy giặt lồng đứng</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>VCC_HS_HNI_1774674328867</t>
+          <t>VCC_HS_LCU_1774682237103</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -682,11 +682,6 @@
           <t>B2C</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Member</t>
-        </is>
-      </c>
       <c r="I3" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
@@ -694,22 +689,22 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Vu Thao</t>
+          <t>Thu Ha</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0945005001</t>
+          <t>0965290825</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>21 lê đức thọ</t>
+          <t>Gần bưu điện San Thàng, phường Tân Phong, Lai Châu, Phường Tân Phong, Tỉnh Lai Châu</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Zalo</t>
+          <t>Hotline</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -719,7 +714,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Sau bán</t>
+          <t>Trong bán</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -729,31 +724,22 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>Khác</t>
+          <t>Liên hệ chậm</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1. KH phản ánh: Ngày 28/3 tôi có sử dụng 1 dịch vụ bảo dưỡng máy giặt Toshiba lồng ngang của viettel, thực sự tôi cảm thấy cực kỳ thất vọng. Việc tháo bảo dưỡng máy giặt tôi đánh giá rất ok, còn việc xử lý tiếng ồn khi máy vắt thì có vấn đề. Bạn kỹ thuật đã xác định được hỏng vòng bi, tôi có hỏi bao nhiêu tiền thì bạn ấy bảo để em gọi về viettel hỏi xem giá bao nhiêu và báo giá tôi là: 850.000 VNĐ. Lúc đó tôi đang làm việc và cũng chưa biết vòng bi nó thế nào, và cũng nghĩ là của Viettel thì k phải nghĩ về giá, tôi báo luôn bạn ấy là ok, thay cho anh. Đến lúc bạn ấy tháo ra và bảo k có sẵn và phải đi ra ngoài mua. Sau khi mua về thì hoá ra nó là cái vòng bi bé tí, rẻ tiền. Giá thị trường có 110.000VNĐ. Tôi vẫn thanh toán đầy đủ. Ngay sau khi tôi thanh toán xong thì thấy 2 tin nhắn của viettel báo là: 
-Tin nhắn 1: dịch vụ bảo dưỡng máy giặt (550.000 VNĐ)
-Tin nhắn 2: nạp gas điều hoà (864.000 VNĐ)
-Tôi chỉ sử dụng mỗi dịch vụ bảo dưỡng máy giặt, tôi không sử dụng dịch vụ Nạp ga điều hòa. Phải chăng là để hợp lý cái hóa đơn vòng bi kia, hay nói đúng hơn là lừa dối khách hàng. Tôi định share thông tin cho bạn bè để tránh gặp tình huống như tôi. Nhưng tôi nghĩ viettel chắc k làm như vậy
-2. KH yêu cầu: cần các bạn xác nhận lại cho tôi 2 vấn đề: 
-1. có phải giá vòng bi của Viettel báo là: 850.000 VNĐ hay không? 
-2. Tin nhắn đơn Nạp Ga của tôi là như thế nào?
-***Ghi chú: KH có 2 đơn hàng
-Nạp ga là DH_B2C_HNI_1774701771288
-BDVS  máy giặt là VCC_HS_HNI_1774674328867</t>
+          <t>Đơn trong ngày nhưng chưa có KT nào liên hệ vs KH. Yêu cầu phản hồi gâp</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>13:30 30/03/2026</t>
+          <t>08:00 31/03/2026</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>13:30 31/03/2026</t>
+          <t>14:00 31/03/2026</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -768,16 +754,16 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>Lê Duy Tuấn</t>
+          <t>Lê Anh Tuấn</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>293859</t>
+          <t>068418</t>
         </is>
       </c>
       <c r="Y3" s="2">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -801,62 +787,62 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>KV1</t>
+          <t>KV3</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>GPTH</t>
+          <t>DVKT</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>CNTT</t>
+          <t>Home Service</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Cáp quang</t>
+          <t>Bảo dưỡng Điều hòa treo tường (9.000BTU ÷ 12.000 BTU)</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>KHDN_TT.VHKT_NAN_0989441</t>
+          <t>VCC_HS_HCM_1774611396681</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>B2B</t>
+          <t>B2C</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Khách hàng doanh nghiệp</t>
+          <t>Khách hàng cá nhân</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MAVIN ANH SƠN</t>
+          <t>Vũ Xuân Thái</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0983985357</t>
+          <t>0903538328</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Khu B - KCN Nam Cấm</t>
+          <t>vinhomes grand park q9 hcm Phường Thủ Đức - Phường Thủ Đức - Hồ Chí Minh</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Hotline</t>
+          <t>Facebook</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -871,27 +857,27 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hỗ trợ</t>
+          <t>Khiếu nại</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>Thủ tục/giấy tờ/ Hóa đơn/ Hồ sơ lắp đặt</t>
+          <t>Khác</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>Hóa đơn của KHDN bị mất nên cần xin lại hóa đơn ở HĐ này.</t>
+          <t>KH đặt đơn dịch vụ 1 điều hòa + 1 bình nóng lạnh nhưng KT nhìn nhầm thành 2 điều hòa. KT qua nhà KH thấy có bình nóng lạnh nên báo với KH là ko vệ sinh được bình nóng lạnh. KH ko đồng ý và yêu cầu giải trình vấn đề này</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>10:00 30/03/2026</t>
+          <t>08:00 31/03/2026</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>10:00 31/03/2026</t>
+          <t>09:00 01/04/2026</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -906,60 +892,65 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>Nguyễn Quốc Hùng</t>
+          <t>Nguyễn Thành Long</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>416898</t>
+          <t>282101</t>
         </is>
       </c>
       <c r="Y4" s="2">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="Z4">
         <v>0</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>AIO</t>
+          <t>HS</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>P.Triển khai</t>
+          <t>VHKT</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Sonln15</t>
+          <t>VHKT</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>KV1</t>
+          <t>KV3</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>HNI</t>
+          <t>CTO</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>GPTH</t>
+          <t>DVKT</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>M&amp;E</t>
+          <t>Home Service</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Nồi áp suất</t>
+          <t>Bảo dưỡng Điều hòa treo tường (9.000BTU ÷ 12.000 BTU)</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>VCC_HS_CTO_1774616933241</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -969,27 +960,27 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Diamond</t>
+          <t>Member</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Khách hàng chuỗi</t>
+          <t>Khách hàng cá nhân</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Nguyễn Thị Thu Thuý</t>
+          <t>Đỗ Viết Tấn</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0968821715</t>
+          <t>0968313821</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>test</t>
+          <t>Ấp Phú Xuân thị trấn mái dầm châu thành hậu Giang, Xã Châu Thành, Thành phố Cần Thơ</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -1004,7 +995,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Trong bán</t>
+          <t>Sau bán</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1014,27 +1005,27 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>Hiệu suất thấp</t>
+          <t>Sau bảo dưỡng thiết bị bị hỏng</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>test</t>
+          <t>KH phản ánh sau khi KT VCC bảo dưỡng vệ sinh điều hòa thì máy không chạy nữa. Yêu cầu cho KT qua kiểm tra lại</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>14:55 30/03/2026</t>
+          <t>08:00 31/03/2026</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>14:55 31/03/2026</t>
+          <t>09:00 01/04/2026</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>Đang tiến hành</t>
+          <t>Chưa thực hiện</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1044,1252 +1035,1816 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>Nguyễn Thị Thu Thúy</t>
+          <t>Nguyễn Minh Tiên</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>433273</t>
+          <t>431446</t>
         </is>
       </c>
       <c r="Y5" s="2">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="Z5">
         <v>0</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>IOC</t>
+          <t>HS</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>P.Triển khai</t>
+          <t>VHKT</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>truongdv17</t>
+          <t>VHKT</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>KV1</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>HNI</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>DVKT</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Home Service</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Gói hỗ trợ kỹ thuật - Dịch vụ kiểm tra</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>VCC_HS_HNI_1774581791644</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>B2C</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Member</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Khách hàng cá nhân</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Chii Huệ</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0389920628</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>514C14 Nguyễn Quý Đức Thanh Xuân</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Trong bán</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Sự cố</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>Sau bảo dưỡng thiết bị bị hỏng</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>KH phản ánh sau khi KT đến bảo dưỡng điều hòa vào ngày 28/03 thì hôm sau điều hòa không mở được, yêu cầu KT đến kiểm tra lại gấp</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>08:00 31/03/2026</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>09:00 01/04/2026</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Chưa thực hiện</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Lê Duy Tuấn</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>293859</t>
+        </is>
+      </c>
+      <c r="Y6" s="2">
+        <v>46112</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>HS</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>KV1</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>BNH</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>GPTH</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NLMT</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Hệ thống NLMT</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>KHCN_TT.GPTH_BNH_1634096</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>B2C</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Khách hàng cá nhân</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Nguyễn Ngọc Ân</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0988386838</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Xã Xuân Cẩm, Tỉnh Bắc Ninh</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Hotline</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Sau bán</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Sự cố</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>1. KH chưa báo cn
+2. KH phản ánh: nhà KH có thêm ats của máy nổ, về nguyên tắc máy điện phải chạy nlmt, khi nlmt hết thì chạy máy nổ. Hiện tại thì khi mất điện ko chạy sang nlmt, và khi nlmt hết rồi vẫn ko thấy chạy máy nổ. 
+3. KH yêu cầu: Kiểm tra trước nội dung về ats của máy nổ và nlmt. Và khắc phục tình trạng ko sử dụng này của KH.</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>15:55 30/03/2026</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>15:55 31/03/2026</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Chưa thực hiện</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>nguyễn văn Tuần</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>461581</t>
+        </is>
+      </c>
+      <c r="Y7" s="2">
+        <v>46111</v>
+      </c>
+      <c r="Z7">
+        <v>1</v>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>AIO</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>KV2</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>KHA</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>GPTH</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NLMT</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Hệ thống NLMT</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>KHCN_TT.GPTH_NTN_1426310</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>B2C</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Khách hàng cá nhân</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Nguyễn Văn Vinh</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0947885479</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>21/8,Phường Phủ Hà,Thành phố Phan Rang - Tháp Chàm,Tỉnh Ninh Thuận</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Hotline</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Sau bán</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Sự cố</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>1 KH đã báo cn: A Hoàng lắp đặt nlmt
+2. KH phản ánh: Lỗi ivt, app báo lỗi trên đt ko chạy điện: lỗi kỹ thuật.
+3. KH phản ánh: Điều KT qua kiểm tra, khắc phục gấp cho KH</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>15:37 30/03/2026</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>15:37 31/03/2026</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Đang tiến hành</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Nguyễn Văn Vương</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>069846</t>
+        </is>
+      </c>
+      <c r="Y8" s="2">
+        <v>46111</v>
+      </c>
+      <c r="Z8">
+        <v>1</v>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>AIO</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>KV1</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>NAN</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>GPTH</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>CNTT</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Cáp quang</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>KHDN_TT.VHKT_NAN_0989441</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>B2B</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Khách hàng doanh nghiệp</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MAVIN ANH SƠN</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0983985357</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Khu B - KCN Nam Cấm</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Hotline</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Sau bán</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Hỗ trợ</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>Thủ tục/giấy tờ/ Hóa đơn/ Hồ sơ lắp đặt</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>Hóa đơn của KHDN bị mất nên cần xin lại hóa đơn ở HĐ này.</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>10:00 30/03/2026</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>10:00 31/03/2026</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Chưa thực hiện</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Sắp quá hạn</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Nguyễn Quốc Hùng</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>416898</t>
+        </is>
+      </c>
+      <c r="Y9" s="2">
+        <v>46111</v>
+      </c>
+      <c r="Z9">
+        <v>1</v>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>AIO</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>P.Triển khai</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Sonln15</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>KV1</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>HNI</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>GPTH</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>M&amp;E</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Nồi áp suất</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>B2C</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Diamond</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Khách hàng chuỗi</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Nguyễn Thị Thu Thuý</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0968821715</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Hotline</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Trong bán</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Sự cố</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>Hiệu suất thấp</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>14:55 30/03/2026</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>14:55 31/03/2026</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Đang tiến hành</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Sắp quá hạn</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Nguyễn Thị Thu Thúy</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>433273</t>
+        </is>
+      </c>
+      <c r="Y10" s="2">
+        <v>46111</v>
+      </c>
+      <c r="Z10">
+        <v>1</v>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>IOC</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>P.Triển khai</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>truongdv17</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>KV3</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>HCM</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_VLG_1679600</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>Nguyễn Tài Năng</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>0916001008</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>A1/38D</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>Trong bán</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>Hỗ trợ</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>Hỗ trợ lắp đặt</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>1. KH đã báo cn
 2. KH phản ánh: Chưa thấy lắp đặt nlmt cho KH, CN chỉ thấy nói chung chung là đợi linh kiện về, ko có ngày hẹn cụ thể cho KH.
 3. KH yêu cầu: Có ngày cụ thể cho KH và triển khai lắp đặt cho KH.</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>11:41 30/03/2026</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>11:41 31/03/2026</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>Chưa thực hiện</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>Trong hạn</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Sắp quá hạn</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
         <is>
           <t>Nguyễn Thành Long</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="X11" t="inlineStr">
         <is>
           <t>282101</t>
         </is>
       </c>
-      <c r="Y6" s="2">
+      <c r="Y11" s="2">
         <v>46111</v>
       </c>
-      <c r="Z6">
-        <v>0</v>
-      </c>
-      <c r="AA6" t="inlineStr">
+      <c r="Z11">
+        <v>1</v>
+      </c>
+      <c r="AA11" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AB11" t="inlineStr">
         <is>
           <t>P.Triển khai</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
+      <c r="AC11" t="inlineStr">
         <is>
           <t>Tuyendv</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>KV1</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>NAN</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>KHCN_PINNLMT_NAN_0334667</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>Lê Trung An</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>0865878212</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>xóm 9, Xã Đại Sơn, Huyện Đô Lương, Tỉnh Nghệ An</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>Hỗ trợ</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>Hướng dẫn, hỗ trợ sử dụng sản phẩm</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>1. KH đã báo cn
 2. KH yêu cầu: Muốn hiện thông số trên app từ ivt qua điện lưới với điện dùng cho GĐ để báo điện lực.</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>11:30 30/03/2026</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>11:30 31/03/2026</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>Chưa thực hiện</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>Trong hạn</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Sắp quá hạn</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
         <is>
           <t>Nguyễn Minh Linh</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>285776</t>
         </is>
       </c>
-      <c r="Y7" s="2">
+      <c r="Y12" s="2">
         <v>46111</v>
       </c>
-      <c r="Z7">
-        <v>0</v>
-      </c>
-      <c r="AA7" t="inlineStr">
+      <c r="Z12">
+        <v>1</v>
+      </c>
+      <c r="AA12" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AB12" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
+      <c r="AC12" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>KV1</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>HNI</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>KHDN_TT.GPTH_HNI_1665498</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>B2B</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>Diamond</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>Khách hàng doanh nghiệp</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>CÔNG TY CỔ PHẦN TUẤN CƯỜNG</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>0914880646</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>Thôn 7</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>Nhân viên nội bộ VCC</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="P13" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="R13" t="inlineStr">
         <is>
           <t>CN 0981168696  báo sự cố hộ KH
 1. KH phản ánh: Lỗi ivt, mất điện lưới hiện tại pin ko xả được
 2. KH yêu cầu: KHDN là xưởng sản xuất cần qua hỗ trợ, kiểm tra, khắc phục gấp cho KH.</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>09:00 30/03/2026</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>09:00 31/03/2026</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>Chưa thực hiện</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>Trong hạn</t>
-        </is>
-      </c>
-      <c r="Y8" s="2">
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Sắp quá hạn</t>
+        </is>
+      </c>
+      <c r="Y13" s="2">
         <v>46111</v>
       </c>
-      <c r="Z8">
-        <v>0</v>
-      </c>
-      <c r="AA8" t="inlineStr">
+      <c r="Z13">
+        <v>1</v>
+      </c>
+      <c r="AA13" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AB13" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
+      <c r="AC13" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>KV1</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>BNH</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>KHDN_TT.GPTH_NAN_1650078</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>B2B</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>KHCN_TT.GPTH_BGG_1601525</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>B2C</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
         <is>
           <t>Diamond</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>CÔNG TY CỔ PHẦN TƯ VẤN THIẾT KẾ VÀ XÂY DỰNG LỘC PHÁT</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>0982229238</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>Nhà số 9, ngõ 30, đường Trần Tấn, Phường Vinh Lộc, Tỉnh Nghệ An</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Hoàng Văn Hoạt</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0344334808</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Thán</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="O14" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="P14" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>1. KH chưa báo cn
-2. KH phản ánh: Nhảy áp ở chỗ cục pin nlmt
-3. KH yêu cầu: Qua hỗ trợ, kiểm tra nguyên nhân và khắc phục dứt điểm cho KH.</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>08:00 30/03/2026</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>09:00 31/03/2026</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>Chưa thực hiện</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>Trong hạn</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>Nguyễn Văn Tân</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>460719</t>
-        </is>
-      </c>
-      <c r="Y9" s="2">
-        <v>46111</v>
-      </c>
-      <c r="Z9">
-        <v>0</v>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>AIO</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>KV1</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>BNH</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>GPTH</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>NLMT</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Hệ thống NLMT</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>KHCN_TT.GPTH_BGG_1601525</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>B2C</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Diamond</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>Khách hàng cá nhân</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>Hoàng Văn Hoạt</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>0344334808</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>Thán</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>Hotline</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>Bình thường</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>Sau bán</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>Sự cố</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
+      <c r="Q14" t="inlineStr">
         <is>
           <t>Chất lượng, hiệu suất của sản phẩm/hệ thống thấp</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="R14" t="inlineStr">
         <is>
           <t>1. KH đã báo kỹ thuật Thành 0977357868 nhưng chưa được hỗ trợ
 2. KH phản ánh lắp điện NLMT nhưng tiền điện vẫn cao
 3. KH yêu cầu kỹ thuật qua hỗ trợ xử lý</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>08:00 30/03/2026</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>09:00 31/03/2026</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>Chưa thực hiện</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>Trong hạn</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Sắp quá hạn</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
         <is>
           <t>Nguyễn Thị Nhị</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="X14" t="inlineStr">
         <is>
           <t>239095</t>
         </is>
       </c>
-      <c r="Y10" s="2">
+      <c r="Y14" s="2">
         <v>46111</v>
       </c>
-      <c r="Z10">
-        <v>0</v>
-      </c>
-      <c r="AA10" t="inlineStr">
+      <c r="Z14">
+        <v>1</v>
+      </c>
+      <c r="AA14" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AB14" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
+      <c r="AC14" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="15">
+      <c r="A15" t="inlineStr">
         <is>
           <t>KV1</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>HPG</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>YCKS_HDG_TLS/0120467</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>Diamond</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>Ngô Hữu Thế</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>0984379375</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>494 Phố Việt Hòa, Tp Hải Phòng</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="O15" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="P15" t="inlineStr">
         <is>
           <t>Hỗ trợ</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="Q15" t="inlineStr">
         <is>
           <t>Thủ tục/giấy tờ/ Hóa đơn/ Hồ sơ lắp đặt</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="R15" t="inlineStr">
         <is>
           <t>1. KH chưa báo chi nhánh
 2. KH phản ánh sơ đồ đấu nối điện bị sai
 3. KH yêu cầu chi nhánh gửi lại 1 bản hợp đồng sơ đồ đấu nối để KH kiểm tra</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>08:00 30/03/2026</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>09:00 31/03/2026</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>Chưa thực hiện</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>Trong hạn</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Sắp quá hạn</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
         <is>
           <t>Phạm Quân Khu</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="X15" t="inlineStr">
         <is>
           <t>272645</t>
         </is>
       </c>
-      <c r="Y11" s="2">
+      <c r="Y15" s="2">
         <v>46111</v>
       </c>
-      <c r="Z11">
-        <v>0</v>
-      </c>
-      <c r="AA11" t="inlineStr">
+      <c r="Z15">
+        <v>1</v>
+      </c>
+      <c r="AA15" t="inlineStr">
         <is>
           <t>IOC</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AB15" t="inlineStr">
         <is>
           <t>P.Triển khai</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
+      <c r="AC15" t="inlineStr">
         <is>
           <t>vinhvv4</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>KV1</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>NAN</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_NAN_1574225</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>Diamond</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>Nguyên Văn Tú</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>0868081789</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>1,Xã Yên Sơn,Huyện Đô Lương,Tỉnh Nghệ An</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="O16" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="P16" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="Q16" t="inlineStr">
         <is>
           <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="R16" t="inlineStr">
         <is>
           <t>1. KH đã báo giám đốc chi nhánh nhưng chưa được xử lý dứt điểm
 2. KH phản ánh NLMT bị hỏng không sử dụng được
 3. KH yêu cầu kỹ thuật qua hỗ trợ thay aptomat to hơn</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>08:00 30/03/2026</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>09:00 31/03/2026</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>Chưa thực hiện</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>Trong hạn</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Sắp quá hạn</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
         <is>
           <t>Nguyễn Minh Linh</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
+      <c r="X16" t="inlineStr">
         <is>
           <t>285776</t>
         </is>
       </c>
-      <c r="Y12" s="2">
+      <c r="Y16" s="2">
         <v>46111</v>
       </c>
-      <c r="Z12">
-        <v>0</v>
-      </c>
-      <c r="AA12" t="inlineStr">
+      <c r="Z16">
+        <v>1</v>
+      </c>
+      <c r="AA16" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
+      <c r="AB16" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
+      <c r="AC16" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>KV1</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>TNN</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>Bàng Lâm Sung</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>0968525115</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="L17" t="inlineStr">
         <is>
           <t>tổ 53</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="O17" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="P17" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="Q17" t="inlineStr">
         <is>
           <t>Tấm pin bị rò rỉ/ Lỗi</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="R17" t="inlineStr">
         <is>
           <t>1. KH đã LH kỹ thuật nhưng không nghe máy
 2. KH phản ánh NLMT lỗi BMS không nhận pin
 3. KH yêu cầu kỹ thuật liên hệ hỗ trợ</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>08:00 30/03/2026</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="T17" t="inlineStr">
         <is>
           <t>09:00 31/03/2026</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>Chưa thực hiện</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>Trong hạn</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Đang tiến hành</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Sắp quá hạn</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
         <is>
           <t>Trần Xuân Kương</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
+      <c r="X17" t="inlineStr">
         <is>
           <t>289759</t>
         </is>
       </c>
-      <c r="Y13" s="2">
+      <c r="Y17" s="2">
         <v>46111</v>
       </c>
-      <c r="Z13">
-        <v>0</v>
-      </c>
-      <c r="AA13" t="inlineStr">
+      <c r="Z17">
+        <v>1</v>
+      </c>
+      <c r="AA17" t="inlineStr">
         <is>
           <t>IOC</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
+      <c r="AB17" t="inlineStr">
         <is>
           <t>P.Triển khai</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
+      <c r="AC17" t="inlineStr">
         <is>
           <t>tietvt16</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>KV1</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>HNI</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_HNI_1631868</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>Diamond</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>Nguyễn Thị Thu Hà</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>0989790925</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t>đông xuân, xã sóc sơn</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t>Nhân viên nội bộ VCC</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
+      <c r="O18" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
+      <c r="P18" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr">
+      <c r="Q18" t="inlineStr">
         <is>
           <t>Inverter không hoạt động</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="R18" t="inlineStr">
         <is>
           <t>CN báo hộ: Nguyễn Văn Lâm
 464695
@@ -2298,429 +2853,429 @@
 3. KH yc KT qua kiểm tra gấp cho KH</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>08:00 30/03/2026</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="T18" t="inlineStr">
         <is>
           <t>09:00 31/03/2026</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="U18" t="inlineStr">
         <is>
           <t>Chưa thực hiện</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>Trong hạn</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>Nguyễn Văn Vinh</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>469835</t>
-        </is>
-      </c>
-      <c r="Y14" s="2">
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Sắp quá hạn</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Lê Duy Tuấn</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>293859</t>
+        </is>
+      </c>
+      <c r="Y18" s="2">
         <v>46111</v>
       </c>
-      <c r="Z14">
-        <v>0</v>
-      </c>
-      <c r="AA14" t="inlineStr">
+      <c r="Z18">
+        <v>1</v>
+      </c>
+      <c r="AA18" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
+      <c r="AB18" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
+      <c r="AC18" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>KV1</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>HNI</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_HNI_1641827</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>Diamond</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>Nguyễn Trọng Đạt</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>0904113488</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="L19" t="inlineStr">
         <is>
           <t>36 Ngõ 104 Thúy Lĩnh, Phường Hoàng Mai, Thành phố Hà Nội</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="N19" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr">
+      <c r="O19" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr">
+      <c r="P19" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr">
+      <c r="Q19" t="inlineStr">
         <is>
           <t>Sản phẩm không sử dụng được / không hoạt động</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="R19" t="inlineStr">
         <is>
           <t>KH chưa báo CN
  KH đang sd NLMT, nhưng hiện tại hệ thống ko hoạt động, ko phát được điện
 YC KT qua kiểm tra và xử lý</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t>08:00 30/03/2026</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="T19" t="inlineStr">
         <is>
           <t>23:55 05/04/2026</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr">
+      <c r="V19" t="inlineStr">
         <is>
           <t>Trong hạn</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>Nguyễn Hoàng Minh</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
+      <c r="X19" t="inlineStr">
         <is>
           <t>292404</t>
         </is>
       </c>
-      <c r="Y15" s="2">
+      <c r="Y19" s="2">
         <v>46111</v>
       </c>
-      <c r="Z15">
-        <v>0</v>
-      </c>
-      <c r="AA15" t="inlineStr">
+      <c r="Z19">
+        <v>1</v>
+      </c>
+      <c r="AA19" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
+      <c r="AB19" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
+      <c r="AC19" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+    <row r="20">
+      <c r="A20" t="inlineStr">
         <is>
           <t>KV3</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>CTO</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>KHDN_TT.GPTH_CTO_1417803</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>B2B</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>Khách hàng doanh nghiệp</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>công ty TNHH quảng cáo đăng nguyễn</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t>0909393390</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="L20" t="inlineStr">
         <is>
           <t>ô môn</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
+      <c r="N20" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr">
+      <c r="O20" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr">
+      <c r="P20" t="inlineStr">
         <is>
           <t>Hỗ trợ</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr">
+      <c r="Q20" t="inlineStr">
         <is>
           <t>Hỗ trợ lắp đặt</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="R20" t="inlineStr">
         <is>
           <t>KH chưa báo CN
 HIện tại KH cần di dời thiết bị cách đấy khoảng 2-3m , nhờ KT qua hỗ trợ</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="S20" t="inlineStr">
         <is>
           <t>08:00 30/03/2026</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
+      <c r="T20" t="inlineStr">
         <is>
           <t>09:00 31/03/2026</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="U20" t="inlineStr">
         <is>
           <t>Chưa thực hiện</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>Trong hạn</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Sắp quá hạn</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
         <is>
           <t>Võ Chí Trung</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
+      <c r="X20" t="inlineStr">
         <is>
           <t>469593</t>
         </is>
       </c>
-      <c r="Y16" s="2">
+      <c r="Y20" s="2">
         <v>46111</v>
       </c>
-      <c r="Z16">
-        <v>0</v>
-      </c>
-      <c r="AA16" t="inlineStr">
+      <c r="Z20">
+        <v>1</v>
+      </c>
+      <c r="AA20" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
+      <c r="AB20" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
+      <c r="AC20" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
+    <row r="21">
+      <c r="A21" t="inlineStr">
         <is>
           <t>KV2</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>HUE</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>Tấm pin NLMT</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>KHDN_TT.GPTH_TTH_1626383</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>B2B</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>Diamond</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>Khách hàng doanh nghiệp</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>CÔNG TY TNHH SẢN XUẤT THƯƠNG MẠI VIỆT PHÚ HƯNG</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t>0985005322</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="L21" t="inlineStr">
         <is>
           <t>19 Trưng Nữ Vương</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
+      <c r="N21" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr">
+      <c r="O21" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr">
+      <c r="P21" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr">
+      <c r="Q21" t="inlineStr">
         <is>
           <t>Hiệu suất sản phẩm kém</t>
         </is>
       </c>
-      <c r="R17" t="inlineStr">
+      <c r="R21" t="inlineStr">
         <is>
           <t>KH chưa báo CN
 KH đang sử dụng tấm PIN NLMT của VCC, 
@@ -2728,753 +3283,186 @@
 KH YC KT qua kiểm tra và xử lý cho KH gấp</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>08:00 30/03/2026</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
+      <c r="T21" t="inlineStr">
         <is>
           <t>09:00 31/03/2026</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="U21" t="inlineStr">
         <is>
           <t>Chưa thực hiện</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>Trong hạn</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Sắp quá hạn</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
         <is>
           <t>Lê Văn Đồng</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
+      <c r="X21" t="inlineStr">
         <is>
           <t>422252</t>
         </is>
       </c>
-      <c r="Y17" s="2">
+      <c r="Y21" s="2">
         <v>46111</v>
       </c>
-      <c r="Z17">
-        <v>0</v>
-      </c>
-      <c r="AA17" t="inlineStr">
+      <c r="Z21">
+        <v>1</v>
+      </c>
+      <c r="AA21" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
+      <c r="AB21" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
+      <c r="AC21" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>KV1</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>HNI</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>KV3</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>HCM</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>KHCN_TT.GPTH_HNI_1631868</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>B2C</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>KHDN_TT.GPTH_BDG_1495422</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>B2B</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
         <is>
           <t>Diamond</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>Khách hàng cá nhân</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>Lê Văn Vĩnh</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>0948519572</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>SN 7A ngõ 564/12 đường Nguyễn Văn Cừ</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>Nhân viên nội bộ VCC</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>Hot</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Khách hàng doanh nghiệp</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VẬN TẢI BẢO LONG PHÁT</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>0918236379</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Số 617, đường ĐT 743B, khu phố Đông Tân</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>Zalo</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>Sự cố</t>
-        </is>
-      </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>Sản phẩm không sử dụng được / không hoạt động</t>
-        </is>
-      </c>
-      <c r="R18" t="inlineStr">
-        <is>
-          <t>CN báo hộ SDT: 985792828
-KH đang sd NLMT nhưng hiện tại thiết bị ko sản sinh ra điện
-YC KT qua kiểm tra và xử lý cho KH</t>
-        </is>
-      </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>08:00 30/03/2026</t>
-        </is>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>09:00 31/03/2026</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>Đang tiến hành</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>Trong hạn</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>Trần Huy Quý</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>437012</t>
-        </is>
-      </c>
-      <c r="Y18" s="2">
-        <v>46111</v>
-      </c>
-      <c r="Z18">
-        <v>0</v>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>AIO</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>KV3</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>HCM</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>GPTH</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>NLMT</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Hệ thống NLMT</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>KHDN_TT.GPTH_BDG_1495422</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>B2B</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Diamond</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>Khách hàng doanh nghiệp</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI VẬN TẢI BẢO LONG PHÁT</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>0918236379</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>Số 617, đường ĐT 743B, khu phố Đông Tân</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>Zalo</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>Bình thường</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>Sau bán</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
+      <c r="P22" t="inlineStr">
         <is>
           <t>Hỗ trợ</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr">
+      <c r="Q22" t="inlineStr">
         <is>
           <t>Cài đặt hệ thống (APP/Mật khẩu)</t>
         </is>
       </c>
-      <c r="R19" t="inlineStr">
+      <c r="R22" t="inlineStr">
         <is>
           <t>1. KH báo cn người hỗ trợ trước nhưng ko liên hệ được
 2. KH phản ánh: KH kết nối được app báo lỗi ngoại tuyến
 3. KH yêu cầu: Hỗ trợ, hướng dẫn KH sử dụng, KH hay bị gặp vấn đề này nhiều hỗ trợ KH dứt điểm giúp.</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="S22" t="inlineStr">
         <is>
           <t>16:08 26/03/2026</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
+      <c r="T22" t="inlineStr">
         <is>
           <t>09:00 05/04/2026</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="U22" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
+      <c r="V22" t="inlineStr">
         <is>
           <t>Trong hạn</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>Trần Văn Thắng</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
+      <c r="X22" t="inlineStr">
         <is>
           <t>470289</t>
-        </is>
-      </c>
-      <c r="Y19" s="2">
-        <v>46107</v>
-      </c>
-      <c r="Z19">
-        <v>4</v>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>AIO</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>KV2</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>DNG</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>GPTH</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>CNTT</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Camera</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>KHCN_TT.GPTH_DNG_1240036</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>B2C</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>Khách hàng cá nhân</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>Nguyễn Văn Thiên</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>0935302100</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>48 nguyễn đình chiểu, Phường Khuê Mỹ, Quận Ngũ Hành Sơn, Thành phố Đà Nẵng</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>Hotline</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>Bình thường</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>Sau bán</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>Hỗ trợ</t>
-        </is>
-      </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>Cài đặt hệ thống (APP/Mật khẩu)</t>
-        </is>
-      </c>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>1. KH phản ánh: Camera bị rớt không kết nối được, và cả mật khẩu wifi
-2. KH yêu cầu: Hỗ trợ KH cài đặt lại camera.</t>
-        </is>
-      </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>10:11 27/03/2026</t>
-        </is>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>16:50 31/03/2026</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>Đang tiến hành</t>
-        </is>
-      </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>Sắp quá hạn</t>
-        </is>
-      </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>Phan Văn Tuấn</t>
-        </is>
-      </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>271620</t>
-        </is>
-      </c>
-      <c r="Y20" s="2">
-        <v>46108</v>
-      </c>
-      <c r="Z20">
-        <v>3</v>
-      </c>
-      <c r="AA20" t="inlineStr">
-        <is>
-          <t>AIO</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>P.Triển khai</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Sonln15</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>KV2</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>GLI</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>GPTH</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>NLMT</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Hệ thống NLMT</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>KHCN_TT.GPTH_GLI_1676729</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>B2C</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Member</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>Khách hàng cá nhân</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>Rơ Ô WÊ</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>0396081566</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>Thôn Ia Prông</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>Hotline</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>Hot</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>Trong bán</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>Khiếu nại</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>Tiến độ triển khai chậm</t>
-        </is>
-      </c>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>KH phản ánh đã đặt cọc lắp đặt hệ thống điện năng lượng mặt trời 20 ngày rồi nhưng chưa co KT nào qua lắp cho KH. Yêu cầu xử lý gấp</t>
-        </is>
-      </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>10:43 26/03/2026</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>08:35 31/03/2026</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>Đang tiến hành</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>Sắp quá hạn</t>
-        </is>
-      </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>Nguyễn Hà Nguyên</t>
-        </is>
-      </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>060709</t>
-        </is>
-      </c>
-      <c r="Y21" s="2">
-        <v>46107</v>
-      </c>
-      <c r="Z21">
-        <v>4</v>
-      </c>
-      <c r="AA21" t="inlineStr">
-        <is>
-          <t>AIO</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>P.Triển khai</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Sonln15</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>KV2</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>KHA</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>GPTH</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>NLMT</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Hệ thống NLMT</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>KHCN_NLMT_NTN_0241352</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>B2C</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>Khách hàng cá nhân</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>Nguyễn Văn Sanh</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>0913785605</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>KP2, Thị trấn Phước Dân, Huyện Ninh Phước, Tỉnh Ninh Thuận</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>Hotline</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>Bình thường</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>Sau bán</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>Sự cố</t>
-        </is>
-      </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
-        </is>
-      </c>
-      <c r="R22" t="inlineStr">
-        <is>
-          <t>1. KH đã báo cn
-2. KH phản ánh: Ivt bị lỗi ko hoạt động, KH ktra thấy còn ko chạy
-3. KH yêu cầu: Qua hỗ trợ, kiểm tra, khắc phục tình trạng này cho KH</t>
-        </is>
-      </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>08:25 26/03/2026</t>
-        </is>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>16:50 30/03/2026</t>
-        </is>
-      </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>Đang tiến hành</t>
-        </is>
-      </c>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>Sắp quá hạn</t>
-        </is>
-      </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>Nguyễn Văn Vương</t>
-        </is>
-      </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>069846</t>
         </is>
       </c>
       <c r="Y22" s="2">
         <v>46107</v>
       </c>
       <c r="Z22">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
@@ -3495,520 +3483,802 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>KV2</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>DNG</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>GPTH</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>CNTT</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Camera</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>KHCN_TT.GPTH_DNG_1240036</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>B2C</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Khách hàng cá nhân</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Nguyễn Văn Thiên</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>0935302100</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>48 nguyễn đình chiểu, Phường Khuê Mỹ, Quận Ngũ Hành Sơn, Thành phố Đà Nẵng</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>Hotline</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>Sau bán</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Hỗ trợ</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>Cài đặt hệ thống (APP/Mật khẩu)</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>1. KH phản ánh: Camera bị rớt không kết nối được, và cả mật khẩu wifi
+2. KH yêu cầu: Hỗ trợ KH cài đặt lại camera.</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>10:11 27/03/2026</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>16:50 31/03/2026</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Đang tiến hành</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Sắp quá hạn</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Phan Văn Tuấn</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>271620</t>
+        </is>
+      </c>
+      <c r="Y23" s="2">
+        <v>46108</v>
+      </c>
+      <c r="Z23">
+        <v>4</v>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>AIO</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>P.Triển khai</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Sonln15</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>KV2</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>GLI</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>GPTH</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NLMT</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Hệ thống NLMT</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>KHCN_TT.GPTH_GLI_1676729</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>B2C</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Member</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Khách hàng cá nhân</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Rơ Ô WÊ</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>0396081566</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Thôn Ia Prông</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>Hotline</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>Trong bán</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Khiếu nại</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>Tiến độ triển khai chậm</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>KH phản ánh đã đặt cọc lắp đặt hệ thống điện năng lượng mặt trời 20 ngày rồi nhưng chưa co KT nào qua lắp cho KH. Yêu cầu xử lý gấp</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>10:43 26/03/2026</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>08:35 31/03/2026</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Đang tiến hành</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Sắp quá hạn</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Nguyễn Hà Nguyên</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>060709</t>
+        </is>
+      </c>
+      <c r="Y24" s="2">
+        <v>46107</v>
+      </c>
+      <c r="Z24">
+        <v>5</v>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>AIO</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>P.Triển khai</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Sonln15</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>KV1</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>HYN</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_HDG_1304417</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>Diamond</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>Nguyễn Thị Hồng Khánh</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t>0377883716</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="L25" t="inlineStr">
         <is>
           <t>Thôn Ngọc Loan,Xã Tân Quang,Huyện Văn Lâm,Tỉnh Hưng Yên</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr">
+      <c r="N25" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr">
+      <c r="O25" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P23" t="inlineStr">
+      <c r="P25" t="inlineStr">
         <is>
           <t>Hỗ trợ</t>
         </is>
       </c>
-      <c r="Q23" t="inlineStr">
+      <c r="Q25" t="inlineStr">
         <is>
           <t>Hướng dẫn, hỗ trợ sử dụng sản phẩm</t>
         </is>
       </c>
-      <c r="R23" t="inlineStr">
+      <c r="R25" t="inlineStr">
         <is>
           <t>KH chưa báo CN
 KH yêu cầu NVKT qua lại thiết bị inverter của KH 
 Số liên hệ:</t>
         </is>
       </c>
-      <c r="S23" t="inlineStr">
+      <c r="S25" t="inlineStr">
         <is>
           <t>08:00 26/03/2026</t>
         </is>
       </c>
-      <c r="T23" t="inlineStr">
+      <c r="T25" t="inlineStr">
         <is>
           <t>17:25 02/04/2026</t>
         </is>
       </c>
-      <c r="U23" t="inlineStr">
+      <c r="U25" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V23" t="inlineStr">
+      <c r="V25" t="inlineStr">
         <is>
           <t>Trong hạn</t>
         </is>
       </c>
-      <c r="W23" t="inlineStr">
+      <c r="W25" t="inlineStr">
         <is>
           <t>Hoàng Văn Phong</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
+      <c r="X25" t="inlineStr">
         <is>
           <t>291011</t>
         </is>
       </c>
-      <c r="Y23" s="2">
+      <c r="Y25" s="2">
         <v>46107</v>
       </c>
-      <c r="Z23">
-        <v>4</v>
-      </c>
-      <c r="AA23" t="inlineStr">
+      <c r="Z25">
+        <v>5</v>
+      </c>
+      <c r="AA25" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
+      <c r="AB25" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
+      <c r="AC25" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
+    <row r="26">
+      <c r="A26" t="inlineStr">
         <is>
           <t>KV3</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>HCM</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_HCM_1169983</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t>Đường Quyền Hồng</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
+      <c r="K26" t="inlineStr">
         <is>
           <t>0907395121</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="L26" t="inlineStr">
         <is>
           <t>Ấp 4, Xã Phước Kiển, Huyện Nhà Bè, Thành phố Hồ Chí Minh</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr">
+      <c r="N26" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr">
+      <c r="O26" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P24" t="inlineStr">
+      <c r="P26" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q24" t="inlineStr">
+      <c r="Q26" t="inlineStr">
         <is>
           <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
-      <c r="R24" t="inlineStr">
+      <c r="R26" t="inlineStr">
         <is>
           <t>1. KH chưa báo CN
 2. KH phản ánh: Lỗi CP bị cúp điện dưới nhà, hiện tại điện ko sử dụng được.
 3. KH yêu cầu: Qua kiểm tra, hỗ trợ, khắc phục gấp cho KH giờ nhà KH đang ko có điện để sử dụng.</t>
         </is>
       </c>
-      <c r="S24" t="inlineStr">
+      <c r="S26" t="inlineStr">
         <is>
           <t>09:32 26/03/2026</t>
         </is>
       </c>
-      <c r="T24" t="inlineStr">
+      <c r="T26" t="inlineStr">
         <is>
           <t>16:05 31/03/2026</t>
         </is>
       </c>
-      <c r="U24" t="inlineStr">
+      <c r="U26" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V24" t="inlineStr">
+      <c r="V26" t="inlineStr">
         <is>
           <t>Sắp quá hạn</t>
         </is>
       </c>
-      <c r="W24" t="inlineStr">
+      <c r="W26" t="inlineStr">
         <is>
           <t>Điểu Ngọc Lâm</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr">
+      <c r="X26" t="inlineStr">
         <is>
           <t>432612</t>
         </is>
       </c>
-      <c r="Y24" s="2">
+      <c r="Y26" s="2">
         <v>46107</v>
       </c>
-      <c r="Z24">
-        <v>4</v>
-      </c>
-      <c r="AA24" t="inlineStr">
+      <c r="Z26">
+        <v>5</v>
+      </c>
+      <c r="AA26" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
+      <c r="AB26" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
+      <c r="AC26" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+    <row r="27">
+      <c r="A27" t="inlineStr">
         <is>
           <t>KV2</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>KHA</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_KHA_1631515</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t>Diamond</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="J27" t="inlineStr">
         <is>
           <t>Phạm Hải Triều</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
+      <c r="K27" t="inlineStr">
         <is>
           <t>0903576559</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="L27" t="inlineStr">
         <is>
           <t>Phường Nha Trang, Tỉnh Khánh Hòa</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t>Nhân viên nội bộ VCC</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr">
+      <c r="N27" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr">
+      <c r="O27" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P25" t="inlineStr">
+      <c r="P27" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q25" t="inlineStr">
+      <c r="Q27" t="inlineStr">
         <is>
           <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
-      <c r="R25" t="inlineStr">
+      <c r="R27" t="inlineStr">
         <is>
           <t>CN báo sự cố hộ KH
 1. KH phản ánh: Ắc quy, pin gần như ko hoạt động. Chỉ có bám tải, ivt hoạt động
 2. KH yêu cầu: Qua hỗ trợ, kiểm tra, xử lý sớm cho KH.</t>
         </is>
       </c>
-      <c r="S25" t="inlineStr">
+      <c r="S27" t="inlineStr">
         <is>
           <t>08:00 26/03/2026</t>
         </is>
       </c>
-      <c r="T25" t="inlineStr">
+      <c r="T27" t="inlineStr">
         <is>
           <t>17:35 27/03/2026</t>
         </is>
       </c>
-      <c r="U25" t="inlineStr">
+      <c r="U27" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V25" t="inlineStr">
+      <c r="V27" t="inlineStr">
         <is>
           <t>Quá hạn</t>
         </is>
       </c>
-      <c r="W25" t="inlineStr">
+      <c r="W27" t="inlineStr">
         <is>
           <t>Phan Trọng Nghĩa</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr">
+      <c r="X27" t="inlineStr">
         <is>
           <t>234935</t>
         </is>
       </c>
-      <c r="Y25" s="2">
+      <c r="Y27" s="2">
         <v>46107</v>
       </c>
-      <c r="Z25">
-        <v>4</v>
-      </c>
-      <c r="AA25" t="inlineStr">
+      <c r="Z27">
+        <v>5</v>
+      </c>
+      <c r="AA27" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr">
+      <c r="AB27" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
+      <c r="AC27" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
+    <row r="28">
+      <c r="A28" t="inlineStr">
         <is>
           <t>KV1</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>HNI</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>KHDN_TT.GPTH_HNI_1646163</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>B2B</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="H28" t="inlineStr">
         <is>
           <t>Diamond</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t>Khách hàng doanh nghiệp</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
+      <c r="J28" t="inlineStr">
         <is>
           <t>Công Ty Tnhh Đầu Tư Xây Dựng Và Thương Mại Triệu Phúc</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
+      <c r="K28" t="inlineStr">
         <is>
           <t>0973721368</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="L28" t="inlineStr">
         <is>
           <t>Triệu Xuyên, Long xuyên</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr">
+      <c r="M28" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr">
+      <c r="N28" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr">
+      <c r="O28" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P26" t="inlineStr">
+      <c r="P28" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q26" t="inlineStr">
+      <c r="Q28" t="inlineStr">
         <is>
           <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
-      <c r="R26" t="inlineStr">
+      <c r="R28" t="inlineStr">
         <is>
           <t>1. KH đã báo cn a Long gđ kỹ thuật, a Dương Đăng Minh chủ ký HĐ, a Vương lắp đặt.
 2. KH phản ánh: Bị nhảy áp liên tục 1 tháng phải nhảy 20 ngày rơi vào khoảng 2h đêm và 12h trưa ban ngày, và chập tối lúc GĐ đang vào sinh hoạt. CN nhiều lần xuống ktra và kiến nghị nhưng có câu trả lời KH ko được hài lòng lắm. Đặc biệt là a Long GĐ KT có thái độ là đổ cho GĐ tắt áp, KH bức xúc vì KH bỏ đồng tiền ra mà lại đổ lỗi cho nhà KH. KH cũng báo với a Dương Đăng Minh, a Minh cũng bảo là để cháu bảo ae xuống thế nọ thế kia khất để ra giêng để sửa mà giờ hết tháng rồi vẫn ko thấy đâu.
@@ -4016,290 +4286,290 @@
 ***SĐT liên hệ: 0945268772, chú Bồng</t>
         </is>
       </c>
-      <c r="S26" t="inlineStr">
+      <c r="S28" t="inlineStr">
         <is>
           <t>14:58 25/03/2026</t>
         </is>
       </c>
-      <c r="T26" t="inlineStr">
+      <c r="T28" t="inlineStr">
         <is>
           <t>23:00 06/04/2026</t>
         </is>
       </c>
-      <c r="U26" t="inlineStr">
+      <c r="U28" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V26" t="inlineStr">
+      <c r="V28" t="inlineStr">
         <is>
           <t>Trong hạn</t>
         </is>
       </c>
-      <c r="W26" t="inlineStr">
+      <c r="W28" t="inlineStr">
         <is>
           <t>Lê Duy Tuấn</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr">
+      <c r="X28" t="inlineStr">
         <is>
           <t>293859</t>
         </is>
       </c>
-      <c r="Y26" s="2">
+      <c r="Y28" s="2">
         <v>46106</v>
       </c>
-      <c r="Z26">
-        <v>5</v>
-      </c>
-      <c r="AA26" t="inlineStr">
+      <c r="Z28">
+        <v>6</v>
+      </c>
+      <c r="AA28" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr">
+      <c r="AB28" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
+      <c r="AC28" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
+    <row r="29">
+      <c r="A29" t="inlineStr">
         <is>
           <t>KV1</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>BNH</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_BNH_1600729</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
+      <c r="J29" t="inlineStr">
         <is>
           <t>Nguyễn Khương</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
+      <c r="K29" t="inlineStr">
         <is>
           <t>0977113014</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
+      <c r="L29" t="inlineStr">
         <is>
           <t>Xã Tân Chi, Tỉnh Bắc Ninh</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr">
+      <c r="M29" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr">
+      <c r="N29" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O27" t="inlineStr">
+      <c r="O29" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P27" t="inlineStr">
+      <c r="P29" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q27" t="inlineStr">
+      <c r="Q29" t="inlineStr">
         <is>
           <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
-      <c r="R27" t="inlineStr">
+      <c r="R29" t="inlineStr">
         <is>
           <t>1. KH đã báo cn nhưng bạn nv kinh doanh a Vượng chuyển công tác nên chuyển cho a Phong, a Phong lại chuyển công tác cho số người mới nhưng chưa thấy.
 2. KH phản ánh: Biểu đồ biến tần tăng giảm đột biến, sụt pin về 0,pv về 0, tất cả đều về 0, thi thoảng còn bị mất điện. Hôm vừa rồi đầu xuân vào app báo thấy mất kết nối điện lưới trong khi nhà xung quanh vẫn có, sau khi xem tbao ở trên app lại ko có bất kỳ tbao nào về biến tần bị ngắt hay gì cả. KH Kbt có ai can thiệp vào app không
 3. KH yêu cầu: Kiểm tra biến tần cho KH, đã yêu cầu hãng xử lý rất nhiều lần rồi, nhưng giờ vẫn có tình trạng gặp lỗi. Ngoài ra KH yêu cầu là xử lý triệt để cho KH vì sắp tới mùa hè nó lên 3,4kw bị nhảy mà giờ còn kh thấy có tbao trên app.</t>
         </is>
       </c>
-      <c r="S27" t="inlineStr">
+      <c r="S29" t="inlineStr">
         <is>
           <t>09:20 25/03/2026</t>
         </is>
       </c>
-      <c r="T27" t="inlineStr">
+      <c r="T29" t="inlineStr">
         <is>
           <t>18:30 30/03/2026</t>
         </is>
       </c>
-      <c r="U27" t="inlineStr">
+      <c r="U29" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V27" t="inlineStr">
-        <is>
-          <t>Sắp quá hạn</t>
-        </is>
-      </c>
-      <c r="W27" t="inlineStr">
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Quá hạn</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
         <is>
           <t>nguyễn văn Tuần</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr">
+      <c r="X29" t="inlineStr">
         <is>
           <t>461581</t>
         </is>
       </c>
-      <c r="Y27" s="2">
+      <c r="Y29" s="2">
         <v>46106</v>
       </c>
-      <c r="Z27">
-        <v>5</v>
-      </c>
-      <c r="AA27" t="inlineStr">
+      <c r="Z29">
+        <v>6</v>
+      </c>
+      <c r="AA29" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
+      <c r="AB29" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
+      <c r="AC29" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
+    <row r="30">
+      <c r="A30" t="inlineStr">
         <is>
           <t>KV1</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>PTO</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_VPC_1503902</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t>Diamond</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
+      <c r="J30" t="inlineStr">
         <is>
           <t>Nguyễn Việt Hùng</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
+      <c r="K30" t="inlineStr">
         <is>
           <t>0966547344</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
+      <c r="L30" t="inlineStr">
         <is>
           <t>Tự lập Mê Linh,Phường Hùng Vương,Thành phố Phúc Yên,Tỉnh Vĩnh Phúc</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr">
+      <c r="M30" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr">
+      <c r="N30" t="inlineStr">
         <is>
           <t>Hot</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr">
+      <c r="O30" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P28" t="inlineStr">
+      <c r="P30" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q28" t="inlineStr">
+      <c r="Q30" t="inlineStr">
         <is>
           <t>Không kết nối được app/Wifi và không theo dõi được hiệu suất</t>
         </is>
       </c>
-      <c r="R28" t="inlineStr">
+      <c r="R30" t="inlineStr">
         <is>
           <t>KH đã báo CN
 KH đang dùng NLMT hiện tại bị lỗi biến tần, ko kết nối được app
@@ -4307,573 +4577,573 @@
 NOTE: địa chỉ hiện tại của KH: thôn phú mỹ, xã tiến thắng, Hà Nội</t>
         </is>
       </c>
-      <c r="S28" t="inlineStr">
+      <c r="S30" t="inlineStr">
         <is>
           <t>15:34 24/03/2026</t>
         </is>
       </c>
-      <c r="T28" t="inlineStr">
+      <c r="T30" t="inlineStr">
         <is>
           <t>17:30 01/04/2026</t>
         </is>
       </c>
-      <c r="U28" t="inlineStr">
+      <c r="U30" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V28" t="inlineStr">
+      <c r="V30" t="inlineStr">
         <is>
           <t>Sắp quá hạn</t>
         </is>
       </c>
-      <c r="W28" t="inlineStr">
+      <c r="W30" t="inlineStr">
         <is>
           <t>Phạm Văn Nghĩa</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr">
+      <c r="X30" t="inlineStr">
         <is>
           <t>023020</t>
         </is>
       </c>
-      <c r="Y28" s="2">
+      <c r="Y30" s="2">
         <v>46105</v>
       </c>
-      <c r="Z28">
-        <v>6</v>
-      </c>
-      <c r="AA28" t="inlineStr">
+      <c r="Z30">
+        <v>7</v>
+      </c>
+      <c r="AA30" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
+      <c r="AB30" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
+      <c r="AC30" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
+    <row r="31">
+      <c r="A31" t="inlineStr">
         <is>
           <t>KV3</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>HCM</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>Inverter</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_BDG_1352264</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="H31" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
+      <c r="J31" t="inlineStr">
         <is>
           <t>Nguyễn Liễu Thông</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
+      <c r="K31" t="inlineStr">
         <is>
           <t>0362126000</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
+      <c r="L31" t="inlineStr">
         <is>
           <t>ph</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr">
+      <c r="M31" t="inlineStr">
         <is>
           <t>Nhân viên nội bộ VCC</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr">
+      <c r="N31" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O29" t="inlineStr">
+      <c r="O31" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P29" t="inlineStr">
+      <c r="P31" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q29" t="inlineStr">
+      <c r="Q31" t="inlineStr">
         <is>
           <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
-      <c r="R29" t="inlineStr">
+      <c r="R31" t="inlineStr">
         <is>
           <t>không hoạt động</t>
         </is>
       </c>
-      <c r="S29" t="inlineStr">
+      <c r="S31" t="inlineStr">
         <is>
           <t>09:29 26/03/2026</t>
         </is>
       </c>
-      <c r="T29" t="inlineStr">
-        <is>
-          <t>09:00 01/04/2026</t>
-        </is>
-      </c>
-      <c r="U29" t="inlineStr">
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>17:30 03/04/2026</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V29" t="inlineStr">
-        <is>
-          <t>Sắp quá hạn</t>
-        </is>
-      </c>
-      <c r="W29" t="inlineStr">
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
         <is>
           <t>Nguyễn Văn Toản</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr">
+      <c r="X31" t="inlineStr">
         <is>
           <t>427880</t>
         </is>
       </c>
-      <c r="Y29" s="2">
+      <c r="Y31" s="2">
         <v>46107</v>
       </c>
-      <c r="Z29">
-        <v>4</v>
-      </c>
-      <c r="AA29" t="inlineStr">
+      <c r="Z31">
+        <v>5</v>
+      </c>
+      <c r="AA31" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB29" t="inlineStr">
+      <c r="AB31" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
+      <c r="AC31" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
+    <row r="32">
+      <c r="A32" t="inlineStr">
         <is>
           <t>KV1</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>PTO</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_PTO_1620637</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="H32" t="inlineStr">
         <is>
           <t>Diamond</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
+      <c r="J32" t="inlineStr">
         <is>
           <t>Nguyễn Đình Mạnh</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
+      <c r="K32" t="inlineStr">
         <is>
           <t>0988308581</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
+      <c r="L32" t="inlineStr">
         <is>
           <t>Xã Thanh Cao, Huyện Lương Sơn, Tỉnh Hòa Bình</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr">
+      <c r="M32" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr">
+      <c r="N32" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O30" t="inlineStr">
+      <c r="O32" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P30" t="inlineStr">
+      <c r="P32" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q30" t="inlineStr">
+      <c r="Q32" t="inlineStr">
         <is>
           <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
-      <c r="R30" t="inlineStr">
+      <c r="R32" t="inlineStr">
         <is>
           <t>KH chưa báo CN
 KH phản ánh: hệ thống bị lỗi, điện bật 10 -15s chớp 1 lần
 KH yêu cầu chuyển KT xuống xử lý gấp</t>
         </is>
       </c>
-      <c r="S30" t="inlineStr">
+      <c r="S32" t="inlineStr">
         <is>
           <t>15:09 24/03/2026</t>
         </is>
       </c>
-      <c r="T30" t="inlineStr">
+      <c r="T32" t="inlineStr">
         <is>
           <t>21:10 23/04/2026</t>
         </is>
       </c>
-      <c r="U30" t="inlineStr">
+      <c r="U32" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V30" t="inlineStr">
+      <c r="V32" t="inlineStr">
         <is>
           <t>Trong hạn</t>
         </is>
       </c>
-      <c r="W30" t="inlineStr">
+      <c r="W32" t="inlineStr">
         <is>
           <t>Bùi Anh Nguyễn</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr">
+      <c r="X32" t="inlineStr">
         <is>
           <t>414445</t>
         </is>
       </c>
-      <c r="Y30" s="2">
+      <c r="Y32" s="2">
         <v>46105</v>
       </c>
-      <c r="Z30">
-        <v>6</v>
-      </c>
-      <c r="AA30" t="inlineStr">
+      <c r="Z32">
+        <v>7</v>
+      </c>
+      <c r="AA32" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
+      <c r="AB32" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
+      <c r="AC32" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
+    <row r="33">
+      <c r="A33" t="inlineStr">
         <is>
           <t>KV2</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>DLK</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_DLK_1648454</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="H33" t="inlineStr">
         <is>
           <t>Diamond</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
+      <c r="I33" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
+      <c r="J33" t="inlineStr">
         <is>
           <t>Huỳnh Chí Băng</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
+      <c r="K33" t="inlineStr">
         <is>
           <t>0366448992</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr">
+      <c r="L33" t="inlineStr">
         <is>
           <t>Xã Ea Khăl, Tỉnh Đắk Lắk</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr">
+      <c r="M33" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr">
+      <c r="N33" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O31" t="inlineStr">
+      <c r="O33" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P31" t="inlineStr">
+      <c r="P33" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q31" t="inlineStr">
+      <c r="Q33" t="inlineStr">
         <is>
           <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
-      <c r="R31" t="inlineStr">
+      <c r="R33" t="inlineStr">
         <is>
           <t>KH đã báo CN: a Nguyễn Văn Hà	nửa thasg nhưng chưa có ai đến hỗ trợ
 KH phản ánh hệ thống điện năng lượng mặt trời ko hoạt động
 KH yêu cầu xử lý gấp</t>
         </is>
       </c>
-      <c r="S31" t="inlineStr">
+      <c r="S33" t="inlineStr">
         <is>
           <t>15:19 24/03/2026</t>
         </is>
       </c>
-      <c r="T31" t="inlineStr">
+      <c r="T33" t="inlineStr">
         <is>
           <t>10:50 31/03/2026</t>
         </is>
       </c>
-      <c r="U31" t="inlineStr">
+      <c r="U33" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V31" t="inlineStr">
+      <c r="V33" t="inlineStr">
         <is>
           <t>Sắp quá hạn</t>
         </is>
       </c>
-      <c r="W31" t="inlineStr">
+      <c r="W33" t="inlineStr">
         <is>
           <t>Nguyễn Văn Hà</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr">
+      <c r="X33" t="inlineStr">
         <is>
           <t>008244</t>
         </is>
       </c>
-      <c r="Y31" s="2">
+      <c r="Y33" s="2">
         <v>46105</v>
       </c>
-      <c r="Z31">
-        <v>6</v>
-      </c>
-      <c r="AA31" t="inlineStr">
+      <c r="Z33">
+        <v>7</v>
+      </c>
+      <c r="AA33" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB31" t="inlineStr">
+      <c r="AB33" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
+      <c r="AC33" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
+    <row r="34">
+      <c r="A34" t="inlineStr">
         <is>
           <t>KV1</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>NAN</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>CNTT</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>Camera 360 độ</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>299/2025/HĐKT</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t>B2B</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t>Khách hàng doanh nghiệp</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
+      <c r="J34" t="inlineStr">
         <is>
           <t>Ban Quản Lý Rừng Phòng Hộ Bắc Nghệ An</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
+      <c r="K34" t="inlineStr">
         <is>
           <t>0869217169</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
+      <c r="L34" t="inlineStr">
         <is>
           <t>Khối 11, Xã Quỳnh Lưu, Tỉnh Nghệ An</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr">
+      <c r="M34" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr">
+      <c r="N34" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O32" t="inlineStr">
+      <c r="O34" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P32" t="inlineStr">
+      <c r="P34" t="inlineStr">
         <is>
           <t>Hỗ trợ</t>
         </is>
       </c>
-      <c r="Q32" t="inlineStr">
+      <c r="Q34" t="inlineStr">
         <is>
           <t>Hướng dẫn, hỗ trợ sử dụng sản phẩm</t>
         </is>
       </c>
-      <c r="R32" t="inlineStr">
+      <c r="R34" t="inlineStr">
         <is>
           <t>1. KH đã báo cn
 2. KH phản ánh: camera 360 chưa kết nối được hệ thống điều khiển, chưa lên được tivi để xem và cũng như pccc rừng mùa khô.
@@ -4881,433 +5151,433 @@
 ***SĐT liên hệ: 0988867428, Anh Thức</t>
         </is>
       </c>
-      <c r="S32" t="inlineStr">
+      <c r="S34" t="inlineStr">
         <is>
           <t>08:45 24/03/2026</t>
         </is>
       </c>
-      <c r="T32" t="inlineStr">
-        <is>
-          <t>23:05 30/03/2026</t>
-        </is>
-      </c>
-      <c r="U32" t="inlineStr">
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>23:35 15/04/2026</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V32" t="inlineStr">
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Võ Trọng Đức</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>293804</t>
+        </is>
+      </c>
+      <c r="Y34" s="2">
+        <v>46105</v>
+      </c>
+      <c r="Z34">
+        <v>7</v>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>IOC</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>P.Triển khai</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>tietvt16</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>KV3</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>CMU</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>GPTH</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>CNTT</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Camera</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>KHCN_TT.GPTH_CMU_1265325</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>B2C</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Member</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Khách hàng cá nhân</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Bích Loan</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>0946842984</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>Bích Loan Cống Hội Đồng Nguyên</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>Nhân viên nội bộ VCC</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>Sau bán</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Sự cố</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>cammera bị off 1 cai</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>10:28 26/03/2026</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>17:30 01/04/2026</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Đang tiến hành</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
         <is>
           <t>Sắp quá hạn</t>
         </is>
       </c>
-      <c r="W32" t="inlineStr">
-        <is>
-          <t>Võ Trọng Đức</t>
-        </is>
-      </c>
-      <c r="X32" t="inlineStr">
-        <is>
-          <t>293804</t>
-        </is>
-      </c>
-      <c r="Y32" s="2">
-        <v>46105</v>
-      </c>
-      <c r="Z32">
-        <v>6</v>
-      </c>
-      <c r="AA32" t="inlineStr">
-        <is>
-          <t>IOC</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Lý Hoài Bảo</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>433302</t>
+        </is>
+      </c>
+      <c r="Y35" s="2">
+        <v>46107</v>
+      </c>
+      <c r="Z35">
+        <v>5</v>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>AIO</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
         <is>
           <t>P.Triển khai</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>tietvt16</t>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Tuyendv</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
+    <row r="36">
+      <c r="A36" t="inlineStr">
         <is>
           <t>KV3</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>CMU</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>CNTT</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>Camera</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>KHCN_TT.GPTH_CMU_1265325</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NLMT</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Hệ thống NLMT</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>KHCN_TT.GPTH_BPC_1427400</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Member</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>Bích Loan</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>0946842984</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>Bích Loan Cống Hội Đồng Nguyên</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>Nhân viên nội bộ VCC</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Công Ty Tnhh Phúc An Solutions</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>0972342939</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>abc,Phường An Lộc,Thị xã Bình Long,Tỉnh Bình Phước</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>Hotline</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O33" t="inlineStr">
+      <c r="O36" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P33" t="inlineStr">
+      <c r="P36" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q33" t="inlineStr">
+      <c r="Q36" t="inlineStr">
         <is>
           <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
-      <c r="R33" t="inlineStr">
-        <is>
-          <t>cammera bị off 1 cai</t>
-        </is>
-      </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>10:28 26/03/2026</t>
-        </is>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>17:30 01/04/2026</t>
-        </is>
-      </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>Đang tiến hành</t>
-        </is>
-      </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>Trong hạn</t>
-        </is>
-      </c>
-      <c r="W33" t="inlineStr">
-        <is>
-          <t>Lý Hoài Bảo</t>
-        </is>
-      </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>433302</t>
-        </is>
-      </c>
-      <c r="Y33" s="2">
-        <v>46107</v>
-      </c>
-      <c r="Z33">
-        <v>4</v>
-      </c>
-      <c r="AA33" t="inlineStr">
-        <is>
-          <t>AIO</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>P.Triển khai</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Tuyendv</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>KV3</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>GPTH</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>NLMT</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>Hệ thống NLMT</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>KHCN_TT.GPTH_BPC_1427400</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>B2C</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>Khách hàng cá nhân</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>Công Ty Tnhh Phúc An Solutions</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>0972342939</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>abc,Phường An Lộc,Thị xã Bình Long,Tỉnh Bình Phước</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>Hotline</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>Bình thường</t>
-        </is>
-      </c>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>Sau bán</t>
-        </is>
-      </c>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>Sự cố</t>
-        </is>
-      </c>
-      <c r="Q34" t="inlineStr">
-        <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
-        </is>
-      </c>
-      <c r="R34" t="inlineStr">
+      <c r="R36" t="inlineStr">
         <is>
           <t>1. KH chưa báo cn
 2. KH phản ánh: Cục pin lưu trữ đang ko hoạt động, ko sử dụng được.
 3. KH yêu cầu: Có KT qua kiểm tra, khắc phục tình trạng này cho KH.</t>
         </is>
       </c>
-      <c r="S34" t="inlineStr">
+      <c r="S36" t="inlineStr">
         <is>
           <t>14:29 23/03/2026</t>
         </is>
       </c>
-      <c r="T34" t="inlineStr">
+      <c r="T36" t="inlineStr">
         <is>
           <t>07:20 02/04/2026</t>
         </is>
       </c>
-      <c r="U34" t="inlineStr">
+      <c r="U36" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V34" t="inlineStr">
+      <c r="V36" t="inlineStr">
         <is>
           <t>Sắp quá hạn</t>
         </is>
       </c>
-      <c r="W34" t="inlineStr">
+      <c r="W36" t="inlineStr">
         <is>
           <t>Phạm Trung Hiếu</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr">
+      <c r="X36" t="inlineStr">
         <is>
           <t>264250</t>
         </is>
       </c>
-      <c r="Y34" s="2">
+      <c r="Y36" s="2">
         <v>46104</v>
       </c>
-      <c r="Z34">
-        <v>7</v>
-      </c>
-      <c r="AA34" t="inlineStr">
+      <c r="Z36">
+        <v>8</v>
+      </c>
+      <c r="AA36" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB34" t="inlineStr">
+      <c r="AB36" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
+      <c r="AC36" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
+    <row r="37">
+      <c r="A37" t="inlineStr">
         <is>
           <t>KV2</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>GLI</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>Inverter</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="F37" t="inlineStr">
         <is>
           <t>100901-KD/HDMB-2021/GLI-TT</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t>B2B</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="H37" t="inlineStr">
         <is>
           <t>Member</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
+      <c r="I37" t="inlineStr">
         <is>
           <t>Khách hàng doanh nghiệp</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr">
+      <c r="J37" t="inlineStr">
         <is>
           <t>Đồn Biên Phòng 723</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
+      <c r="K37" t="inlineStr">
         <is>
           <t>0862000202</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr">
+      <c r="L37" t="inlineStr">
         <is>
           <t>Đồn Biên Phòng 723</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr">
+      <c r="M37" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr">
+      <c r="N37" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O35" t="inlineStr">
+      <c r="O37" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P35" t="inlineStr">
+      <c r="P37" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q35" t="inlineStr">
+      <c r="Q37" t="inlineStr">
         <is>
           <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
-      <c r="R35" t="inlineStr">
+      <c r="R37" t="inlineStr">
         <is>
           <t>1.Đã báo chi nhánh chưa: chưa báo 
 2.Đã báo qua đâu: KH gọi TĐ
@@ -5315,290 +5585,290 @@
 4. KH yêu cầu KT qua kiểm tra xử lý cho KH.</t>
         </is>
       </c>
-      <c r="S35" t="inlineStr">
+      <c r="S37" t="inlineStr">
         <is>
           <t>08:00 23/03/2026</t>
         </is>
       </c>
-      <c r="T35" t="inlineStr">
+      <c r="T37" t="inlineStr">
         <is>
           <t>14:00 31/03/2026</t>
         </is>
       </c>
-      <c r="U35" t="inlineStr">
+      <c r="U37" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V35" t="inlineStr">
+      <c r="V37" t="inlineStr">
         <is>
           <t>Sắp quá hạn</t>
         </is>
       </c>
-      <c r="W35" t="inlineStr">
+      <c r="W37" t="inlineStr">
         <is>
           <t>Nguyễn Hà Nguyên</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr">
+      <c r="X37" t="inlineStr">
         <is>
           <t>060709</t>
         </is>
       </c>
-      <c r="Y35" s="2">
+      <c r="Y37" s="2">
         <v>46104</v>
       </c>
-      <c r="Z35">
-        <v>7</v>
-      </c>
-      <c r="AA35" t="inlineStr">
+      <c r="Z37">
+        <v>8</v>
+      </c>
+      <c r="AA37" t="inlineStr">
         <is>
           <t>IOC</t>
         </is>
       </c>
-      <c r="AB35" t="inlineStr">
+      <c r="AB37" t="inlineStr">
         <is>
           <t>P.Triển khai</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
+      <c r="AC37" t="inlineStr">
         <is>
           <t>truongdv17</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
+    <row r="38">
+      <c r="A38" t="inlineStr">
         <is>
           <t>KV2</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>DNG</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C38" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="D38" t="inlineStr">
         <is>
           <t>SS</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="E38" t="inlineStr">
         <is>
           <t>Công tắc thông minh</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="F38" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_DNG_1416913</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
+      <c r="H38" t="inlineStr">
         <is>
           <t>Member</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
+      <c r="I38" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr">
+      <c r="J38" t="inlineStr">
         <is>
           <t>Lê Đắc Quỳ</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr">
+      <c r="K38" t="inlineStr">
         <is>
           <t>0915313915</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr">
+      <c r="L38" t="inlineStr">
         <is>
           <t>Phường Hòa Xuân, Thành phố Đà Nẵng</t>
         </is>
       </c>
-      <c r="M36" t="inlineStr">
+      <c r="M38" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr">
+      <c r="N38" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O36" t="inlineStr">
+      <c r="O38" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P36" t="inlineStr">
+      <c r="P38" t="inlineStr">
         <is>
           <t>Hỗ trợ</t>
         </is>
       </c>
-      <c r="Q36" t="inlineStr">
+      <c r="Q38" t="inlineStr">
         <is>
           <t>Hướng dẫn, hỗ trợ sử dụng sản phẩm</t>
         </is>
       </c>
-      <c r="R36" t="inlineStr">
+      <c r="R38" t="inlineStr">
         <is>
           <t>1. KH đã báo cn
 2. KH phản ánh: Vào được aio app smart home nhưng ko thấy có công tắc.
 3. KH yêu cầu: Qua hỗ trợ, kiểm tra thiết bị cho KH, KH sẵn sàng trả phí.</t>
         </is>
       </c>
-      <c r="S36" t="inlineStr">
+      <c r="S38" t="inlineStr">
         <is>
           <t>08:00 23/03/2026</t>
         </is>
       </c>
-      <c r="T36" t="inlineStr">
+      <c r="T38" t="inlineStr">
         <is>
           <t>07:50 08/04/2026</t>
         </is>
       </c>
-      <c r="U36" t="inlineStr">
+      <c r="U38" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V36" t="inlineStr">
+      <c r="V38" t="inlineStr">
         <is>
           <t>Trong hạn</t>
         </is>
       </c>
-      <c r="W36" t="inlineStr">
+      <c r="W38" t="inlineStr">
         <is>
           <t>Ngô Văn Minh</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr">
+      <c r="X38" t="inlineStr">
         <is>
           <t>083585</t>
         </is>
       </c>
-      <c r="Y36" s="2">
+      <c r="Y38" s="2">
         <v>46104</v>
       </c>
-      <c r="Z36">
-        <v>7</v>
-      </c>
-      <c r="AA36" t="inlineStr">
+      <c r="Z38">
+        <v>8</v>
+      </c>
+      <c r="AA38" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB36" t="inlineStr">
+      <c r="AB38" t="inlineStr">
         <is>
           <t>P.Triển khai</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
+      <c r="AC38" t="inlineStr">
         <is>
           <t>Sonln15</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
+    <row r="39">
+      <c r="A39" t="inlineStr">
         <is>
           <t>KV1</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>BNH</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="D39" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="E39" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="F39" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_BGG_1597213</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="H39" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
+      <c r="I39" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr">
+      <c r="J39" t="inlineStr">
         <is>
           <t>Dương Văn Quân</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr">
+      <c r="K39" t="inlineStr">
         <is>
           <t>0359999199</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr">
+      <c r="L39" t="inlineStr">
         <is>
           <t>xã Hoàng Vân</t>
         </is>
       </c>
-      <c r="M37" t="inlineStr">
+      <c r="M39" t="inlineStr">
         <is>
           <t>Happycall</t>
         </is>
       </c>
-      <c r="N37" t="inlineStr">
+      <c r="N39" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O37" t="inlineStr">
+      <c r="O39" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P37" t="inlineStr">
+      <c r="P39" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q37" t="inlineStr">
+      <c r="Q39" t="inlineStr">
         <is>
           <t>Chất lượng, hiệu suất của sản phẩm/hệ thống thấp</t>
         </is>
       </c>
-      <c r="R37" t="inlineStr">
+      <c r="R39" t="inlineStr">
         <is>
           <t>1.Đã báo chi nhánh chưa: chưa báo
 2.Đã báo qua đâu: DTV HPC
@@ -5606,145 +5876,145 @@
 4.KH yêu cầu KT qua kiểm tra cho KH</t>
         </is>
       </c>
-      <c r="S37" t="inlineStr">
+      <c r="S39" t="inlineStr">
         <is>
           <t>08:00 23/03/2026</t>
         </is>
       </c>
-      <c r="T37" t="inlineStr">
+      <c r="T39" t="inlineStr">
         <is>
           <t>18:00 26/03/2026</t>
         </is>
       </c>
-      <c r="U37" t="inlineStr">
+      <c r="U39" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V37" t="inlineStr">
+      <c r="V39" t="inlineStr">
         <is>
           <t>Quá hạn</t>
         </is>
       </c>
-      <c r="W37" t="inlineStr">
+      <c r="W39" t="inlineStr">
         <is>
           <t>Phạm Văn Huy</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr">
+      <c r="X39" t="inlineStr">
         <is>
           <t>408869</t>
         </is>
       </c>
-      <c r="Y37" s="2">
+      <c r="Y39" s="2">
         <v>46104</v>
       </c>
-      <c r="Z37">
-        <v>7</v>
-      </c>
-      <c r="AA37" t="inlineStr">
+      <c r="Z39">
+        <v>8</v>
+      </c>
+      <c r="AA39" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB37" t="inlineStr">
+      <c r="AB39" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
+      <c r="AC39" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
+    <row r="40">
+      <c r="A40" t="inlineStr">
         <is>
           <t>KV3</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>CMU</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C40" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="D40" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="E40" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="F40" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_CMU_1384534</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="G40" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
+      <c r="H40" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
+      <c r="I40" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr">
+      <c r="J40" t="inlineStr">
         <is>
           <t>Nguyễn Đức Hiếu</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr">
+      <c r="K40" t="inlineStr">
         <is>
           <t>0949001616</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr">
+      <c r="L40" t="inlineStr">
         <is>
           <t>Khóm 10</t>
         </is>
       </c>
-      <c r="M38" t="inlineStr">
+      <c r="M40" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N38" t="inlineStr">
+      <c r="N40" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O38" t="inlineStr">
+      <c r="O40" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P38" t="inlineStr">
+      <c r="P40" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q38" t="inlineStr">
+      <c r="Q40" t="inlineStr">
         <is>
           <t>Không kết nối được app/Wifi và không theo dõi được hiệu suất</t>
         </is>
       </c>
-      <c r="R38" t="inlineStr">
+      <c r="R40" t="inlineStr">
         <is>
           <t>1.Đã báo chi nhánh chưa: đã báo
 2.Đã báo cho ai:  KT Thái
@@ -5753,467 +6023,186 @@
 5.KH yêu cầu KT qua kiểm tra gấp cho KH.</t>
         </is>
       </c>
-      <c r="S38" t="inlineStr">
+      <c r="S40" t="inlineStr">
         <is>
           <t>09:44 20/03/2026</t>
         </is>
       </c>
-      <c r="T38" t="inlineStr">
+      <c r="T40" t="inlineStr">
         <is>
           <t>23:55 31/03/2026</t>
         </is>
       </c>
-      <c r="U38" t="inlineStr">
+      <c r="U40" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V38" t="inlineStr">
+      <c r="V40" t="inlineStr">
         <is>
           <t>Sắp quá hạn</t>
         </is>
       </c>
-      <c r="W38" t="inlineStr">
+      <c r="W40" t="inlineStr">
         <is>
           <t>Võ Duy Khang</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr">
+      <c r="X40" t="inlineStr">
         <is>
           <t>473069</t>
         </is>
       </c>
-      <c r="Y38" s="2">
+      <c r="Y40" s="2">
         <v>46101</v>
       </c>
-      <c r="Z38">
-        <v>10</v>
-      </c>
-      <c r="AA38" t="inlineStr">
+      <c r="Z40">
+        <v>11</v>
+      </c>
+      <c r="AA40" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB38" t="inlineStr">
+      <c r="AB40" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
+      <c r="AC40" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>KV1</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>KV3</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>HCM</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="D41" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="E41" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>VCC_YCTX_NAN_37485587203842849</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>KHCN_TT.GPTH_HCM_1638575</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>Khách hàng cá nhân</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>Xuân Hương</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>0974371218</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>Xã Nhân Hòa, Tỉnh Nghệ An</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr">
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Diamond</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Khách hàng doanh nghiệp</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ TAYOTO</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>0911937779</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>quốc lộ 55, Xã Hồ Tràm, Thành phố Hồ Chí Minh, Xã Hồ Tràm, Thành phố Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
         <is>
           <t>Happycall</t>
         </is>
       </c>
-      <c r="N39" t="inlineStr">
+      <c r="N41" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O39" t="inlineStr">
-        <is>
-          <t>Trước bán</t>
-        </is>
-      </c>
-      <c r="P39" t="inlineStr">
-        <is>
-          <t>Hỗ trợ</t>
-        </is>
-      </c>
-      <c r="Q39" t="inlineStr">
-        <is>
-          <t>Tư vấn sản phẩm/dịch vụ</t>
-        </is>
-      </c>
-      <c r="R39" t="inlineStr">
-        <is>
-          <t>KH báo chưa thấy có nv liên hệ để tư vấn NLMT.</t>
-        </is>
-      </c>
-      <c r="S39" t="inlineStr">
-        <is>
-          <t>15:32 20/03/2026</t>
-        </is>
-      </c>
-      <c r="T39" t="inlineStr">
-        <is>
-          <t>17:15 02/04/2026</t>
-        </is>
-      </c>
-      <c r="U39" t="inlineStr">
-        <is>
-          <t>Đang tiến hành</t>
-        </is>
-      </c>
-      <c r="V39" t="inlineStr">
-        <is>
-          <t>Sắp quá hạn</t>
-        </is>
-      </c>
-      <c r="W39" t="inlineStr">
-        <is>
-          <t>Trần Bình Thanh</t>
-        </is>
-      </c>
-      <c r="X39" t="inlineStr">
-        <is>
-          <t>069159</t>
-        </is>
-      </c>
-      <c r="Y39" s="2">
-        <v>46101</v>
-      </c>
-      <c r="Z39">
-        <v>10</v>
-      </c>
-      <c r="AA39" t="inlineStr">
-        <is>
-          <t>IOC</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>P.KDNLMT</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>P.KDNLMT</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>KV3</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>HCM</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>GPTH</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>NLMT</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>Hệ thống NLMT</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>KHCN_TT.GPTH_HCM_1638575</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>B2C</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Diamond</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>Khách hàng doanh nghiệp</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ TAYOTO</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>0911937779</t>
-        </is>
-      </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>quốc lộ 55, Xã Hồ Tràm, Thành phố Hồ Chí Minh, Xã Hồ Tràm, Thành phố Hồ Chí Minh</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>Happycall</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>Bình thường</t>
-        </is>
-      </c>
-      <c r="O40" t="inlineStr">
+      <c r="O41" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P40" t="inlineStr">
+      <c r="P41" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q40" t="inlineStr">
+      <c r="Q41" t="inlineStr">
         <is>
           <t>Sản phẩm bị ngắt quãng/ Không theo dõi và không nghe được</t>
         </is>
       </c>
-      <c r="R40" t="inlineStr">
+      <c r="R41" t="inlineStr">
         <is>
           <t>1. KH chưa báo cn
 2. KH phản ánh: Sự cố từ TT_1772587360264 trước sau khi xử lý KH thấy hệ thống nlmt ko có ổn định, lâu lâu tự ngắt và phải bảo nv tắt 3 công tắc cp đi bật lại mãi mới được.
 3. KH yêu cầu: Kiểm tra lại hàng hóa xem có đúng với HĐ về chất lượng, hiệu suất không. Nếu có vấn đề thì thay mới tinh cho KH để hệ thống vận hành trơn tru.</t>
         </is>
       </c>
-      <c r="S40" t="inlineStr">
+      <c r="S41" t="inlineStr">
         <is>
           <t>09:25 19/03/2026</t>
         </is>
       </c>
-      <c r="T40" t="inlineStr">
+      <c r="T41" t="inlineStr">
         <is>
           <t>08:35 25/04/2026</t>
         </is>
       </c>
-      <c r="U40" t="inlineStr">
+      <c r="U41" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V40" t="inlineStr">
+      <c r="V41" t="inlineStr">
         <is>
           <t>Trong hạn</t>
         </is>
       </c>
-      <c r="W40" t="inlineStr">
+      <c r="W41" t="inlineStr">
         <is>
           <t>Lê Đức Cảnh</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr">
+      <c r="X41" t="inlineStr">
         <is>
           <t>291002</t>
         </is>
       </c>
-      <c r="Y40" s="2">
+      <c r="Y41" s="2">
         <v>46100</v>
       </c>
-      <c r="Z40">
-        <v>11</v>
-      </c>
-      <c r="AA40" t="inlineStr">
-        <is>
-          <t>AIO</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>KV3</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>HCM</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>GPTH</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>NLMT</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>Hệ thống NLMT</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>KHCN_TT.GPTH_HCM_1646383</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>B2C</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Diamond</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>Khách hàng cá nhân</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>Nguyễn Hữu Nghĩa</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>0945919596</t>
-        </is>
-      </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>Phường Tam Thắng, Thành phố Hồ Chí Minh, Phường Tam Thắng, Thành phố Hồ Chí Minh</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>Happycall</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>Bình thường</t>
-        </is>
-      </c>
-      <c r="O41" t="inlineStr">
-        <is>
-          <t>Sau bán</t>
-        </is>
-      </c>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t>Hỗ trợ</t>
-        </is>
-      </c>
-      <c r="Q41" t="inlineStr">
-        <is>
-          <t>Hướng dẫn, hỗ trợ sử dụng sản phẩm</t>
-        </is>
-      </c>
-      <c r="R41" t="inlineStr">
-        <is>
-          <t>KH yc ktra nguyên nhân xảy ra sự cố TT_1772849052506</t>
-        </is>
-      </c>
-      <c r="S41" t="inlineStr">
-        <is>
-          <t>08:00 16/03/2026</t>
-        </is>
-      </c>
-      <c r="T41" t="inlineStr">
-        <is>
-          <t>08:45 12/04/2026</t>
-        </is>
-      </c>
-      <c r="U41" t="inlineStr">
-        <is>
-          <t>Đang tiến hành</t>
-        </is>
-      </c>
-      <c r="V41" t="inlineStr">
-        <is>
-          <t>Trong hạn</t>
-        </is>
-      </c>
-      <c r="W41" t="inlineStr">
-        <is>
-          <t>Lê Đức Cảnh</t>
-        </is>
-      </c>
-      <c r="X41" t="inlineStr">
-        <is>
-          <t>291002</t>
-        </is>
-      </c>
-      <c r="Y41" s="2">
-        <v>46097</v>
-      </c>
       <c r="Z41">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
@@ -6234,90 +6223,233 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
+          <t>KV3</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>HCM</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>GPTH</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NLMT</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Hệ thống NLMT</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>KHCN_TT.GPTH_HCM_1646383</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>B2C</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Diamond</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Khách hàng cá nhân</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Nguyễn Hữu Nghĩa</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>0945919596</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>Phường Tam Thắng, Thành phố Hồ Chí Minh, Phường Tam Thắng, Thành phố Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>Happycall</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>Sau bán</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Hỗ trợ</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>Hướng dẫn, hỗ trợ sử dụng sản phẩm</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>KH yc ktra nguyên nhân xảy ra sự cố TT_1772849052506</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>08:00 16/03/2026</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>08:45 12/04/2026</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Đang tiến hành</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Lê Đức Cảnh</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>291002</t>
+        </is>
+      </c>
+      <c r="Y42" s="2">
+        <v>46097</v>
+      </c>
+      <c r="Z42">
+        <v>15</v>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>AIO</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
           <t>KV1</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>BNH</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C43" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="D43" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="E43" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="F43" t="inlineStr">
         <is>
           <t>KHCN_PINNLMT_BGG_0404930</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="G43" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
+      <c r="H43" t="inlineStr">
         <is>
           <t>Member</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
+      <c r="I43" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr">
+      <c r="J43" t="inlineStr">
         <is>
           <t>Lê Văn Mạnh</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr">
+      <c r="K43" t="inlineStr">
         <is>
           <t>0987567050</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr">
+      <c r="L43" t="inlineStr">
         <is>
           <t>Xã Liên Chung,Huyện Tân Yên,Tỉnh Bắc Giang</t>
         </is>
       </c>
-      <c r="M42" t="inlineStr">
+      <c r="M43" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N42" t="inlineStr">
+      <c r="N43" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O42" t="inlineStr">
+      <c r="O43" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P42" t="inlineStr">
+      <c r="P43" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q42" t="inlineStr">
+      <c r="Q43" t="inlineStr">
         <is>
           <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
-      <c r="R42" t="inlineStr">
+      <c r="R43" t="inlineStr">
         <is>
           <t>1.Đã báo chi nhánh chưa: đã báo
 2.KH báo cho GĐ Trường 
@@ -6326,280 +6458,280 @@
  5.KH yêu cầu KT qua kiểm tra gấp cho KH.</t>
         </is>
       </c>
-      <c r="S42" t="inlineStr">
+      <c r="S43" t="inlineStr">
         <is>
           <t>10:21 10/03/2026</t>
         </is>
       </c>
-      <c r="T42" t="inlineStr">
+      <c r="T43" t="inlineStr">
         <is>
           <t>09:00 30/03/2026</t>
         </is>
       </c>
-      <c r="U42" t="inlineStr">
+      <c r="U43" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V42" t="inlineStr">
+      <c r="V43" t="inlineStr">
         <is>
           <t>Quá hạn</t>
         </is>
       </c>
-      <c r="W42" t="inlineStr">
+      <c r="W43" t="inlineStr">
         <is>
           <t>Thân Đức Giang</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr">
+      <c r="X43" t="inlineStr">
         <is>
           <t>081984</t>
         </is>
       </c>
-      <c r="Y42" s="2">
+      <c r="Y43" s="2">
         <v>46091</v>
       </c>
-      <c r="Z42">
-        <v>20</v>
-      </c>
-      <c r="AA42" t="inlineStr">
+      <c r="Z43">
+        <v>21</v>
+      </c>
+      <c r="AA43" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB42" t="inlineStr">
+      <c r="AB43" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
+      <c r="AC43" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
+    <row r="44">
+      <c r="A44" t="inlineStr">
         <is>
           <t>KV2</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>QTI</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C44" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="D44" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="E44" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="F44" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_QTI_0991884</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="G44" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
+      <c r="I44" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr">
+      <c r="J44" t="inlineStr">
         <is>
           <t>Nguyễn Thị Như Mỹ</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
+      <c r="K44" t="inlineStr">
         <is>
           <t>0963369267</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr">
+      <c r="L44" t="inlineStr">
         <is>
           <t>KP4, Thị trấn Cam Lộ, Huyện Cam Lộ, Tỉnh Quảng Trị</t>
         </is>
       </c>
-      <c r="M43" t="inlineStr">
+      <c r="M44" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N43" t="inlineStr">
+      <c r="N44" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O43" t="inlineStr">
+      <c r="O44" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P43" t="inlineStr">
+      <c r="P44" t="inlineStr">
         <is>
           <t>Bảo hành</t>
         </is>
       </c>
-      <c r="Q43" t="inlineStr">
+      <c r="Q44" t="inlineStr">
         <is>
           <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
-      <c r="R43" t="inlineStr">
+      <c r="R44" t="inlineStr">
         <is>
           <t>1. KH đã báo cn: a Nguyễn Đình Bằng bên nlmt
 2. KH phản ánh: Hệ thống inverter báo lỗi mã lỗi 01.M011 và ko đẩy ra sản lượng điện nlmt.
 3. KH yêu cầu: Điều KT qua hỗ trợ giúp KH.</t>
         </is>
       </c>
-      <c r="S43" t="inlineStr">
+      <c r="S44" t="inlineStr">
         <is>
           <t>08:00 09/03/2026</t>
         </is>
       </c>
-      <c r="T43" t="inlineStr">
+      <c r="T44" t="inlineStr">
         <is>
           <t>11:45 10/04/2026</t>
         </is>
       </c>
-      <c r="U43" t="inlineStr">
+      <c r="U44" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V43" t="inlineStr">
+      <c r="V44" t="inlineStr">
         <is>
           <t>Trong hạn</t>
         </is>
       </c>
-      <c r="W43" t="inlineStr">
+      <c r="W44" t="inlineStr">
         <is>
           <t>Trương Thành</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr">
+      <c r="X44" t="inlineStr">
         <is>
           <t>462341</t>
         </is>
       </c>
-      <c r="Y43" s="2">
+      <c r="Y44" s="2">
         <v>46090</v>
       </c>
-      <c r="Z43">
-        <v>21</v>
-      </c>
-      <c r="AA43" t="inlineStr">
+      <c r="Z44">
+        <v>22</v>
+      </c>
+      <c r="AA44" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB43" t="inlineStr">
+      <c r="AB44" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
+      <c r="AC44" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
+    <row r="45">
+      <c r="A45" t="inlineStr">
         <is>
           <t>KV2</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B45" t="inlineStr">
         <is>
           <t>QNI</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="C45" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="D45" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="E45" t="inlineStr">
         <is>
           <t>Tấm pin NLMT</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="F45" t="inlineStr">
         <is>
           <t>KHCN_PINNLMT_KTM_0284233</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="G45" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
+      <c r="I45" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr">
+      <c r="J45" t="inlineStr">
         <is>
           <t>Nguyễn Xuân Quyết</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr">
+      <c r="K45" t="inlineStr">
         <is>
           <t>0981397050</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr">
+      <c r="L45" t="inlineStr">
         <is>
           <t>Khối phố 6, Thị trấn Plei Kần, Huyện Ngọc Hồi, Tỉnh Kon Tum</t>
         </is>
       </c>
-      <c r="M44" t="inlineStr">
+      <c r="M45" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N44" t="inlineStr">
+      <c r="N45" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O44" t="inlineStr">
+      <c r="O45" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P44" t="inlineStr">
+      <c r="P45" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q44" t="inlineStr">
+      <c r="Q45" t="inlineStr">
         <is>
           <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
-      <c r="R44" t="inlineStr">
+      <c r="R45" t="inlineStr">
         <is>
           <t>1.Đã báo chi nhánh chưa: đã báo 
 2.Đã báo cho ai:  NV Văn
@@ -6608,145 +6740,145 @@
 5.	 KH yêu cầu KT qua kiểm tra gấp cho KH</t>
         </is>
       </c>
-      <c r="S44" t="inlineStr">
+      <c r="S45" t="inlineStr">
         <is>
           <t>14:54 05/03/2026</t>
         </is>
       </c>
-      <c r="T44" t="inlineStr">
+      <c r="T45" t="inlineStr">
         <is>
           <t>17:00 31/03/2026</t>
         </is>
       </c>
-      <c r="U44" t="inlineStr">
+      <c r="U45" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V44" t="inlineStr">
+      <c r="V45" t="inlineStr">
         <is>
           <t>Sắp quá hạn</t>
         </is>
       </c>
-      <c r="W44" t="inlineStr">
+      <c r="W45" t="inlineStr">
         <is>
           <t>Đỗ Lê Thanh Dĩnh</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr">
+      <c r="X45" t="inlineStr">
         <is>
           <t>041111</t>
         </is>
       </c>
-      <c r="Y44" s="2">
+      <c r="Y45" s="2">
         <v>46086</v>
       </c>
-      <c r="Z44">
-        <v>25</v>
-      </c>
-      <c r="AA44" t="inlineStr">
+      <c r="Z45">
+        <v>26</v>
+      </c>
+      <c r="AA45" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB44" t="inlineStr">
+      <c r="AB45" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
+      <c r="AC45" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
+    <row r="46">
+      <c r="A46" t="inlineStr">
         <is>
           <t>KV3</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B46" t="inlineStr">
         <is>
           <t>HCM</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C46" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="D46" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="E46" t="inlineStr">
         <is>
           <t>Inverter</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="F46" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_VTU_1502475</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="G46" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
+      <c r="H46" t="inlineStr">
         <is>
           <t>Diamond</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
+      <c r="I46" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr">
+      <c r="J46" t="inlineStr">
         <is>
           <t>Nguyễn Phú Quý</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr">
+      <c r="K46" t="inlineStr">
         <is>
           <t>0947110192</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr">
+      <c r="L46" t="inlineStr">
         <is>
           <t>120 Chu Mạnh Trinh,Phường 8,Thành phố Vũng Tàu,Tỉnh Bà Rịa - Vũng Tàu, Phường Tam Thắng, Thành phố Hồ Chí Minh</t>
         </is>
       </c>
-      <c r="M45" t="inlineStr">
+      <c r="M46" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N45" t="inlineStr">
+      <c r="N46" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O45" t="inlineStr">
+      <c r="O46" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P45" t="inlineStr">
+      <c r="P46" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q45" t="inlineStr">
+      <c r="Q46" t="inlineStr">
         <is>
           <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
-      <c r="R45" t="inlineStr">
+      <c r="R46" t="inlineStr">
         <is>
           <t>1. Đã báo chi nhánh chưa: chưa báo
 2.KH gọi điện lên TĐ
@@ -6754,470 +6886,326 @@
 4.KH yêu cầu Kt kiểm tra lại pin và CN đưa ra phương án xử lý vấn đề thiệt hại kinh tế cho KH khi sử dụng điện NLMT không hiệu quả.</t>
         </is>
       </c>
-      <c r="S45" t="inlineStr">
+      <c r="S46" t="inlineStr">
         <is>
           <t>15:09 03/03/2026</t>
         </is>
       </c>
-      <c r="T45" t="inlineStr">
+      <c r="T46" t="inlineStr">
         <is>
           <t>12:55 15/03/2026</t>
         </is>
       </c>
-      <c r="U45" t="inlineStr">
+      <c r="U46" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V45" t="inlineStr">
+      <c r="V46" t="inlineStr">
         <is>
           <t>Trong hạn</t>
         </is>
       </c>
-      <c r="W45" t="inlineStr">
+      <c r="W46" t="inlineStr">
         <is>
           <t>Lê Đức Cảnh</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr">
+      <c r="X46" t="inlineStr">
         <is>
           <t>291002</t>
         </is>
       </c>
-      <c r="Y45" s="2">
+      <c r="Y46" s="2">
         <v>46084</v>
       </c>
-      <c r="Z45">
-        <v>27</v>
-      </c>
-      <c r="AA45" t="inlineStr">
+      <c r="Z46">
+        <v>28</v>
+      </c>
+      <c r="AA46" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB45" t="inlineStr">
+      <c r="AB46" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
+      <c r="AC46" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
+    <row r="47">
+      <c r="A47" t="inlineStr">
         <is>
           <t>KV1</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B47" t="inlineStr">
         <is>
           <t>NAN</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C47" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="D47" t="inlineStr">
         <is>
           <t>CNTT</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="E47" t="inlineStr">
         <is>
           <t>Camera</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="F47" t="inlineStr">
         <is>
           <t>081101/HĐMBLĐ-2024/THQUYNHHUNG-NAN</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="G47" t="inlineStr">
         <is>
           <t>B2B</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
+      <c r="I47" t="inlineStr">
         <is>
           <t>Khách hàng doanh nghiệp</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr">
+      <c r="J47" t="inlineStr">
         <is>
           <t>Trường Tiểu Học Quỳnh Hưng</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr">
+      <c r="K47" t="inlineStr">
         <is>
           <t>0963785576</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr">
+      <c r="L47" t="inlineStr">
         <is>
           <t>Xóm 6,Xã Quỳnh Hưng,Huyện Quỳnh Lưu,Tỉnh Nghệ An</t>
         </is>
       </c>
-      <c r="M46" t="inlineStr">
+      <c r="M47" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N46" t="inlineStr">
+      <c r="N47" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O46" t="inlineStr">
+      <c r="O47" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P46" t="inlineStr">
+      <c r="P47" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q46" t="inlineStr">
+      <c r="Q47" t="inlineStr">
         <is>
           <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
-      <c r="R46" t="inlineStr">
+      <c r="R47" t="inlineStr">
         <is>
           <t>1. Kh chưa báo cn
 2. Kh phản ánh: Hiện tại ko có mắt cam nào xem đc, mạng thì vẫn bình thường
 3. Kh yc: Yc cn hỗ trợ</t>
         </is>
       </c>
-      <c r="S46" t="inlineStr">
+      <c r="S47" t="inlineStr">
         <is>
           <t>16:54 26/02/2026</t>
         </is>
       </c>
-      <c r="T46" t="inlineStr">
+      <c r="T47" t="inlineStr">
         <is>
           <t>18:00 31/03/2026</t>
         </is>
       </c>
-      <c r="U46" t="inlineStr">
+      <c r="U47" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V46" t="inlineStr">
+      <c r="V47" t="inlineStr">
         <is>
           <t>Sắp quá hạn</t>
         </is>
       </c>
-      <c r="W46" t="inlineStr">
+      <c r="W47" t="inlineStr">
         <is>
           <t>Lê Văn Toán</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr">
+      <c r="X47" t="inlineStr">
         <is>
           <t>119464</t>
         </is>
       </c>
-      <c r="Y46" s="2">
+      <c r="Y47" s="2">
         <v>46079</v>
       </c>
-      <c r="Z46">
-        <v>32</v>
-      </c>
-      <c r="AA46" t="inlineStr">
+      <c r="Z47">
+        <v>33</v>
+      </c>
+      <c r="AA47" t="inlineStr">
         <is>
           <t>IOC</t>
         </is>
       </c>
-      <c r="AB46" t="inlineStr">
+      <c r="AB47" t="inlineStr">
         <is>
           <t>P.Triển khai</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr">
+      <c r="AC47" t="inlineStr">
         <is>
           <t>tietvt16</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
+    <row r="48">
+      <c r="A48" t="inlineStr">
         <is>
           <t>KV3</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B48" t="inlineStr">
         <is>
           <t>DNI</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C48" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="D48" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="E48" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="F48" t="inlineStr">
         <is>
           <t>KHDN_TT.GPTH_DNI_1659133</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="G48" t="inlineStr">
         <is>
           <t>B2B</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
+      <c r="H48" t="inlineStr">
         <is>
           <t>Diamond</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
+      <c r="I48" t="inlineStr">
         <is>
           <t>Khách hàng doanh nghiệp</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr">
+      <c r="J48" t="inlineStr">
         <is>
           <t>CÔNG TY TNHH KHOA HỌC KỸ THUẬT TOÀN CẦU</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr">
+      <c r="K48" t="inlineStr">
         <is>
           <t>0907002673</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr">
+      <c r="L48" t="inlineStr">
         <is>
           <t>Lầu 19, Khu A, Số 4 Nguyễn Đình Chiểu, Phường Tân Định, Thành phố Hồ Chí Minh</t>
         </is>
       </c>
-      <c r="M47" t="inlineStr">
+      <c r="M48" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N47" t="inlineStr">
+      <c r="N48" t="inlineStr">
         <is>
           <t>Hot</t>
         </is>
       </c>
-      <c r="O47" t="inlineStr">
+      <c r="O48" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P47" t="inlineStr">
+      <c r="P48" t="inlineStr">
         <is>
           <t>Bảo hành</t>
         </is>
       </c>
-      <c r="Q47" t="inlineStr">
+      <c r="Q48" t="inlineStr">
         <is>
           <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
-      <c r="R47" t="inlineStr">
+      <c r="R48" t="inlineStr">
         <is>
           <t>1. Kh đã báo cn
 2. Kh phản ánh: Hệ của kh dạo này sd có hiện tượng liên tục bị sập. Kh đã báo kt và kt phản hồi do kh sd quá tải nhưng từ khi lắp đến nay kh báo chỉ dùng bằng đó thiết bị chứ ko hơn
 3. kh yc: YC cn hỗ trợ sớm</t>
         </is>
       </c>
-      <c r="S47" t="inlineStr">
+      <c r="S48" t="inlineStr">
         <is>
           <t>13:30 23/02/2026</t>
         </is>
       </c>
-      <c r="T47" t="inlineStr">
+      <c r="T48" t="inlineStr">
         <is>
           <t>18:30 21/03/2026</t>
         </is>
       </c>
-      <c r="U47" t="inlineStr">
+      <c r="U48" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V47" t="inlineStr">
+      <c r="V48" t="inlineStr">
         <is>
           <t>Trong hạn</t>
         </is>
       </c>
-      <c r="W47" t="inlineStr">
+      <c r="W48" t="inlineStr">
         <is>
           <t>Nguyễn Hữu Tâm Định</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr">
+      <c r="X48" t="inlineStr">
         <is>
           <t>450471</t>
         </is>
       </c>
-      <c r="Y47" s="2">
+      <c r="Y48" s="2">
         <v>46076</v>
       </c>
-      <c r="Z47">
-        <v>35</v>
-      </c>
-      <c r="AA47" t="inlineStr">
-        <is>
-          <t>AIO</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>KV1</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>GPTH</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>NLMT</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>Inverter</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>KHCN_TT.GPTH_NAN_1364237</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>B2C</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>Khách hàng cá nhân</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>Trương Công An</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>0914531694</t>
-        </is>
-      </c>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>khối 2</t>
-        </is>
-      </c>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>Hotline</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>Hot</t>
-        </is>
-      </c>
-      <c r="O48" t="inlineStr">
-        <is>
-          <t>Sau bán</t>
-        </is>
-      </c>
-      <c r="P48" t="inlineStr">
-        <is>
-          <t>Bảo hành</t>
-        </is>
-      </c>
-      <c r="Q48" t="inlineStr">
-        <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
-        </is>
-      </c>
-      <c r="R48" t="inlineStr">
-        <is>
-          <t>- KH phản ánh nhân sự Lê Văn Anh mang thiết bị ivt đi bảo hành từ 8/12/2025  tới nay 16/1/2026 vẫn chưa có ivt gửi về cho KH. Đã rất lâu và thiệt hại rất nhiều, trước đấy có mang ắc quy đi BH cũng k được giờ mang ivt đi hơn tháng chưa thấy phản hồi 
-- KH Yc ktra lại và phản hồi mang thiết bị về lắp đặt  lại cho KH</t>
-        </is>
-      </c>
-      <c r="S48" t="inlineStr">
-        <is>
-          <t>08:00 19/01/2026</t>
-        </is>
-      </c>
-      <c r="T48" t="inlineStr">
-        <is>
-          <t>22:00 17/04/2026</t>
-        </is>
-      </c>
-      <c r="U48" t="inlineStr">
-        <is>
-          <t>Đang tiến hành</t>
-        </is>
-      </c>
-      <c r="V48" t="inlineStr">
-        <is>
-          <t>Trong hạn</t>
-        </is>
-      </c>
-      <c r="W48" t="inlineStr">
-        <is>
-          <t>Lê Văn Anh</t>
-        </is>
-      </c>
-      <c r="X48" t="inlineStr">
-        <is>
-          <t>069170</t>
-        </is>
-      </c>
-      <c r="Y48" s="2">
-        <v>46041</v>
-      </c>
       <c r="Z48">
-        <v>70</v>
+        <v>36</v>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
@@ -7243,279 +7231,279 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
+          <t>NAN</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>GPTH</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NLMT</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Inverter</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>KHCN_TT.GPTH_NAN_1364237</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>B2C</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Khách hàng cá nhân</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Trương Công An</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0914531694</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>khối 2</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>Hotline</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>Sau bán</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Bảo hành</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>- KH phản ánh nhân sự Lê Văn Anh mang thiết bị ivt đi bảo hành từ 8/12/2025  tới nay 16/1/2026 vẫn chưa có ivt gửi về cho KH. Đã rất lâu và thiệt hại rất nhiều, trước đấy có mang ắc quy đi BH cũng k được giờ mang ivt đi hơn tháng chưa thấy phản hồi 
+- KH Yc ktra lại và phản hồi mang thiết bị về lắp đặt  lại cho KH</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>08:00 19/01/2026</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>22:00 17/04/2026</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Đang tiến hành</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Lê Văn Anh</t>
+        </is>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>069170</t>
+        </is>
+      </c>
+      <c r="Y49" s="2">
+        <v>46041</v>
+      </c>
+      <c r="Z49">
+        <v>71</v>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>AIO</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>KV1</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
           <t>TNN</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="C50" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="D50" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="E50" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="F50" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_TNN_0885867</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="G50" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
+      <c r="I50" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J49" t="inlineStr">
+      <c r="J50" t="inlineStr">
         <is>
           <t>Nguyễn Đức Hùng</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr">
+      <c r="K50" t="inlineStr">
         <is>
           <t>0396264028</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr">
+      <c r="L50" t="inlineStr">
         <is>
           <t>Xóm Ấp Chè, Xã Văn Hán, Huyện Đồng Hỷ, Tỉnh Thái Nguyên</t>
         </is>
       </c>
-      <c r="M49" t="inlineStr">
+      <c r="M50" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N49" t="inlineStr">
+      <c r="N50" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O49" t="inlineStr">
+      <c r="O50" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P49" t="inlineStr">
+      <c r="P50" t="inlineStr">
         <is>
           <t>Bảo hành</t>
         </is>
       </c>
-      <c r="Q49" t="inlineStr">
+      <c r="Q50" t="inlineStr">
         <is>
           <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
-      <c r="R49" t="inlineStr">
+      <c r="R50" t="inlineStr">
         <is>
           <t>1. Đã báo CN: Chưa báo
 2. KH báo sự cố: 1 cục pin lưu trữ không vào điện và khi mất điện lưới hệ không tải điện vào để sử dụng.
 3. Kh yêu cầu: KT qua kiểm tra cho Kh</t>
         </is>
       </c>
-      <c r="S49" t="inlineStr">
+      <c r="S50" t="inlineStr">
         <is>
           <t>08:00 14/01/2026</t>
         </is>
       </c>
-      <c r="T49" t="inlineStr">
+      <c r="T50" t="inlineStr">
         <is>
           <t>17:00 25/02/2026</t>
         </is>
       </c>
-      <c r="U49" t="inlineStr">
+      <c r="U50" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V49" t="inlineStr">
+      <c r="V50" t="inlineStr">
         <is>
           <t>Trong hạn</t>
         </is>
       </c>
-      <c r="W49" t="inlineStr">
+      <c r="W50" t="inlineStr">
         <is>
           <t>Trần Xuân Kương</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr">
+      <c r="X50" t="inlineStr">
         <is>
           <t>289759</t>
         </is>
       </c>
-      <c r="Y49" s="2">
+      <c r="Y50" s="2">
         <v>46036</v>
       </c>
-      <c r="Z49">
-        <v>75</v>
-      </c>
-      <c r="AA49" t="inlineStr">
+      <c r="Z50">
+        <v>76</v>
+      </c>
+      <c r="AA50" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB49" t="inlineStr">
+      <c r="AB50" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
-      <c r="AC49" t="inlineStr">
+      <c r="AC50" t="inlineStr">
         <is>
           <t>VHKT</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>KV1</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>BNH</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>GPTH</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>M&amp;E</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>Bếp từ</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>KHDN_TT.GPTH_HNI_2402026_CDV</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>B2C</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Silver</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>Khách hàng cá nhân</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>Nguyễn Quang Vũ</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>0983034568</t>
-        </is>
-      </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>CNCT Viettel Bắc Ninh</t>
-        </is>
-      </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>Nhân viên nội bộ VCC</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>Bình thường</t>
-        </is>
-      </c>
-      <c r="O50" t="inlineStr">
-        <is>
-          <t>Sau bán</t>
-        </is>
-      </c>
-      <c r="P50" t="inlineStr">
-        <is>
-          <t>Bảo hành</t>
-        </is>
-      </c>
-      <c r="Q50" t="inlineStr">
-        <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
-        </is>
-      </c>
-      <c r="R50" t="inlineStr">
-        <is>
-          <t>KH nội bộ VCC T12/2025 quay số trúng thưởng bếp từ đơn AIO, bếp không hoạt động. Yêu cầu Kt qua bảo hành gấp. 
-Quà tặng trúng thưởng nên không có thông tin mã HĐ.</t>
-        </is>
-      </c>
-      <c r="S50" t="inlineStr">
-        <is>
-          <t>08:00 05/01/2026</t>
-        </is>
-      </c>
-      <c r="T50" t="inlineStr">
-        <is>
-          <t>10:25 03/04/2026</t>
-        </is>
-      </c>
-      <c r="U50" t="inlineStr">
-        <is>
-          <t>Đang tiến hành</t>
-        </is>
-      </c>
-      <c r="V50" t="inlineStr">
-        <is>
-          <t>Trong hạn</t>
-        </is>
-      </c>
-      <c r="W50" t="inlineStr">
-        <is>
-          <t>Đinh Thị Ngọc</t>
-        </is>
-      </c>
-      <c r="X50" t="inlineStr">
-        <is>
-          <t>205029</t>
-        </is>
-      </c>
-      <c r="Y50" s="2">
-        <v>46027</v>
-      </c>
-      <c r="Z50">
-        <v>84</v>
-      </c>
-      <c r="AA50" t="inlineStr">
-        <is>
-          <t>AIO</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>P.Triển khai</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Anhnt631</t>
         </is>
       </c>
     </row>
@@ -7527,80 +7515,224 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
+          <t>BNH</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>GPTH</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>M&amp;E</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Bếp từ</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>KHDN_TT.GPTH_HNI_2402026_CDV</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>B2C</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Khách hàng cá nhân</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Nguyễn Quang Vũ</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>0983034568</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>CNCT Viettel Bắc Ninh</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>Nhân viên nội bộ VCC</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>Sau bán</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Bảo hành</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>KH nội bộ VCC T12/2025 quay số trúng thưởng bếp từ đơn AIO, bếp không hoạt động. Yêu cầu Kt qua bảo hành gấp. 
+Quà tặng trúng thưởng nên không có thông tin mã HĐ.</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>08:00 05/01/2026</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>10:25 03/04/2026</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Đang tiến hành</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Đinh Thị Ngọc</t>
+        </is>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>205029</t>
+        </is>
+      </c>
+      <c r="Y51" s="2">
+        <v>46027</v>
+      </c>
+      <c r="Z51">
+        <v>85</v>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>AIO</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>P.Triển khai</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Anhnt631</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>KV1</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
           <t>QNH</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="C52" t="inlineStr">
         <is>
           <t>DVKT</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="D52" t="inlineStr">
         <is>
           <t>Home Service</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="E52" t="inlineStr">
         <is>
           <t>Dịch vụ khác</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
+      <c r="F52" t="inlineStr">
         <is>
           <t>23092025/HĐTP-SPT-VIETTEL</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
+      <c r="G52" t="inlineStr">
         <is>
           <t>B2B</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
+      <c r="I52" t="inlineStr">
         <is>
           <t>Khách hàng doanh nghiệp</t>
         </is>
       </c>
-      <c r="J51" t="inlineStr">
+      <c r="J52" t="inlineStr">
         <is>
           <t>CÔNG TY CỔ PHẦN SPT VIỆT NAM</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr">
+      <c r="K52" t="inlineStr">
         <is>
           <t>0962892720</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr">
+      <c r="L52" t="inlineStr">
         <is>
           <t>...</t>
         </is>
       </c>
-      <c r="M51" t="inlineStr">
+      <c r="M52" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N51" t="inlineStr">
+      <c r="N52" t="inlineStr">
         <is>
           <t>Hot</t>
         </is>
       </c>
-      <c r="O51" t="inlineStr">
+      <c r="O52" t="inlineStr">
         <is>
           <t>Trong bán</t>
         </is>
       </c>
-      <c r="P51" t="inlineStr">
+      <c r="P52" t="inlineStr">
         <is>
           <t>Khiếu nại</t>
         </is>
       </c>
-      <c r="Q51" t="inlineStr">
+      <c r="Q52" t="inlineStr">
         <is>
           <t>Tiến độ triển khai chậm</t>
         </is>
       </c>
-      <c r="R51" t="inlineStr">
+      <c r="R52" t="inlineStr">
         <is>
           <t>- Đối tác Công ty cổ phần SPT Việt Nam (sdt phản ánh 0975014010) tiếp tục gọi tđ phản ánh về vấn đề chậm trễ tiến độ và thiếu nhân lực thi công cho dự án Thi công lắp đặt hệ thống Chiller. 
 - Kh báo hiện tại vẫn chậm tiến độ, cn ko thay đổi hay tiến triển thêm gì
@@ -7608,53 +7740,53 @@
 - Kh yc: Yc TCT có biện pháp xử lý rõ ràng cho kh</t>
         </is>
       </c>
-      <c r="S51" t="inlineStr">
+      <c r="S52" t="inlineStr">
         <is>
           <t>08:00 10/12/2025</t>
         </is>
       </c>
-      <c r="T51" t="inlineStr">
+      <c r="T52" t="inlineStr">
         <is>
           <t>15:00 16/12/2025</t>
         </is>
       </c>
-      <c r="U51" t="inlineStr">
+      <c r="U52" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V51" t="inlineStr">
+      <c r="V52" t="inlineStr">
         <is>
           <t>Trong hạn</t>
         </is>
       </c>
-      <c r="W51" t="inlineStr">
+      <c r="W52" t="inlineStr">
         <is>
           <t>Đặng Việt Phú</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr">
+      <c r="X52" t="inlineStr">
         <is>
           <t>062146</t>
         </is>
       </c>
-      <c r="Y51" s="2">
+      <c r="Y52" s="2">
         <v>46001</v>
       </c>
-      <c r="Z51">
-        <v>110</v>
-      </c>
-      <c r="AA51" t="inlineStr">
+      <c r="Z52">
+        <v>111</v>
+      </c>
+      <c r="AA52" t="inlineStr">
         <is>
           <t>IOC</t>
         </is>
       </c>
-      <c r="AB51" t="inlineStr">
+      <c r="AB52" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
-      <c r="AC51" t="inlineStr">
+      <c r="AC52" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>

--- a/data/3.R_pakh.xlsx
+++ b/data/3.R_pakh.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC47"/>
+  <dimension ref="A1:AC52"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="25" max="25" width="20.7109375" style="2" customWidth="1"/>
@@ -511,32 +511,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>KV1</t>
+          <t>KV3</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>QNH</t>
+          <t>TNH</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>DVKT</t>
+          <t>GPTH</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Home Service</t>
+          <t>NLMT</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Bảo dưỡng Điều hòa treo tường (9.000BTU ÷ 12.000 BTU)</t>
+          <t>Tấm pin NLMT</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>VCC_HS_QNH_1774857132975</t>
+          <t>VCC_YCTX_TNH_39022344127055742</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -551,22 +551,22 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Quang Vinh</t>
+          <t>Anh Thanh</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0836242666</t>
+          <t>0971787957</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>539 cao thắng hạ Long quảng ninh, Phường Hà Lầm, Tỉnh Quảng Ninh</t>
+          <t>Xã Cần Giuộc, Tỉnh Tây Ninh</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Facebook</t>
+          <t>Hotline</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -586,22 +586,22 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>Liên hệ chậm</t>
+          <t>Liên hệ tư vấn chậm</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>KH báo chưa có KT liên hệ.</t>
+          <t>KH có nhu cầu lắp  trọn gói NLMT áp mái theo công suất có hệ lưu trữ  KH phản ánh chưa có nhân viên liên hệ tư vấn</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>10:36 01/04/2026</t>
+          <t>08:00 02/04/2026</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>14:36 01/04/2026</t>
+          <t>09:00 03/04/2026</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -616,33 +616,33 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>Đào Minh Đức</t>
+          <t>Lê Thanh Huy</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>290593</t>
+          <t>488102</t>
         </is>
       </c>
       <c r="Y2" s="2">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="Z2">
         <v>0</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>HS</t>
+          <t>IOC</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>VHKT</t>
+          <t>P.KDNLMT</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>VHKT</t>
+          <t>P.KDNLMT</t>
         </is>
       </c>
     </row>
@@ -654,7 +654,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>GLI</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -664,17 +664,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>CNTT</t>
+          <t>NLMT</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Camera</t>
+          <t>Tấm pin NLMT</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>KHCN_TT.GPTH_DNG_1278799</t>
+          <t>KHCN_PINNLMT_GLI_0299078</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -694,17 +694,17 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Trần Công Sơn</t>
+          <t>Bùi Quang Vinh</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0326272266</t>
+          <t>0983885630</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>265 Hà Huy Tập, Phường Hòa Khê, Quận Thanh Khê, Thành phố Đà Nẵng</t>
+          <t>Nayder</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -729,29 +729,27 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>Lỗi kết nối giữa thiết bị và hệ thống theo dõi</t>
+          <t>Tấm pin bị rò rỉ/ Lỗi</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1. KH chưa báo cn
-2. KH phản ánh: Camera ko kết nối, ko sử dụng được
-3. KH yêu cầu: KT qua kiểm tra thiết bị cho KH, nếu có phát sinh KH sẽ trả phí.</t>
+          <t>hệ thống nlmt bị lỗi, viên pin bị lủng. Kĩ thuật báo theo dõi. Điện bị sụt</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>10:28 01/04/2026</t>
+          <t>15:36 01/04/2026</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>10:28 02/04/2026</t>
+          <t>15:36 02/04/2026</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>Đang tiến hành</t>
+          <t>Chưa thực hiện</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -761,19 +759,19 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>Lê Thị Yến</t>
+          <t>Nguyễn Đình Thi</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>006333</t>
+          <t>075692</t>
         </is>
       </c>
       <c r="Y3" s="2">
         <v>46113</v>
       </c>
       <c r="Z3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
@@ -782,44 +780,44 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>P.Triển khai</t>
+          <t>VHKT</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Sonln15</t>
+          <t>VHKT</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>KV3</t>
+          <t>KV1</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>DTP</t>
+          <t>SLA</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>GPTH</t>
+          <t>DVKT</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NLMT</t>
+          <t>Home Service</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Hệ thống NLMT</t>
+          <t>Bảo dưỡng Điều hòa treo tường (9.000BTU ÷ 12.000 BTU)</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>KHCN_TT.GPTH_DTP_1618649</t>
+          <t>VCC_HS_SLA_1774835186760</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -827,11 +825,6 @@
           <t>B2C</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Diamond</t>
-        </is>
-      </c>
       <c r="I4" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
@@ -839,59 +832,57 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Nguyen Hoang Dung</t>
+          <t>Vu Tung</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0937819993</t>
+          <t>0919195360</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Hung Vuong Doi Dien Nha Van Hoa Khom 02 Phuong An Thanh TX Hong Ngu Dong Thap Phường An Thạnh Thị xã Hồng Ngự Tỉnh Đồng Tháp</t>
+          <t>Số nhà 329, tk19, xã mai sơn, tỉnh sơn la, Xã Mai Sơn, Tỉnh Sơn La</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Nhân viên nội bộ VCC</t>
+          <t>Facebook</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Bình thường</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Sau bán</t>
+          <t>Trước bán</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sự cố</t>
+          <t>Khiếu nại</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Liên hệ chậm</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>CN báo sự cố hộ KH
-1. KH phản ánh: Pin lưu trữ ko thấy xả, ko thấy giao tiếp với hệ thống
-2. KH yêu cầu: KT qua kiểm tra, khắc phục tình trạng này cho KH.</t>
+          <t>KH báo chưa thấy có KT gọi và đến, hẹn cả ngày hôm qua nhưng chỉ thấy gọi điện xin mã otp xong mất hút luôn.</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>10:06 01/04/2026</t>
+          <t>15:14 01/04/2026</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>10:06 02/04/2026</t>
+          <t>09:00 02/04/2026</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -901,28 +892,28 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>Trong hạn</t>
+          <t>Sắp quá hạn</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>Lê Thanh Phong</t>
+          <t>Nguyễn Chí Thanh</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>071101</t>
+          <t>081164</t>
         </is>
       </c>
       <c r="Y4" s="2">
         <v>46113</v>
       </c>
       <c r="Z4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>AIO</t>
+          <t>HS</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -944,85 +935,1063 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>GPTH</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NLMT</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Hệ thống NLMT</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>KHCN_TT.GPTH_AGG_1524617</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>B2C</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Khách hàng cá nhân</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Đoàn Thị Cẩm Tú</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0977285985</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Xã An Châu, Tỉnh An Giang</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Hotline</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Sau bán</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Sự cố</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>1. KH chưa báo cn
+2. KH phản ánh: Sự cố từ những lần trước đến giờ lại xảy ra và lại thấy báo lỗi khác so với các lần trước, KH khi lên app thấy báo lỗi là gôm công suất bị lỗi. CN cũng có qua khắc phục từ những lần trước rồi và có a Toản qua hỗ trợ, khắc phục được rồi và còn theo dõi thêm 1 tuần rưỡi nữa vẫn hoạt động bình thường, mà đến nay hệ thống nlmt lại ko thu được điện nữa.
+3. KH yêu cầu: Qua kiểm tra lại hệ thống, khắc phục tình trạng này dứt điểm cho KH.</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>14:45 01/04/2026</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>14:45 02/04/2026</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Đang tiến hành</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Sắp quá hạn</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Hà Thanh Tâm</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>088087</t>
+        </is>
+      </c>
+      <c r="Y5" s="2">
+        <v>46113</v>
+      </c>
+      <c r="Z5">
+        <v>1</v>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>AIO</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>KV1</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>PTO</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>GPTH</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NLMT</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Inverter</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>170301- ĐHG/KD/HDMBLĐ-2025/CNCTPTO-NKT</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>B2C</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Khách hàng cá nhân</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Lê Thị Hạnh</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0976373685</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Tiền Phong</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Hotline</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Sau bán</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Sự cố</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>Sản phẩm không sử dụng được / không hoạt động</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>Chị gửi yêu cầu cả tháng mà không có kt liên hệ</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>14:18 01/04/2026</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>14:18 02/04/2026</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Chưa thực hiện</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Sắp quá hạn</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Lê Trung Kiên</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>119420</t>
+        </is>
+      </c>
+      <c r="Y6" s="2">
+        <v>46113</v>
+      </c>
+      <c r="Z6">
+        <v>1</v>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>IOC</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>P.Triển khai</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>truongdv17</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>KV1</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>NAN</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>DVKT</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Home Service</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Bảo dưỡng Điều hòa treo tường (9.000BTU ÷ 12.000 BTU)</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>DH_B2C_NAN_1775021385791</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>B2C</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Khách hàng cá nhân</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Anhh Sơn</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0394561708</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>xóm đồng tâm</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Trước bán</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Khiếu nại</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>Liên hệ chậm</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>KH có đơn Bảo dưỡng Điều hòa treo tường theo lịch thì ngày 2.4 làm, nhưng vẫn chưa có kT liên hệ</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>08:00 02/04/2026</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>14:00 02/04/2026</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Chưa thực hiện</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Nguyễn Minh Linh</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>285776</t>
+        </is>
+      </c>
+      <c r="Y7" s="2">
+        <v>46114</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>IOC</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>KV3</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>HCM</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>GPTH</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NLMT</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Hệ thống NLMT</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>VCC_YCTX_HCM_39129780211356091</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>B2C</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Khách hàng cá nhân</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Chị Quỳnh</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0913239085</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Phường Thủ Đức, Thành phố Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Hotline</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Trước bán</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Khiếu nại</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>Liên hệ tư vấn chậm</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>KH có nhu cầu dùng NLMT , KH phản ánh chưa có nhân viên liên hệ tư vấn. YC liên hệ KH sớm</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>08:00 02/04/2026</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>09:00 03/04/2026</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Chưa thực hiện</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Hoàng Xuân Lượng</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>007573</t>
+        </is>
+      </c>
+      <c r="Y8" s="2">
+        <v>46114</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>IOC</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>P.KDNLMT</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>P.KDNLMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>KV1</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>HTH</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>DVKT</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Home Service</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Dịch vụ kiểm tra và thay thế máy nén - Điều hòa 9.000 ÷ 12.000 BTU</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>VCC_HS_HTH_1774973804481</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>B2C</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Khách hàng cá nhân</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Bùi Tuấn Anh</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0974014593</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>51 Phan Đình Phùng</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>VIP</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Trước bán</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Khiếu nại</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>Liên hệ chậm</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>KH đặt đơn từ 31.3, lịch hẹn làm là 1.4, nhưng chưa có ai liên hệ</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>16:29 01/04/2026</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>09:00 02/04/2026</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Chưa thực hiện</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Sắp quá hạn</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Nguyễn Quang Ngân</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>413580</t>
+        </is>
+      </c>
+      <c r="Y9" s="2">
+        <v>46113</v>
+      </c>
+      <c r="Z9">
+        <v>1</v>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>HS</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>KV1</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>QNH</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>DVKT</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Home Service</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Gói hỗ trợ kỹ thuật - Dịch vụ kiểm tra</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>VCC_HS_QNH_1772878620516</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>B2C</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Khách hàng cá nhân</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Pham Manh Hiep</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0982144616</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>số nhà 1qh tổ 52e khu 4b phường cao xanh tp hạ long tỉnh qn, Phường Hạ Long, Tỉnh Quảng Ninh</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Trước bán</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Khiếu nại</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>Liên hệ chậm</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>KH đặt dịch vụ trước cả tháng trời nhưng đến ngày làm hôm nay thì KT liên hệ bảo dời sang 1,2 tuần sau. KH cảm thấy dvu quá chán luôn.</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>15:53 01/04/2026</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>09:00 02/04/2026</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Đang tiến hành</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Sắp quá hạn</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Đào Minh Đức</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>290593</t>
+        </is>
+      </c>
+      <c r="Y10" s="2">
+        <v>46113</v>
+      </c>
+      <c r="Z10">
+        <v>1</v>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>HS</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>KV2</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>QTI</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>GPTH</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>M&amp;E</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Điều hòa</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>KHCN_TT.GPTH_QBH_1506880</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>B2C</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Khách hàng cá nhân</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Nguyễn Hữu Thành</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0971988556</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Đại Nam 1</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Hotline</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Sau bán</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Sự cố</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>Khách hàng báo qua hotline điều hòa bị lỗi. Kiểm tra vẫn còn hạn bảo hành</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>13:30 01/04/2026</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>13:30 02/04/2026</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Chưa thực hiện</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Sắp quá hạn</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Hoàng Mạnh Huy</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>064050</t>
+        </is>
+      </c>
+      <c r="Y11" s="2">
+        <v>46113</v>
+      </c>
+      <c r="Z11">
+        <v>1</v>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>AIO</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>P.Triển khai</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Sonln15</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>KV3</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
           <t>TNH</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Hệ thống NLMT</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Inverter</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_LAN_1530029</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>Lê Thị Lụa</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>0975020753</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>152 Hùng Vương, KP 4,Thị trấn Tân Thạnh,Huyện Tân Thạnh,Tỉnh Long An</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>Inverter không hoạt động</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
         <is>
           <t>1. KH đã báo CN
 2. KH phản ánh: Ivt bị lỗi ko lên màn hình, ko xả và nạp được
@@ -1031,1006 +2000,1006 @@
 - SĐT liên hệ và phản ánh: 0962608008 chồng của KH</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>08:20 01/04/2026</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>08:20 02/04/2026</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>Chưa thực hiện</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>Trong hạn</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Đang tiến hành</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Quá hạn</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
         <is>
           <t>Nguyễn Văn Hào</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>075543</t>
         </is>
       </c>
-      <c r="Y5" s="2">
+      <c r="Y12" s="2">
         <v>46113</v>
       </c>
-      <c r="Z5">
-        <v>0</v>
-      </c>
-      <c r="AA5" t="inlineStr">
+      <c r="Z12">
+        <v>1</v>
+      </c>
+      <c r="AA12" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>KV3</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>DNI</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>Tấm pin NLMT</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_DNI_1625162</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>Diamond</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>Lê Thị Hồng Phương</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>0918005760</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>Phường Long Bình, Tỉnh Đồng Nai</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="P13" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="R13" t="inlineStr">
         <is>
           <t>1. KH đã báo cn
 2. KH phản ánh: Hệ thống nlmt của KH bình ắc quy lưu trữ ko thấy lên ký điện và còn thấy kêu tít tít
 3. KH yêu cầu: KT qua kiểm tra thiết bị, hỗ trợ KH, khắc phục tình trạng này.</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>08:00 01/04/2026</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>09:00 02/04/2026</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>Chưa thực hiện</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>Trong hạn</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>Dương Quang Tuyên</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>071004</t>
-        </is>
-      </c>
-      <c r="Y6" s="2">
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Đang tiến hành</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Sắp quá hạn</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Bùi Đức Dương</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>083045</t>
+        </is>
+      </c>
+      <c r="Y13" s="2">
         <v>46113</v>
       </c>
-      <c r="Z6">
-        <v>0</v>
-      </c>
-      <c r="AA6" t="inlineStr">
+      <c r="Z13">
+        <v>1</v>
+      </c>
+      <c r="AA13" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>KV1</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>BNH</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>Tấm pin NLMT</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_BNH_1621181</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>Diamond</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>Phạm Khắc Hưng</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>0975777212</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>Bắc Đẩu</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="O14" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="P14" t="inlineStr">
         <is>
           <t>Hỗ trợ</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Q14" t="inlineStr">
         <is>
           <t>Hướng dẫn, hỗ trợ sử dụng sản phẩm</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="R14" t="inlineStr">
         <is>
           <t>1. KH đã báo cn
 2. KH phản ánh: Hệ thống nlmt của KH bị đọng lại nước ở trong
 3. KH yêu cầu: Qua kiểm tra thiết bị xem có ảnh hưởng gì tới thiết bị không.</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>17:23 31/03/2026</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>17:23 01/04/2026</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>Chưa thực hiện</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>Sắp quá hạn</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>16:45 03/04/2026</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Đang tiến hành</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
         <is>
           <t>Diệp Văn Đoàn</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="X14" t="inlineStr">
         <is>
           <t>284456</t>
         </is>
       </c>
-      <c r="Y7" s="2">
+      <c r="Y14" s="2">
         <v>46112</v>
       </c>
-      <c r="Z7">
-        <v>1</v>
-      </c>
-      <c r="AA7" t="inlineStr">
+      <c r="Z14">
+        <v>2</v>
+      </c>
+      <c r="AA14" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="15">
+      <c r="A15" t="inlineStr">
         <is>
           <t>KV3</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>VLG</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_TVH_1599327</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Silver</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>Châu Quốc Cường</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>0987195484</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>Cẩm Hương - Mỹ Hòa - Cầu Ngang - Trà Vinh</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>Nhân viên nội bộ VCC</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="O15" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="P15" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="Q15" t="inlineStr">
         <is>
           <t>Chất lượng, hiệu suất của sản phẩm/hệ thống thấp</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="R15" t="inlineStr">
         <is>
           <t>CN báo sự cố hộ KH
 1. KH phản ánh: Hiệu suất kém, sản lượng ít, 1 ngày 10-12kw mà hệ 5kw
 2. KH yêu cầu: Kiểm tra lại hiệu suất, khắc phục lại.</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>08:57 31/03/2026</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>11:40 03/04/2026</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>Trong hạn</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>Hứa Vũ Phong</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="X15" t="inlineStr">
         <is>
           <t>427079</t>
         </is>
       </c>
-      <c r="Y8" s="2">
+      <c r="Y15" s="2">
         <v>46112</v>
       </c>
-      <c r="Z8">
-        <v>1</v>
-      </c>
-      <c r="AA8" t="inlineStr">
+      <c r="Z15">
+        <v>2</v>
+      </c>
+      <c r="AA15" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>KV1</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>HNI</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>DVKT</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>Home Service</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>Gói hỗ trợ kỹ thuật - Dịch vụ kiểm tra</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>VCC_HS_HNI_1774581791644</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>Member</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>Chii Huệ</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>0389920628</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>514C14 Nguyễn Quý Đức Thanh Xuân</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>Facebook</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="O16" t="inlineStr">
         <is>
           <t>Trong bán</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="P16" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="Q16" t="inlineStr">
         <is>
           <t>Sau bảo dưỡng thiết bị bị hỏng</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="R16" t="inlineStr">
         <is>
           <t>KH phản ánh sau khi KT đến bảo dưỡng điều hòa vào ngày 28/03 thì hôm sau điều hòa không mở được, yêu cầu KT đến kiểm tra lại gấp</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>08:00 31/03/2026</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>09:00 01/04/2026</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>21:35 03/04/2026</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>Quá hạn</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
         <is>
           <t>Lê Duy Tuấn</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="X16" t="inlineStr">
         <is>
           <t>293859</t>
         </is>
       </c>
-      <c r="Y9" s="2">
+      <c r="Y16" s="2">
         <v>46112</v>
       </c>
-      <c r="Z9">
-        <v>1</v>
-      </c>
-      <c r="AA9" t="inlineStr">
+      <c r="Z16">
+        <v>2</v>
+      </c>
+      <c r="AA16" t="inlineStr">
         <is>
           <t>HS</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>KV1</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>BNH</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_BNH_1634096</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>Nguyễn Ngọc Ân</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>0988386838</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="L17" t="inlineStr">
         <is>
           <t>Xã Xuân Cẩm, Tỉnh Bắc Ninh</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="O17" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="P17" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="Q17" t="inlineStr">
         <is>
           <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="R17" t="inlineStr">
         <is>
           <t>1. KH chưa báo cn
 2. KH phản ánh: nhà KH có thêm ats của máy nổ, về nguyên tắc máy điện phải chạy nlmt, khi nlmt hết thì chạy máy nổ. Hiện tại thì khi mất điện ko chạy sang nlmt, và khi nlmt hết rồi vẫn ko thấy chạy máy nổ. 
 3. KH yêu cầu: Kiểm tra trước nội dung về ats của máy nổ và nlmt. Và khắc phục tình trạng ko sử dụng này của KH.</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>15:55 30/03/2026</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>18:50 01/04/2026</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>18:40 02/04/2026</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="V17" t="inlineStr">
         <is>
           <t>Sắp quá hạn</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>nguyễn văn Tuần</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>461581</t>
-        </is>
-      </c>
-      <c r="Y10" s="2">
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Phạm Văn Huy</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>408869</t>
+        </is>
+      </c>
+      <c r="Y17" s="2">
         <v>46111</v>
       </c>
-      <c r="Z10">
-        <v>2</v>
-      </c>
-      <c r="AA10" t="inlineStr">
+      <c r="Z17">
+        <v>3</v>
+      </c>
+      <c r="AA17" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>KV1</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>NAN</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>CNTT</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>Cáp quang</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>KHDN_TT.VHKT_NAN_0989441</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>B2B</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>Khách hàng doanh nghiệp</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>CÔNG TY TNHH MAVIN ANH SƠN</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>0983985357</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t>Khu B - KCN Nam Cấm</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="O18" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="P18" t="inlineStr">
         <is>
           <t>Hỗ trợ</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="Q18" t="inlineStr">
         <is>
           <t>Thủ tục/giấy tờ/ Hóa đơn/ Hồ sơ lắp đặt</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="R18" t="inlineStr">
         <is>
           <t>Hóa đơn của KHDN bị mất nên cần xin lại hóa đơn ở HĐ này.</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>10:00 30/03/2026</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="T18" t="inlineStr">
         <is>
           <t>10:00 31/03/2026</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="U18" t="inlineStr">
         <is>
           <t>Chưa thực hiện</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="V18" t="inlineStr">
         <is>
           <t>Quá hạn</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>Nguyễn Quốc Hùng</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="X18" t="inlineStr">
         <is>
           <t>416898</t>
         </is>
       </c>
-      <c r="Y11" s="2">
+      <c r="Y18" s="2">
         <v>46111</v>
       </c>
-      <c r="Z11">
-        <v>2</v>
-      </c>
-      <c r="AA11" t="inlineStr">
+      <c r="Z18">
+        <v>3</v>
+      </c>
+      <c r="AA18" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AB18" t="inlineStr">
         <is>
           <t>P.Triển khai</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
+      <c r="AC18" t="inlineStr">
         <is>
           <t>Sonln15</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>KV1</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>HNI</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_HNI_1515521</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>Diamond</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>Anh Quang</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>0903442166</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="L19" t="inlineStr">
         <is>
           <t>Phường Ô Chợ Dừa, Thành phố Hà Nội</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t>Nhân viên nội bộ VCC</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="N19" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="O19" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="P19" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="Q19" t="inlineStr">
         <is>
           <t>Không kết nối được app/Wifi và không theo dõi được hiệu suất</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="R19" t="inlineStr">
         <is>
           <t>CN báo sự cố hộ KH
 1. KH phản ánh: Mất kết nối ko vào được app theo dõi, ko kết nối được ivt
@@ -2038,1580 +3007,1296 @@
 ***SĐT liên hệ: 0982233886, Anh Dũng - con của KH</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t>10:32 01/04/2026</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="T19" t="inlineStr">
         <is>
           <t>10:32 02/04/2026</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>Chưa thực hiện</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>Trong hạn</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>Lê Duy Tuấn</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>293859</t>
-        </is>
-      </c>
-      <c r="Y12" s="2">
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Sắp quá hạn</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Đặng Văn Lực</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>437013</t>
+        </is>
+      </c>
+      <c r="Y19" s="2">
         <v>46113</v>
       </c>
-      <c r="Z12">
-        <v>0</v>
-      </c>
-      <c r="AA12" t="inlineStr">
+      <c r="Z19">
+        <v>1</v>
+      </c>
+      <c r="AA19" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>KV2</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>HUE</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>KV3</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>DTP</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Hệ thống NLMT</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>KHCN_NLMT_TTH_0240288</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Inverter</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>KHCN_TT.GPTH_DTP_1618243</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Member</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Diamond</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>Nguyễn Thành An</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>0983826353</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>135/2 Bà Triệu, Phường Xuân Phú, Thành phố Huế, Tỉnh Thừa Thiên Huế</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>Hotline</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Nguyễn Thị Kim Dung</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>0946142525</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Ấp Tân Dân</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>Nhân viên nội bộ VCC</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="O20" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="P20" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="Q20" t="inlineStr">
         <is>
           <t>Thiết bị vỡ, hỏng, chập cháy</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>1. KH đã báo cn
-2. KH phản ánh: Tụ điện bị chập chờn tín hiệu xong có tiếng xoẹt xoẹt kêu to, hiện tại thì KH phải đi ngắt cầu dao.
-3. KH yêu cầu: Đến kiểm tra thiết bị và khắc phục tình trạng này gấp, KH đang cảm thấy ko an toàn.</t>
-        </is>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>08:28 01/04/2026</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>08:28 02/04/2026</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>Chưa thực hiện</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>Trong hạn</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>Đặng Hải Quan</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>192135</t>
-        </is>
-      </c>
-      <c r="Y13" s="2">
-        <v>46113</v>
-      </c>
-      <c r="Z13">
-        <v>0</v>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>AIO</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>KV3</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>DTP</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>GPTH</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>NLMT</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Inverter</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>KHCN_TT.GPTH_DTP_1618243</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>B2C</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Diamond</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>Khách hàng cá nhân</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>Nguyễn Thị Kim Dung</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>0946142525</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>Ấp Tân Dân</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>Nhân viên nội bộ VCC</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>Bình thường</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>Sau bán</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>Sự cố</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>Thiết bị vỡ, hỏng, chập cháy</t>
-        </is>
-      </c>
-      <c r="R14" t="inlineStr">
+      <c r="R20" t="inlineStr">
         <is>
           <t>ATS chuyển nguồn thiết bị hỏng.
 KH đã được hỗ trợ.</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="S20" t="inlineStr">
         <is>
           <t>09:49 31/03/2026</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="T20" t="inlineStr">
         <is>
           <t>17:00 15/04/2026</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="U20" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr">
+      <c r="V20" t="inlineStr">
         <is>
           <t>Trong hạn</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>Lưu Văn Liêm</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
+      <c r="X20" t="inlineStr">
         <is>
           <t>324208</t>
         </is>
       </c>
-      <c r="Y14" s="2">
+      <c r="Y20" s="2">
         <v>46112</v>
       </c>
-      <c r="Z14">
-        <v>1</v>
-      </c>
-      <c r="AA14" t="inlineStr">
+      <c r="Z20">
+        <v>2</v>
+      </c>
+      <c r="AA20" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+    <row r="21">
+      <c r="A21" t="inlineStr">
         <is>
           <t>KV1</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>NAN</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>KHCN_PINNLMT_NAN_0334667</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>Lê Trung An</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t>0865878212</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="L21" t="inlineStr">
         <is>
           <t>xóm 9, Xã Đại Sơn, Huyện Đô Lương, Tỉnh Nghệ An</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="N21" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr">
+      <c r="O21" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr">
+      <c r="P21" t="inlineStr">
         <is>
           <t>Hỗ trợ</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr">
+      <c r="Q21" t="inlineStr">
         <is>
           <t>Hướng dẫn, hỗ trợ sử dụng sản phẩm</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="R21" t="inlineStr">
         <is>
           <t>1. KH đã báo cn
 2. KH yêu cầu: Muốn hiện thông số trên app từ ivt qua điện lưới với điện dùng cho GĐ để báo điện lực.</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>11:30 30/03/2026</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="T21" t="inlineStr">
         <is>
           <t>19:10 10/04/2026</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="U21" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr">
+      <c r="V21" t="inlineStr">
         <is>
           <t>Trong hạn</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>Nguyễn Minh Linh</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
+      <c r="X21" t="inlineStr">
         <is>
           <t>285776</t>
         </is>
       </c>
-      <c r="Y15" s="2">
+      <c r="Y21" s="2">
         <v>46111</v>
       </c>
-      <c r="Z15">
-        <v>2</v>
-      </c>
-      <c r="AA15" t="inlineStr">
+      <c r="Z21">
+        <v>3</v>
+      </c>
+      <c r="AA21" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+    <row r="22">
+      <c r="A22" t="inlineStr">
         <is>
           <t>KV1</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>HNI</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>KHDN_TT.GPTH_HNI_1665498</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>B2B</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>Diamond</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>Khách hàng doanh nghiệp</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>CÔNG TY CỔ PHẦN TUẤN CƯỜNG</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t>0914880646</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="L22" t="inlineStr">
         <is>
           <t>Thôn 7</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t>Nhân viên nội bộ VCC</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
+      <c r="N22" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr">
+      <c r="O22" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr">
+      <c r="P22" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr">
+      <c r="Q22" t="inlineStr">
         <is>
           <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="R22" t="inlineStr">
         <is>
           <t>CN 0981168696  báo sự cố hộ KH
 1. KH phản ánh: Lỗi ivt, mất điện lưới hiện tại pin ko xả được
 2. KH yêu cầu: KHDN là xưởng sản xuất cần qua hỗ trợ, kiểm tra, khắc phục gấp cho KH.</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="S22" t="inlineStr">
         <is>
           <t>09:00 30/03/2026</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
+      <c r="T22" t="inlineStr">
         <is>
           <t>18:45 06/04/2026</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="U22" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
+      <c r="V22" t="inlineStr">
         <is>
           <t>Trong hạn</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>Lê Duy Tuấn</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
+      <c r="X22" t="inlineStr">
         <is>
           <t>293859</t>
         </is>
       </c>
-      <c r="Y16" s="2">
+      <c r="Y22" s="2">
         <v>46111</v>
       </c>
-      <c r="Z16">
-        <v>2</v>
-      </c>
-      <c r="AA16" t="inlineStr">
+      <c r="Z22">
+        <v>3</v>
+      </c>
+      <c r="AA22" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
+    <row r="23">
+      <c r="A23" t="inlineStr">
         <is>
           <t>KV1</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>BNH</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_BGG_1601525</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>Diamond</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t>Hoàng Văn Hoạt</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="K23" t="inlineStr">
         <is>
           <t>0344334808</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="L23" t="inlineStr">
         <is>
           <t>Thán</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
+      <c r="N23" t="inlineStr">
         <is>
           <t>Hot</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr">
+      <c r="O23" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr">
+      <c r="P23" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr">
+      <c r="Q23" t="inlineStr">
         <is>
           <t>Chất lượng, hiệu suất của sản phẩm/hệ thống thấp</t>
         </is>
       </c>
-      <c r="R17" t="inlineStr">
+      <c r="R23" t="inlineStr">
         <is>
           <t>1. KH đã báo kỹ thuật Thành 0977357868 nhưng chưa được hỗ trợ
 2. KH phản ánh lắp điện NLMT nhưng tiền điện vẫn cao
 3. KH yêu cầu kỹ thuật qua hỗ trợ xử lý</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="S23" t="inlineStr">
         <is>
           <t>08:00 30/03/2026</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
+      <c r="T23" t="inlineStr">
         <is>
           <t>09:00 05/04/2026</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="U23" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr">
+      <c r="V23" t="inlineStr">
         <is>
           <t>Trong hạn</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
+      <c r="W23" t="inlineStr">
         <is>
           <t>Nguyễn Thị Nhị</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
+      <c r="X23" t="inlineStr">
         <is>
           <t>239095</t>
         </is>
       </c>
-      <c r="Y17" s="2">
+      <c r="Y23" s="2">
         <v>46111</v>
       </c>
-      <c r="Z17">
-        <v>2</v>
-      </c>
-      <c r="AA17" t="inlineStr">
+      <c r="Z23">
+        <v>3</v>
+      </c>
+      <c r="AA23" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+    <row r="24">
+      <c r="A24" t="inlineStr">
         <is>
           <t>KV1</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>HPG</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>YCKS_HDG_TLS/0120467</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t>Diamond</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>Ngô Hữu Thế</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="K24" t="inlineStr">
         <is>
           <t>0984379375</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="L24" t="inlineStr">
         <is>
           <t>494 Phố Việt Hòa, Tp Hải Phòng</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
+      <c r="N24" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr">
+      <c r="O24" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr">
+      <c r="P24" t="inlineStr">
         <is>
           <t>Hỗ trợ</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr">
+      <c r="Q24" t="inlineStr">
         <is>
           <t>Thủ tục/giấy tờ/ Hóa đơn/ Hồ sơ lắp đặt</t>
         </is>
       </c>
-      <c r="R18" t="inlineStr">
+      <c r="R24" t="inlineStr">
         <is>
           <t>1. KH chưa báo chi nhánh
 2. KH phản ánh sơ đồ đấu nối điện bị sai
 3. KH yêu cầu chi nhánh gửi lại 1 bản hợp đồng sơ đồ đấu nối để KH kiểm tra</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="S24" t="inlineStr">
         <is>
           <t>08:00 30/03/2026</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
+      <c r="T24" t="inlineStr">
         <is>
           <t>08:15 05/04/2026</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="U24" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
+      <c r="V24" t="inlineStr">
         <is>
           <t>Trong hạn</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
+      <c r="W24" t="inlineStr">
         <is>
           <t>Phạm Quân Khu</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
+      <c r="X24" t="inlineStr">
         <is>
           <t>272645</t>
         </is>
       </c>
-      <c r="Y18" s="2">
+      <c r="Y24" s="2">
         <v>46111</v>
       </c>
-      <c r="Z18">
-        <v>2</v>
-      </c>
-      <c r="AA18" t="inlineStr">
+      <c r="Z24">
+        <v>3</v>
+      </c>
+      <c r="AA24" t="inlineStr">
         <is>
           <t>IOC</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
+      <c r="AB24" t="inlineStr">
         <is>
           <t>P.Triển khai</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
+      <c r="AC24" t="inlineStr">
         <is>
           <t>vinhvv4</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>KV1</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>NAN</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_NAN_1574225</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>Diamond</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>Nguyên Văn Tú</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t>0868081789</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="L25" t="inlineStr">
         <is>
           <t>1,Xã Yên Sơn,Huyện Đô Lương,Tỉnh Nghệ An</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr">
+      <c r="N25" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr">
+      <c r="O25" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr">
+      <c r="P25" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr">
+      <c r="Q25" t="inlineStr">
         <is>
           <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
-      <c r="R19" t="inlineStr">
+      <c r="R25" t="inlineStr">
         <is>
           <t>1. KH đã báo giám đốc chi nhánh nhưng chưa được xử lý dứt điểm
 2. KH phản ánh NLMT bị hỏng không sử dụng được
 3. KH yêu cầu kỹ thuật qua hỗ trợ thay aptomat to hơn</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="S25" t="inlineStr">
         <is>
           <t>08:00 30/03/2026</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
+      <c r="T25" t="inlineStr">
         <is>
           <t>20:10 15/04/2026</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="U25" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
+      <c r="V25" t="inlineStr">
         <is>
           <t>Trong hạn</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
+      <c r="W25" t="inlineStr">
         <is>
           <t>Nguyễn Minh Linh</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
+      <c r="X25" t="inlineStr">
         <is>
           <t>285776</t>
         </is>
       </c>
-      <c r="Y19" s="2">
+      <c r="Y25" s="2">
         <v>46111</v>
       </c>
-      <c r="Z19">
-        <v>2</v>
-      </c>
-      <c r="AA19" t="inlineStr">
+      <c r="Z25">
+        <v>3</v>
+      </c>
+      <c r="AA25" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+    <row r="26">
+      <c r="A26" t="inlineStr">
         <is>
           <t>KV2</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>DNG</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>Acquy lưu trữ</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_QNM_1510130</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t>Lê Phước Danh</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
+      <c r="K26" t="inlineStr">
         <is>
           <t>0355557906</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="L26" t="inlineStr">
         <is>
           <t>Thôn Pà Dá,Xã Cà Dy,Huyện Nam Giang,Tỉnh Quảng Nam</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t>Nhân viên nội bộ VCC</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr">
+      <c r="N26" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr">
+      <c r="O26" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr">
+      <c r="P26" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr">
+      <c r="Q26" t="inlineStr">
         <is>
           <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
-      <c r="R20" t="inlineStr">
+      <c r="R26" t="inlineStr">
         <is>
           <t>Lỗi pin ko lưu</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="S26" t="inlineStr">
         <is>
           <t>10:43 01/04/2026</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
+      <c r="T26" t="inlineStr">
         <is>
           <t>10:43 02/04/2026</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="U26" t="inlineStr">
         <is>
           <t>Chưa thực hiện</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>Trong hạn</t>
-        </is>
-      </c>
-      <c r="W20" t="inlineStr">
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Sắp quá hạn</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
         <is>
           <t>Nguyễn Bá Châu</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr">
+      <c r="X26" t="inlineStr">
         <is>
           <t>118290</t>
         </is>
       </c>
-      <c r="Y20" s="2">
+      <c r="Y26" s="2">
         <v>46113</v>
       </c>
-      <c r="Z20">
-        <v>0</v>
-      </c>
-      <c r="AA20" t="inlineStr">
+      <c r="Z26">
+        <v>1</v>
+      </c>
+      <c r="AA26" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
+    <row r="27">
+      <c r="A27" t="inlineStr">
         <is>
           <t>KV1</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>HNI</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_HNI_1641827</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t>Diamond</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="J27" t="inlineStr">
         <is>
           <t>Nguyễn Trọng Đạt</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="K27" t="inlineStr">
         <is>
           <t>0904113488</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="L27" t="inlineStr">
         <is>
           <t>36 Ngõ 104 Thúy Lĩnh, Phường Hoàng Mai, Thành phố Hà Nội</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr">
+      <c r="N27" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr">
+      <c r="O27" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr">
+      <c r="P27" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>Sản phẩm không sử dụng được / không hoạt động</t>
-        </is>
-      </c>
-      <c r="R21" t="inlineStr">
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
         <is>
           <t>KH chưa báo CN
  KH đang sd NLMT, nhưng hiện tại hệ thống ko hoạt động, ko phát được điện
 YC KT qua kiểm tra và xử lý</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="S27" t="inlineStr">
         <is>
           <t>08:00 30/03/2026</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>23:55 05/04/2026</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>09:00 06/04/2026</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
+      <c r="V27" t="inlineStr">
         <is>
           <t>Trong hạn</t>
         </is>
       </c>
-      <c r="W21" t="inlineStr">
+      <c r="W27" t="inlineStr">
         <is>
           <t>Nguyễn Hoàng Minh</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
+      <c r="X27" t="inlineStr">
         <is>
           <t>292404</t>
         </is>
       </c>
-      <c r="Y21" s="2">
+      <c r="Y27" s="2">
         <v>46111</v>
       </c>
-      <c r="Z21">
-        <v>2</v>
-      </c>
-      <c r="AA21" t="inlineStr">
+      <c r="Z27">
+        <v>3</v>
+      </c>
+      <c r="AA27" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>KV3</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>CTO</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>KV2</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>HUE</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Hệ thống NLMT</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>KHDN_TT.GPTH_CTO_1417803</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Tấm pin NLMT</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>KHDN_TT.GPTH_TTH_1626383</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
         <is>
           <t>B2B</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Diamond</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
         <is>
           <t>Khách hàng doanh nghiệp</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>công ty TNHH quảng cáo đăng nguyễn</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>0909393390</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>ô môn</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH SẢN XUẤT THƯƠNG MẠI VIỆT PHÚ HƯNG</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>0985005322</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>19 Trưng Nữ Vương</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>Hot</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>Hỗ trợ</t>
-        </is>
-      </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>Hỗ trợ lắp đặt</t>
-        </is>
-      </c>
-      <c r="R22" t="inlineStr">
-        <is>
-          <t>KH chưa báo CN
-HIện tại KH cần di dời thiết bị cách đấy khoảng 2-3m , nhờ KT qua hỗ trợ</t>
-        </is>
-      </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>08:00 30/03/2026</t>
-        </is>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>17:30 01/04/2026</t>
-        </is>
-      </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>Đang tiến hành</t>
-        </is>
-      </c>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>Sắp quá hạn</t>
-        </is>
-      </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>Nguyễn Kiến Quân</t>
-        </is>
-      </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>007344</t>
-        </is>
-      </c>
-      <c r="Y22" s="2">
-        <v>46111</v>
-      </c>
-      <c r="Z22">
-        <v>2</v>
-      </c>
-      <c r="AA22" t="inlineStr">
-        <is>
-          <t>AIO</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>KV2</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>HUE</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>GPTH</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>NLMT</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Tấm pin NLMT</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>KHDN_TT.GPTH_TTH_1626383</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>B2B</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Diamond</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>Khách hàng doanh nghiệp</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>CÔNG TY TNHH SẢN XUẤT THƯƠNG MẠI VIỆT PHÚ HƯNG</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>0985005322</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>19 Trưng Nữ Vương</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>Hotline</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>Bình thường</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>Sau bán</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
+      <c r="P28" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>Hiệu suất sản phẩm kém</t>
-        </is>
-      </c>
-      <c r="R23" t="inlineStr">
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>Chất lượng, hiệu suất của sản phẩm/hệ thống thấp</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
         <is>
           <t>KH chưa báo CN
 KH đang sử dụng tấm PIN NLMT của VCC, 
@@ -3619,580 +4304,725 @@
 KH YC KT qua kiểm tra và xử lý cho KH gấp</t>
         </is>
       </c>
-      <c r="S23" t="inlineStr">
+      <c r="S28" t="inlineStr">
         <is>
           <t>08:00 30/03/2026</t>
         </is>
       </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>17:50 01/04/2026</t>
-        </is>
-      </c>
-      <c r="U23" t="inlineStr">
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>09:00 06/04/2026</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V23" t="inlineStr">
-        <is>
-          <t>Sắp quá hạn</t>
-        </is>
-      </c>
-      <c r="W23" t="inlineStr">
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
         <is>
           <t>Lê Văn Đồng</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
+      <c r="X28" t="inlineStr">
         <is>
           <t>422252</t>
         </is>
       </c>
-      <c r="Y23" s="2">
+      <c r="Y28" s="2">
         <v>46111</v>
       </c>
-      <c r="Z23">
-        <v>2</v>
-      </c>
-      <c r="AA23" t="inlineStr">
+      <c r="Z28">
+        <v>3</v>
+      </c>
+      <c r="AA28" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>KV1</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>HNI</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>GPTH</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NLMT</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Hệ thống NLMT</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>KHCN_TT.GPTH_HNI_1631868</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>B2C</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Diamond</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Khách hàng cá nhân</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Lê Văn Vĩnh</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>0948519572</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>SN 7A ngõ 564/12 đường Nguyễn Văn Cừ</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>Nhân viên nội bộ VCC</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>Sau bán</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Sự cố</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>CN báo hộ SDT: 985792828
+KH đang sd NLMT nhưng hiện tại thiết bị ko sản sinh ra điện
+YC KT qua kiểm tra và xử lý cho KH</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>08:00 30/03/2026</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>17:00 02/04/2026</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Đang tiến hành</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Lê Hồng Sơn</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>462955</t>
+        </is>
+      </c>
+      <c r="Y29" s="2">
+        <v>46111</v>
+      </c>
+      <c r="Z29">
+        <v>3</v>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>AIO</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
         <is>
           <t>KV3</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>HCM</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>KHDN_TT.GPTH_BDG_1495422</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>B2B</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t>Diamond</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t>Khách hàng doanh nghiệp</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
+      <c r="J30" t="inlineStr">
         <is>
           <t>CÔNG TY TNHH THƯƠNG MẠI VẬN TẢI BẢO LONG PHÁT</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
+      <c r="K30" t="inlineStr">
         <is>
           <t>0918236379</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="L30" t="inlineStr">
         <is>
           <t>Số 617, đường ĐT 743B, khu phố Đông Tân</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr">
+      <c r="M30" t="inlineStr">
         <is>
           <t>Zalo</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr">
+      <c r="N30" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr">
+      <c r="O30" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P24" t="inlineStr">
+      <c r="P30" t="inlineStr">
         <is>
           <t>Hỗ trợ</t>
         </is>
       </c>
-      <c r="Q24" t="inlineStr">
+      <c r="Q30" t="inlineStr">
         <is>
           <t>Cài đặt hệ thống (APP/Mật khẩu)</t>
         </is>
       </c>
-      <c r="R24" t="inlineStr">
+      <c r="R30" t="inlineStr">
         <is>
           <t>1. KH báo cn người hỗ trợ trước nhưng ko liên hệ được
 2. KH phản ánh: KH kết nối được app báo lỗi ngoại tuyến
 3. KH yêu cầu: Hỗ trợ, hướng dẫn KH sử dụng, KH hay bị gặp vấn đề này nhiều hỗ trợ KH dứt điểm giúp.</t>
         </is>
       </c>
-      <c r="S24" t="inlineStr">
+      <c r="S30" t="inlineStr">
         <is>
           <t>16:08 26/03/2026</t>
         </is>
       </c>
-      <c r="T24" t="inlineStr">
+      <c r="T30" t="inlineStr">
         <is>
           <t>09:00 05/04/2026</t>
         </is>
       </c>
-      <c r="U24" t="inlineStr">
+      <c r="U30" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V24" t="inlineStr">
+      <c r="V30" t="inlineStr">
         <is>
           <t>Trong hạn</t>
         </is>
       </c>
-      <c r="W24" t="inlineStr">
+      <c r="W30" t="inlineStr">
         <is>
           <t>Trần Văn Thắng</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr">
+      <c r="X30" t="inlineStr">
         <is>
           <t>470289</t>
         </is>
       </c>
-      <c r="Y24" s="2">
+      <c r="Y30" s="2">
         <v>46107</v>
       </c>
-      <c r="Z24">
-        <v>6</v>
-      </c>
-      <c r="AA24" t="inlineStr">
+      <c r="Z30">
+        <v>7</v>
+      </c>
+      <c r="AA30" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+    <row r="31">
+      <c r="A31" t="inlineStr">
         <is>
           <t>KV1</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>HYN</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_HDG_1304417</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="H31" t="inlineStr">
         <is>
           <t>Diamond</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="J31" t="inlineStr">
         <is>
           <t>Nguyễn Thị Hồng Khánh</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
+      <c r="K31" t="inlineStr">
         <is>
           <t>0377883716</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="L31" t="inlineStr">
         <is>
           <t>Thôn Ngọc Loan,Xã Tân Quang,Huyện Văn Lâm,Tỉnh Hưng Yên</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr">
+      <c r="M31" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr">
+      <c r="N31" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr">
+      <c r="O31" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P25" t="inlineStr">
+      <c r="P31" t="inlineStr">
         <is>
           <t>Hỗ trợ</t>
         </is>
       </c>
-      <c r="Q25" t="inlineStr">
+      <c r="Q31" t="inlineStr">
         <is>
           <t>Hướng dẫn, hỗ trợ sử dụng sản phẩm</t>
         </is>
       </c>
-      <c r="R25" t="inlineStr">
+      <c r="R31" t="inlineStr">
         <is>
           <t>KH chưa báo CN
 KH yêu cầu NVKT qua lại thiết bị inverter của KH 
 Số liên hệ:</t>
         </is>
       </c>
-      <c r="S25" t="inlineStr">
+      <c r="S31" t="inlineStr">
         <is>
           <t>08:00 26/03/2026</t>
         </is>
       </c>
-      <c r="T25" t="inlineStr">
+      <c r="T31" t="inlineStr">
         <is>
           <t>17:25 02/04/2026</t>
         </is>
       </c>
-      <c r="U25" t="inlineStr">
+      <c r="U31" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V25" t="inlineStr">
-        <is>
-          <t>Sắp quá hạn</t>
-        </is>
-      </c>
-      <c r="W25" t="inlineStr">
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
         <is>
           <t>Hoàng Văn Phong</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr">
+      <c r="X31" t="inlineStr">
         <is>
           <t>291011</t>
         </is>
       </c>
-      <c r="Y25" s="2">
+      <c r="Y31" s="2">
         <v>46107</v>
       </c>
-      <c r="Z25">
-        <v>6</v>
-      </c>
-      <c r="AA25" t="inlineStr">
+      <c r="Z31">
+        <v>7</v>
+      </c>
+      <c r="AA31" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
+    <row r="32">
+      <c r="A32" t="inlineStr">
         <is>
           <t>KV2</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>KHA</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_KHA_1631515</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="H32" t="inlineStr">
         <is>
           <t>Diamond</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
+      <c r="J32" t="inlineStr">
         <is>
           <t>Phạm Hải Triều</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
+      <c r="K32" t="inlineStr">
         <is>
           <t>0903576559</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="L32" t="inlineStr">
         <is>
           <t>Phường Nha Trang, Tỉnh Khánh Hòa</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr">
+      <c r="M32" t="inlineStr">
         <is>
           <t>Nhân viên nội bộ VCC</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr">
+      <c r="N32" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr">
+      <c r="O32" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P26" t="inlineStr">
+      <c r="P32" t="inlineStr">
         <is>
           <t>Bảo hành</t>
         </is>
       </c>
-      <c r="Q26" t="inlineStr">
+      <c r="Q32" t="inlineStr">
         <is>
           <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
-      <c r="R26" t="inlineStr">
+      <c r="R32" t="inlineStr">
         <is>
           <t>CN báo sự cố hộ KH
 1. KH phản ánh: Ắc quy, pin gần như ko hoạt động. Chỉ có bám tải, ivt hoạt động
 2. KH yêu cầu: Qua hỗ trợ, kiểm tra, xử lý sớm cho KH.</t>
         </is>
       </c>
-      <c r="S26" t="inlineStr">
+      <c r="S32" t="inlineStr">
         <is>
           <t>08:00 26/03/2026</t>
         </is>
       </c>
-      <c r="T26" t="inlineStr">
+      <c r="T32" t="inlineStr">
         <is>
           <t>08:19 16/04/2026</t>
         </is>
       </c>
-      <c r="U26" t="inlineStr">
+      <c r="U32" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V26" t="inlineStr">
+      <c r="V32" t="inlineStr">
         <is>
           <t>Trong hạn</t>
         </is>
       </c>
-      <c r="W26" t="inlineStr">
+      <c r="W32" t="inlineStr">
         <is>
           <t>Phan Trọng Nghĩa</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr">
+      <c r="X32" t="inlineStr">
         <is>
           <t>234935</t>
         </is>
       </c>
-      <c r="Y26" s="2">
+      <c r="Y32" s="2">
         <v>46107</v>
       </c>
-      <c r="Z26">
-        <v>6</v>
-      </c>
-      <c r="AA26" t="inlineStr">
+      <c r="Z32">
+        <v>7</v>
+      </c>
+      <c r="AA32" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
+    <row r="33">
+      <c r="A33" t="inlineStr">
         <is>
           <t>KV1</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>HNI</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>KHDN_TT.GPTH_HNI_1646163</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t>B2B</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="H33" t="inlineStr">
         <is>
           <t>Diamond</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="I33" t="inlineStr">
         <is>
           <t>Khách hàng doanh nghiệp</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
+      <c r="J33" t="inlineStr">
         <is>
           <t>Công Ty Tnhh Đầu Tư Xây Dựng Và Thương Mại Triệu Phúc</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
+      <c r="K33" t="inlineStr">
         <is>
           <t>0973721368</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
+      <c r="L33" t="inlineStr">
         <is>
           <t>Triệu Xuyên, Long xuyên</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr">
+      <c r="M33" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr">
+      <c r="N33" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O27" t="inlineStr">
+      <c r="O33" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P27" t="inlineStr">
+      <c r="P33" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q27" t="inlineStr">
+      <c r="Q33" t="inlineStr">
         <is>
           <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
-      <c r="R27" t="inlineStr">
+      <c r="R33" t="inlineStr">
         <is>
           <t>1. KH đã báo cn a Long gđ kỹ thuật, a Dương Đăng Minh chủ ký HĐ, a Vương lắp đặt.
 2. KH phản ánh: Bị nhảy áp liên tục 1 tháng phải nhảy 20 ngày rơi vào khoảng 2h đêm và 12h trưa ban ngày, và chập tối lúc GĐ đang vào sinh hoạt. CN nhiều lần xuống ktra và kiến nghị nhưng có câu trả lời KH ko được hài lòng lắm. Đặc biệt là a Long GĐ KT có thái độ là đổ cho GĐ tắt áp, KH bức xúc vì KH bỏ đồng tiền ra mà lại đổ lỗi cho nhà KH. KH cũng báo với a Dương Đăng Minh, a Minh cũng bảo là để cháu bảo ae xuống thế nọ thế kia khất để ra giêng để sửa mà giờ hết tháng rồi vẫn ko thấy đâu.
@@ -4200,290 +5030,290 @@
 ***SĐT liên hệ: 0945268772, chú Bồng</t>
         </is>
       </c>
-      <c r="S27" t="inlineStr">
+      <c r="S33" t="inlineStr">
         <is>
           <t>14:58 25/03/2026</t>
         </is>
       </c>
-      <c r="T27" t="inlineStr">
+      <c r="T33" t="inlineStr">
         <is>
           <t>23:00 06/04/2026</t>
         </is>
       </c>
-      <c r="U27" t="inlineStr">
+      <c r="U33" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V27" t="inlineStr">
+      <c r="V33" t="inlineStr">
         <is>
           <t>Trong hạn</t>
         </is>
       </c>
-      <c r="W27" t="inlineStr">
+      <c r="W33" t="inlineStr">
         <is>
           <t>Lê Duy Tuấn</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr">
+      <c r="X33" t="inlineStr">
         <is>
           <t>293859</t>
         </is>
       </c>
-      <c r="Y27" s="2">
+      <c r="Y33" s="2">
         <v>46106</v>
       </c>
-      <c r="Z27">
-        <v>7</v>
-      </c>
-      <c r="AA27" t="inlineStr">
+      <c r="Z33">
+        <v>8</v>
+      </c>
+      <c r="AA33" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
+    <row r="34">
+      <c r="A34" t="inlineStr">
         <is>
           <t>KV1</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>BNH</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_BNH_1600729</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="H34" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
+      <c r="J34" t="inlineStr">
         <is>
           <t>Nguyễn Khương</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
+      <c r="K34" t="inlineStr">
         <is>
           <t>0977113014</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
+      <c r="L34" t="inlineStr">
         <is>
           <t>Xã Tân Chi, Tỉnh Bắc Ninh</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr">
+      <c r="M34" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr">
+      <c r="N34" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr">
+      <c r="O34" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P28" t="inlineStr">
+      <c r="P34" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q28" t="inlineStr">
+      <c r="Q34" t="inlineStr">
         <is>
           <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
-      <c r="R28" t="inlineStr">
+      <c r="R34" t="inlineStr">
         <is>
           <t>1. KH đã báo cn nhưng bạn nv kinh doanh a Vượng chuyển công tác nên chuyển cho a Phong, a Phong lại chuyển công tác cho số người mới nhưng chưa thấy.
 2. KH phản ánh: Biểu đồ biến tần tăng giảm đột biến, sụt pin về 0,pv về 0, tất cả đều về 0, thi thoảng còn bị mất điện. Hôm vừa rồi đầu xuân vào app báo thấy mất kết nối điện lưới trong khi nhà xung quanh vẫn có, sau khi xem tbao ở trên app lại ko có bất kỳ tbao nào về biến tần bị ngắt hay gì cả. KH Kbt có ai can thiệp vào app không
 3. KH yêu cầu: Kiểm tra biến tần cho KH, đã yêu cầu hãng xử lý rất nhiều lần rồi, nhưng giờ vẫn có tình trạng gặp lỗi. Ngoài ra KH yêu cầu là xử lý triệt để cho KH vì sắp tới mùa hè nó lên 3,4kw bị nhảy mà giờ còn kh thấy có tbao trên app.</t>
         </is>
       </c>
-      <c r="S28" t="inlineStr">
+      <c r="S34" t="inlineStr">
         <is>
           <t>09:20 25/03/2026</t>
         </is>
       </c>
-      <c r="T28" t="inlineStr">
+      <c r="T34" t="inlineStr">
         <is>
           <t>18:30 30/03/2026</t>
         </is>
       </c>
-      <c r="U28" t="inlineStr">
+      <c r="U34" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V28" t="inlineStr">
+      <c r="V34" t="inlineStr">
         <is>
           <t>Quá hạn</t>
         </is>
       </c>
-      <c r="W28" t="inlineStr">
+      <c r="W34" t="inlineStr">
         <is>
           <t>nguyễn văn Tuần</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr">
+      <c r="X34" t="inlineStr">
         <is>
           <t>461581</t>
         </is>
       </c>
-      <c r="Y28" s="2">
+      <c r="Y34" s="2">
         <v>46106</v>
       </c>
-      <c r="Z28">
-        <v>7</v>
-      </c>
-      <c r="AA28" t="inlineStr">
+      <c r="Z34">
+        <v>8</v>
+      </c>
+      <c r="AA34" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
+    <row r="35">
+      <c r="A35" t="inlineStr">
         <is>
           <t>KV1</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>PTO</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E35" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="F35" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_VPC_1503902</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="H35" t="inlineStr">
         <is>
           <t>Diamond</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
+      <c r="I35" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
+      <c r="J35" t="inlineStr">
         <is>
           <t>Nguyễn Việt Hùng</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
+      <c r="K35" t="inlineStr">
         <is>
           <t>0966547344</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
+      <c r="L35" t="inlineStr">
         <is>
           <t>Tự lập Mê Linh,Phường Hùng Vương,Thành phố Phúc Yên,Tỉnh Vĩnh Phúc</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr">
+      <c r="M35" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr">
+      <c r="N35" t="inlineStr">
         <is>
           <t>Hot</t>
         </is>
       </c>
-      <c r="O29" t="inlineStr">
+      <c r="O35" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>Sự cố</t>
-        </is>
-      </c>
-      <c r="Q29" t="inlineStr">
-        <is>
-          <t>Không kết nối được app/Wifi và không theo dõi được hiệu suất</t>
-        </is>
-      </c>
-      <c r="R29" t="inlineStr">
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Bảo hành</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
         <is>
           <t>KH đã báo CN
 KH đang dùng NLMT hiện tại bị lỗi biến tần, ko kết nối được app
@@ -4491,428 +5321,428 @@
 NOTE: địa chỉ hiện tại của KH: thôn phú mỹ, xã tiến thắng, Hà Nội</t>
         </is>
       </c>
-      <c r="S29" t="inlineStr">
+      <c r="S35" t="inlineStr">
         <is>
           <t>15:34 24/03/2026</t>
         </is>
       </c>
-      <c r="T29" t="inlineStr">
-        <is>
-          <t>17:30 01/04/2026</t>
-        </is>
-      </c>
-      <c r="U29" t="inlineStr">
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>14:16 16/04/2026</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V29" t="inlineStr">
+      <c r="V35" t="inlineStr">
         <is>
           <t>Trong hạn</t>
         </is>
       </c>
-      <c r="W29" t="inlineStr">
+      <c r="W35" t="inlineStr">
         <is>
           <t>Phạm Văn Nghĩa</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr">
+      <c r="X35" t="inlineStr">
         <is>
           <t>023020</t>
         </is>
       </c>
-      <c r="Y29" s="2">
+      <c r="Y35" s="2">
         <v>46105</v>
       </c>
-      <c r="Z29">
-        <v>8</v>
-      </c>
-      <c r="AA29" t="inlineStr">
+      <c r="Z35">
+        <v>9</v>
+      </c>
+      <c r="AA35" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
+    <row r="36">
+      <c r="A36" t="inlineStr">
         <is>
           <t>KV3</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>HCM</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C36" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D36" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>Inverter</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="F36" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_BDG_1352264</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="H36" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
+      <c r="I36" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
+      <c r="J36" t="inlineStr">
         <is>
           <t>Nguyễn Liễu Thông</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
+      <c r="K36" t="inlineStr">
         <is>
           <t>0362126000</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
+      <c r="L36" t="inlineStr">
         <is>
           <t>ph</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr">
+      <c r="M36" t="inlineStr">
         <is>
           <t>Nhân viên nội bộ VCC</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr">
+      <c r="N36" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O30" t="inlineStr">
+      <c r="O36" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P30" t="inlineStr">
+      <c r="P36" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q30" t="inlineStr">
+      <c r="Q36" t="inlineStr">
         <is>
           <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
-      <c r="R30" t="inlineStr">
+      <c r="R36" t="inlineStr">
         <is>
           <t>không hoạt động</t>
         </is>
       </c>
-      <c r="S30" t="inlineStr">
+      <c r="S36" t="inlineStr">
         <is>
           <t>09:29 26/03/2026</t>
         </is>
       </c>
-      <c r="T30" t="inlineStr">
+      <c r="T36" t="inlineStr">
         <is>
           <t>17:30 03/04/2026</t>
         </is>
       </c>
-      <c r="U30" t="inlineStr">
+      <c r="U36" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V30" t="inlineStr">
+      <c r="V36" t="inlineStr">
         <is>
           <t>Sắp quá hạn</t>
         </is>
       </c>
-      <c r="W30" t="inlineStr">
+      <c r="W36" t="inlineStr">
         <is>
           <t>Nguyễn Văn Toản</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr">
+      <c r="X36" t="inlineStr">
         <is>
           <t>427880</t>
         </is>
       </c>
-      <c r="Y30" s="2">
+      <c r="Y36" s="2">
         <v>46107</v>
       </c>
-      <c r="Z30">
-        <v>6</v>
-      </c>
-      <c r="AA30" t="inlineStr">
+      <c r="Z36">
+        <v>7</v>
+      </c>
+      <c r="AA36" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
+    <row r="37">
+      <c r="A37" t="inlineStr">
         <is>
           <t>KV1</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>PTO</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="F37" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_PTO_1620637</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="H37" t="inlineStr">
         <is>
           <t>Diamond</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
+      <c r="I37" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
+      <c r="J37" t="inlineStr">
         <is>
           <t>Nguyễn Đình Mạnh</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
+      <c r="K37" t="inlineStr">
         <is>
           <t>0988308581</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr">
+      <c r="L37" t="inlineStr">
         <is>
           <t>Xã Thanh Cao, Huyện Lương Sơn, Tỉnh Hòa Bình</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr">
+      <c r="M37" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr">
+      <c r="N37" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O31" t="inlineStr">
+      <c r="O37" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P31" t="inlineStr">
+      <c r="P37" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q31" t="inlineStr">
+      <c r="Q37" t="inlineStr">
         <is>
           <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
-      <c r="R31" t="inlineStr">
+      <c r="R37" t="inlineStr">
         <is>
           <t>KH chưa báo CN
 KH phản ánh: hệ thống bị lỗi, điện bật 10 -15s chớp 1 lần
 KH yêu cầu chuyển KT xuống xử lý gấp</t>
         </is>
       </c>
-      <c r="S31" t="inlineStr">
+      <c r="S37" t="inlineStr">
         <is>
           <t>15:09 24/03/2026</t>
         </is>
       </c>
-      <c r="T31" t="inlineStr">
+      <c r="T37" t="inlineStr">
         <is>
           <t>21:10 23/04/2026</t>
         </is>
       </c>
-      <c r="U31" t="inlineStr">
+      <c r="U37" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V31" t="inlineStr">
+      <c r="V37" t="inlineStr">
         <is>
           <t>Trong hạn</t>
         </is>
       </c>
-      <c r="W31" t="inlineStr">
+      <c r="W37" t="inlineStr">
         <is>
           <t>Bùi Anh Nguyễn</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr">
+      <c r="X37" t="inlineStr">
         <is>
           <t>414445</t>
         </is>
       </c>
-      <c r="Y31" s="2">
+      <c r="Y37" s="2">
         <v>46105</v>
       </c>
-      <c r="Z31">
-        <v>8</v>
-      </c>
-      <c r="AA31" t="inlineStr">
+      <c r="Z37">
+        <v>9</v>
+      </c>
+      <c r="AA37" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
+    <row r="38">
+      <c r="A38" t="inlineStr">
         <is>
           <t>KV1</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>NAN</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C38" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D38" t="inlineStr">
         <is>
           <t>CNTT</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="E38" t="inlineStr">
         <is>
           <t>Camera 360 độ</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="F38" t="inlineStr">
         <is>
           <t>299/2025/HĐKT</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t>B2B</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
+      <c r="I38" t="inlineStr">
         <is>
           <t>Khách hàng doanh nghiệp</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
+      <c r="J38" t="inlineStr">
         <is>
           <t>Ban Quản Lý Rừng Phòng Hộ Bắc Nghệ An</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
+      <c r="K38" t="inlineStr">
         <is>
           <t>0869217169</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
+      <c r="L38" t="inlineStr">
         <is>
           <t>Khối 11, Xã Quỳnh Lưu, Tỉnh Nghệ An</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr">
+      <c r="M38" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr">
+      <c r="N38" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O32" t="inlineStr">
+      <c r="O38" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>Hỗ trợ</t>
-        </is>
-      </c>
-      <c r="Q32" t="inlineStr">
-        <is>
-          <t>Hướng dẫn, hỗ trợ sử dụng sản phẩm</t>
-        </is>
-      </c>
-      <c r="R32" t="inlineStr">
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Sự cố</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
         <is>
           <t>1. KH đã báo cn
 2. KH phản ánh: camera 360 chưa kết nối được hệ thống điều khiển, chưa lên được tivi để xem và cũng như pccc rừng mùa khô.
@@ -4920,578 +5750,435 @@
 ***SĐT liên hệ: 0988867428, Anh Thức</t>
         </is>
       </c>
-      <c r="S32" t="inlineStr">
+      <c r="S38" t="inlineStr">
         <is>
           <t>08:45 24/03/2026</t>
         </is>
       </c>
-      <c r="T32" t="inlineStr">
-        <is>
-          <t>23:35 15/04/2026</t>
-        </is>
-      </c>
-      <c r="U32" t="inlineStr">
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>09:00 16/04/2026</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V32" t="inlineStr">
+      <c r="V38" t="inlineStr">
         <is>
           <t>Trong hạn</t>
         </is>
       </c>
-      <c r="W32" t="inlineStr">
+      <c r="W38" t="inlineStr">
         <is>
           <t>Võ Trọng Đức</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr">
+      <c r="X38" t="inlineStr">
         <is>
           <t>293804</t>
         </is>
       </c>
-      <c r="Y32" s="2">
+      <c r="Y38" s="2">
         <v>46105</v>
       </c>
-      <c r="Z32">
-        <v>8</v>
-      </c>
-      <c r="AA32" t="inlineStr">
+      <c r="Z38">
+        <v>9</v>
+      </c>
+      <c r="AA38" t="inlineStr">
         <is>
           <t>IOC</t>
         </is>
       </c>
-      <c r="AB32" t="inlineStr">
+      <c r="AB38" t="inlineStr">
         <is>
           <t>P.Triển khai</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
+      <c r="AC38" t="inlineStr">
         <is>
           <t>tietvt16</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
+    <row r="39">
+      <c r="A39" t="inlineStr">
         <is>
           <t>KV3</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>CMU</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>CNTT</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>Camera</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>KHCN_TT.GPTH_CMU_1265325</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NLMT</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Hệ thống NLMT</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>KHCN_TT.GPTH_BPC_1427400</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Member</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>Bích Loan</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>0946842984</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>Bích Loan Cống Hội Đồng Nguyên</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>Nhân viên nội bộ VCC</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Công Ty Tnhh Phúc An Solutions</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>0972342939</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>abc,Phường An Lộc,Thị xã Bình Long,Tỉnh Bình Phước</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>Hotline</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O33" t="inlineStr">
+      <c r="O39" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P33" t="inlineStr">
+      <c r="P39" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q33" t="inlineStr">
+      <c r="Q39" t="inlineStr">
         <is>
           <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
-      <c r="R33" t="inlineStr">
-        <is>
-          <t>cammera bị off 1 cai</t>
-        </is>
-      </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>10:28 26/03/2026</t>
-        </is>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>17:30 01/04/2026</t>
-        </is>
-      </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>Đang tiến hành</t>
-        </is>
-      </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>Sắp quá hạn</t>
-        </is>
-      </c>
-      <c r="W33" t="inlineStr">
-        <is>
-          <t>Lý Hoài Bảo</t>
-        </is>
-      </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>433302</t>
-        </is>
-      </c>
-      <c r="Y33" s="2">
-        <v>46107</v>
-      </c>
-      <c r="Z33">
-        <v>6</v>
-      </c>
-      <c r="AA33" t="inlineStr">
-        <is>
-          <t>AIO</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>P.Triển khai</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Tuyendv</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>KV3</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>GPTH</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>NLMT</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>Hệ thống NLMT</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>KHCN_TT.GPTH_BPC_1427400</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>B2C</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>Khách hàng cá nhân</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>Công Ty Tnhh Phúc An Solutions</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>0972342939</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>abc,Phường An Lộc,Thị xã Bình Long,Tỉnh Bình Phước</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>Hotline</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>Bình thường</t>
-        </is>
-      </c>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>Sau bán</t>
-        </is>
-      </c>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>Sự cố</t>
-        </is>
-      </c>
-      <c r="Q34" t="inlineStr">
-        <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
-        </is>
-      </c>
-      <c r="R34" t="inlineStr">
+      <c r="R39" t="inlineStr">
         <is>
           <t>1. KH chưa báo cn
 2. KH phản ánh: Cục pin lưu trữ đang ko hoạt động, ko sử dụng được.
 3. KH yêu cầu: Có KT qua kiểm tra, khắc phục tình trạng này cho KH.</t>
         </is>
       </c>
-      <c r="S34" t="inlineStr">
+      <c r="S39" t="inlineStr">
         <is>
           <t>14:29 23/03/2026</t>
         </is>
       </c>
-      <c r="T34" t="inlineStr">
-        <is>
-          <t>07:20 02/04/2026</t>
-        </is>
-      </c>
-      <c r="U34" t="inlineStr">
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>16:40 03/04/2026</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V34" t="inlineStr">
+      <c r="V39" t="inlineStr">
         <is>
           <t>Sắp quá hạn</t>
         </is>
       </c>
-      <c r="W34" t="inlineStr">
+      <c r="W39" t="inlineStr">
         <is>
           <t>Phạm Trung Hiếu</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr">
+      <c r="X39" t="inlineStr">
         <is>
           <t>264250</t>
         </is>
       </c>
-      <c r="Y34" s="2">
+      <c r="Y39" s="2">
         <v>46104</v>
       </c>
-      <c r="Z34">
-        <v>9</v>
-      </c>
-      <c r="AA34" t="inlineStr">
+      <c r="Z39">
+        <v>10</v>
+      </c>
+      <c r="AA39" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
+    <row r="40">
+      <c r="A40" t="inlineStr">
         <is>
           <t>KV2</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>DNG</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C40" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="D40" t="inlineStr">
         <is>
           <t>SS</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="E40" t="inlineStr">
         <is>
           <t>Công tắc thông minh</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="F40" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_DNG_1416913</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="G40" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="H40" t="inlineStr">
         <is>
           <t>Member</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
+      <c r="I40" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr">
+      <c r="J40" t="inlineStr">
         <is>
           <t>Lê Đắc Quỳ</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
+      <c r="K40" t="inlineStr">
         <is>
           <t>0915313915</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr">
+      <c r="L40" t="inlineStr">
         <is>
           <t>Phường Hòa Xuân, Thành phố Đà Nẵng</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr">
+      <c r="M40" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr">
+      <c r="N40" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O35" t="inlineStr">
+      <c r="O40" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P35" t="inlineStr">
+      <c r="P40" t="inlineStr">
         <is>
           <t>Hỗ trợ</t>
         </is>
       </c>
-      <c r="Q35" t="inlineStr">
+      <c r="Q40" t="inlineStr">
         <is>
           <t>Hướng dẫn, hỗ trợ sử dụng sản phẩm</t>
         </is>
       </c>
-      <c r="R35" t="inlineStr">
+      <c r="R40" t="inlineStr">
         <is>
           <t>1. KH đã báo cn
 2. KH phản ánh: Vào được aio app smart home nhưng ko thấy có công tắc.
 3. KH yêu cầu: Qua hỗ trợ, kiểm tra thiết bị cho KH, KH sẵn sàng trả phí.</t>
         </is>
       </c>
-      <c r="S35" t="inlineStr">
+      <c r="S40" t="inlineStr">
         <is>
           <t>08:00 23/03/2026</t>
         </is>
       </c>
-      <c r="T35" t="inlineStr">
+      <c r="T40" t="inlineStr">
         <is>
           <t>07:50 08/04/2026</t>
         </is>
       </c>
-      <c r="U35" t="inlineStr">
+      <c r="U40" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V35" t="inlineStr">
+      <c r="V40" t="inlineStr">
         <is>
           <t>Trong hạn</t>
         </is>
       </c>
-      <c r="W35" t="inlineStr">
+      <c r="W40" t="inlineStr">
         <is>
           <t>Ngô Văn Minh</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr">
+      <c r="X40" t="inlineStr">
         <is>
           <t>083585</t>
         </is>
       </c>
-      <c r="Y35" s="2">
+      <c r="Y40" s="2">
         <v>46104</v>
       </c>
-      <c r="Z35">
-        <v>9</v>
-      </c>
-      <c r="AA35" t="inlineStr">
+      <c r="Z40">
+        <v>10</v>
+      </c>
+      <c r="AA40" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB35" t="inlineStr">
+      <c r="AB40" t="inlineStr">
         <is>
           <t>P.Triển khai</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
+      <c r="AC40" t="inlineStr">
         <is>
           <t>Sonln15</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
+    <row r="41">
+      <c r="A41" t="inlineStr">
         <is>
           <t>KV1</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>BNH</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="D41" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="E41" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="F41" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_BGG_1597213</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
+      <c r="H41" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
+      <c r="I41" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr">
+      <c r="J41" t="inlineStr">
         <is>
           <t>Dương Văn Quân</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr">
+      <c r="K41" t="inlineStr">
         <is>
           <t>0359999199</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr">
+      <c r="L41" t="inlineStr">
         <is>
           <t>xã Hoàng Vân</t>
         </is>
       </c>
-      <c r="M36" t="inlineStr">
+      <c r="M41" t="inlineStr">
         <is>
           <t>Happycall</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr">
+      <c r="N41" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O36" t="inlineStr">
+      <c r="O41" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P36" t="inlineStr">
+      <c r="P41" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q36" t="inlineStr">
+      <c r="Q41" t="inlineStr">
         <is>
           <t>Chất lượng, hiệu suất của sản phẩm/hệ thống thấp</t>
         </is>
       </c>
-      <c r="R36" t="inlineStr">
+      <c r="R41" t="inlineStr">
         <is>
           <t>1.Đã báo chi nhánh chưa: chưa báo
 2.Đã báo qua đâu: DTV HPC
@@ -5499,433 +6186,433 @@
 4.KH yêu cầu KT qua kiểm tra cho KH</t>
         </is>
       </c>
-      <c r="S36" t="inlineStr">
+      <c r="S41" t="inlineStr">
         <is>
           <t>08:00 23/03/2026</t>
         </is>
       </c>
-      <c r="T36" t="inlineStr">
+      <c r="T41" t="inlineStr">
         <is>
           <t>18:00 26/03/2026</t>
         </is>
       </c>
-      <c r="U36" t="inlineStr">
+      <c r="U41" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V36" t="inlineStr">
+      <c r="V41" t="inlineStr">
         <is>
           <t>Quá hạn</t>
         </is>
       </c>
-      <c r="W36" t="inlineStr">
+      <c r="W41" t="inlineStr">
         <is>
           <t>Phạm Văn Huy</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr">
+      <c r="X41" t="inlineStr">
         <is>
           <t>408869</t>
         </is>
       </c>
-      <c r="Y36" s="2">
+      <c r="Y41" s="2">
         <v>46104</v>
       </c>
-      <c r="Z36">
-        <v>9</v>
-      </c>
-      <c r="AA36" t="inlineStr">
+      <c r="Z41">
+        <v>10</v>
+      </c>
+      <c r="AA41" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
+    <row r="42">
+      <c r="A42" t="inlineStr">
         <is>
           <t>KV3</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>HCM</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C42" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="D42" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="E42" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="F42" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_HCM_1638575</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="G42" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="H42" t="inlineStr">
         <is>
           <t>Diamond</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
+      <c r="I42" t="inlineStr">
         <is>
           <t>Khách hàng doanh nghiệp</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr">
+      <c r="J42" t="inlineStr">
         <is>
           <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ TAYOTO</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr">
+      <c r="K42" t="inlineStr">
         <is>
           <t>0911937779</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr">
+      <c r="L42" t="inlineStr">
         <is>
           <t>quốc lộ 55, Xã Hồ Tràm, Thành phố Hồ Chí Minh, Xã Hồ Tràm, Thành phố Hồ Chí Minh</t>
         </is>
       </c>
-      <c r="M37" t="inlineStr">
+      <c r="M42" t="inlineStr">
         <is>
           <t>Happycall</t>
         </is>
       </c>
-      <c r="N37" t="inlineStr">
+      <c r="N42" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O37" t="inlineStr">
+      <c r="O42" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P37" t="inlineStr">
+      <c r="P42" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>Sản phẩm bị ngắt quãng/ Không theo dõi và không nghe được</t>
-        </is>
-      </c>
-      <c r="R37" t="inlineStr">
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
         <is>
           <t>1. KH chưa báo cn
 2. KH phản ánh: Sự cố từ TT_1772587360264 trước sau khi xử lý KH thấy hệ thống nlmt ko có ổn định, lâu lâu tự ngắt và phải bảo nv tắt 3 công tắc cp đi bật lại mãi mới được.
 3. KH yêu cầu: Kiểm tra lại hàng hóa xem có đúng với HĐ về chất lượng, hiệu suất không. Nếu có vấn đề thì thay mới tinh cho KH để hệ thống vận hành trơn tru.</t>
         </is>
       </c>
-      <c r="S37" t="inlineStr">
+      <c r="S42" t="inlineStr">
         <is>
           <t>09:25 19/03/2026</t>
         </is>
       </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>08:35 25/04/2026</t>
-        </is>
-      </c>
-      <c r="U37" t="inlineStr">
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>09:00 28/04/2026</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V37" t="inlineStr">
+      <c r="V42" t="inlineStr">
         <is>
           <t>Trong hạn</t>
         </is>
       </c>
-      <c r="W37" t="inlineStr">
+      <c r="W42" t="inlineStr">
         <is>
           <t>Lê Đức Cảnh</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr">
+      <c r="X42" t="inlineStr">
         <is>
           <t>291002</t>
         </is>
       </c>
-      <c r="Y37" s="2">
+      <c r="Y42" s="2">
         <v>46100</v>
       </c>
-      <c r="Z37">
-        <v>13</v>
-      </c>
-      <c r="AA37" t="inlineStr">
+      <c r="Z42">
+        <v>14</v>
+      </c>
+      <c r="AA42" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
+    <row r="43">
+      <c r="A43" t="inlineStr">
         <is>
           <t>KV3</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>HCM</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C43" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="D43" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="E43" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="F43" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_HCM_1646383</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="G43" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
+      <c r="H43" t="inlineStr">
         <is>
           <t>Diamond</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
+      <c r="I43" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr">
+      <c r="J43" t="inlineStr">
         <is>
           <t>Nguyễn Hữu Nghĩa</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr">
+      <c r="K43" t="inlineStr">
         <is>
           <t>0945919596</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr">
+      <c r="L43" t="inlineStr">
         <is>
           <t>Phường Tam Thắng, Thành phố Hồ Chí Minh, Phường Tam Thắng, Thành phố Hồ Chí Minh</t>
         </is>
       </c>
-      <c r="M38" t="inlineStr">
+      <c r="M43" t="inlineStr">
         <is>
           <t>Happycall</t>
         </is>
       </c>
-      <c r="N38" t="inlineStr">
+      <c r="N43" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O38" t="inlineStr">
+      <c r="O43" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P38" t="inlineStr">
+      <c r="P43" t="inlineStr">
         <is>
           <t>Hỗ trợ</t>
         </is>
       </c>
-      <c r="Q38" t="inlineStr">
+      <c r="Q43" t="inlineStr">
         <is>
           <t>Hướng dẫn, hỗ trợ sử dụng sản phẩm</t>
         </is>
       </c>
-      <c r="R38" t="inlineStr">
-        <is>
-          <t>KH yc ktra nguyên nhân xảy ra sự cố TT_1772849052506</t>
-        </is>
-      </c>
-      <c r="S38" t="inlineStr">
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>KH yc ktra nguyên nhân xảy ra sự cố Hệ NLMT bị sự cố lỗi. Nhiều lúc lấy điện lưới dùng không dùng điện NLMT.</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
         <is>
           <t>08:00 16/03/2026</t>
         </is>
       </c>
-      <c r="T38" t="inlineStr">
-        <is>
-          <t>08:45 12/04/2026</t>
-        </is>
-      </c>
-      <c r="U38" t="inlineStr">
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>09:00 13/04/2026</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V38" t="inlineStr">
+      <c r="V43" t="inlineStr">
         <is>
           <t>Trong hạn</t>
         </is>
       </c>
-      <c r="W38" t="inlineStr">
+      <c r="W43" t="inlineStr">
         <is>
           <t>Lê Đức Cảnh</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr">
+      <c r="X43" t="inlineStr">
         <is>
           <t>291002</t>
         </is>
       </c>
-      <c r="Y38" s="2">
+      <c r="Y43" s="2">
         <v>46097</v>
       </c>
-      <c r="Z38">
-        <v>16</v>
-      </c>
-      <c r="AA38" t="inlineStr">
+      <c r="Z43">
+        <v>17</v>
+      </c>
+      <c r="AA43" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
+    <row r="44">
+      <c r="A44" t="inlineStr">
         <is>
           <t>KV1</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>BNH</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C44" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="D44" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="E44" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="F44" t="inlineStr">
         <is>
           <t>KHCN_PINNLMT_BGG_0404930</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="G44" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="H44" t="inlineStr">
         <is>
           <t>Member</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
+      <c r="I44" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr">
+      <c r="J44" t="inlineStr">
         <is>
           <t>Lê Văn Mạnh</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr">
+      <c r="K44" t="inlineStr">
         <is>
           <t>0987567050</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr">
+      <c r="L44" t="inlineStr">
         <is>
           <t>Xã Liên Chung,Huyện Tân Yên,Tỉnh Bắc Giang</t>
         </is>
       </c>
-      <c r="M39" t="inlineStr">
+      <c r="M44" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N39" t="inlineStr">
+      <c r="N44" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O39" t="inlineStr">
+      <c r="O44" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P39" t="inlineStr">
+      <c r="P44" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q39" t="inlineStr">
+      <c r="Q44" t="inlineStr">
         <is>
           <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
-      <c r="R39" t="inlineStr">
+      <c r="R44" t="inlineStr">
         <is>
           <t>1.Đã báo chi nhánh chưa: đã báo
 2.KH báo cho GĐ Trường 
@@ -5934,285 +6621,285 @@
  5.KH yêu cầu KT qua kiểm tra gấp cho KH.</t>
         </is>
       </c>
-      <c r="S39" t="inlineStr">
+      <c r="S44" t="inlineStr">
         <is>
           <t>10:21 10/03/2026</t>
         </is>
       </c>
-      <c r="T39" t="inlineStr">
+      <c r="T44" t="inlineStr">
         <is>
           <t>09:00 30/03/2026</t>
         </is>
       </c>
-      <c r="U39" t="inlineStr">
+      <c r="U44" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V39" t="inlineStr">
+      <c r="V44" t="inlineStr">
         <is>
           <t>Quá hạn</t>
         </is>
       </c>
-      <c r="W39" t="inlineStr">
+      <c r="W44" t="inlineStr">
         <is>
           <t>Thân Đức Giang</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr">
+      <c r="X44" t="inlineStr">
         <is>
           <t>081984</t>
         </is>
       </c>
-      <c r="Y39" s="2">
+      <c r="Y44" s="2">
         <v>46091</v>
       </c>
-      <c r="Z39">
-        <v>22</v>
-      </c>
-      <c r="AA39" t="inlineStr">
+      <c r="Z44">
+        <v>23</v>
+      </c>
+      <c r="AA44" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
+    <row r="45">
+      <c r="A45" t="inlineStr">
         <is>
           <t>KV2</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B45" t="inlineStr">
         <is>
           <t>QTI</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C45" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="D45" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="E45" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="F45" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_QTI_0991884</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="G45" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
+      <c r="I45" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr">
+      <c r="J45" t="inlineStr">
         <is>
           <t>Nguyễn Thị Như Mỹ</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr">
+      <c r="K45" t="inlineStr">
         <is>
           <t>0963369267</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr">
+      <c r="L45" t="inlineStr">
         <is>
           <t>KP4, Thị trấn Cam Lộ, Huyện Cam Lộ, Tỉnh Quảng Trị</t>
         </is>
       </c>
-      <c r="M40" t="inlineStr">
+      <c r="M45" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N40" t="inlineStr">
+      <c r="N45" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O40" t="inlineStr">
+      <c r="O45" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P40" t="inlineStr">
+      <c r="P45" t="inlineStr">
         <is>
           <t>Bảo hành</t>
         </is>
       </c>
-      <c r="Q40" t="inlineStr">
+      <c r="Q45" t="inlineStr">
         <is>
           <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
-      <c r="R40" t="inlineStr">
+      <c r="R45" t="inlineStr">
         <is>
           <t>1. KH đã báo cn: a Nguyễn Đình Bằng bên nlmt
 2. KH phản ánh: Hệ thống inverter báo lỗi mã lỗi 01.M011 và ko đẩy ra sản lượng điện nlmt.
 3. KH yêu cầu: Điều KT qua hỗ trợ giúp KH.</t>
         </is>
       </c>
-      <c r="S40" t="inlineStr">
+      <c r="S45" t="inlineStr">
         <is>
           <t>08:00 09/03/2026</t>
         </is>
       </c>
-      <c r="T40" t="inlineStr">
+      <c r="T45" t="inlineStr">
         <is>
           <t>11:45 10/04/2026</t>
         </is>
       </c>
-      <c r="U40" t="inlineStr">
+      <c r="U45" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V40" t="inlineStr">
+      <c r="V45" t="inlineStr">
         <is>
           <t>Trong hạn</t>
         </is>
       </c>
-      <c r="W40" t="inlineStr">
+      <c r="W45" t="inlineStr">
         <is>
           <t>Trương Thành</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr">
+      <c r="X45" t="inlineStr">
         <is>
           <t>462341</t>
         </is>
       </c>
-      <c r="Y40" s="2">
+      <c r="Y45" s="2">
         <v>46090</v>
       </c>
-      <c r="Z40">
-        <v>23</v>
-      </c>
-      <c r="AA40" t="inlineStr">
+      <c r="Z45">
+        <v>24</v>
+      </c>
+      <c r="AA45" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
+    <row r="46">
+      <c r="A46" t="inlineStr">
         <is>
           <t>KV3</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B46" t="inlineStr">
         <is>
           <t>HCM</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C46" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="D46" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="E46" t="inlineStr">
         <is>
           <t>Inverter</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="F46" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_VTU_1502475</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="G46" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
+      <c r="H46" t="inlineStr">
         <is>
           <t>Diamond</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
+      <c r="I46" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr">
+      <c r="J46" t="inlineStr">
         <is>
           <t>Nguyễn Phú Quý</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr">
+      <c r="K46" t="inlineStr">
         <is>
           <t>0947110192</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr">
+      <c r="L46" t="inlineStr">
         <is>
           <t>120 Chu Mạnh Trinh,Phường 8,Thành phố Vũng Tàu,Tỉnh Bà Rịa - Vũng Tàu, Phường Tam Thắng, Thành phố Hồ Chí Minh</t>
         </is>
       </c>
-      <c r="M41" t="inlineStr">
+      <c r="M46" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N41" t="inlineStr">
+      <c r="N46" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O41" t="inlineStr">
+      <c r="O46" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P41" t="inlineStr">
+      <c r="P46" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q41" t="inlineStr">
+      <c r="Q46" t="inlineStr">
         <is>
           <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
-      <c r="R41" t="inlineStr">
+      <c r="R46" t="inlineStr">
         <is>
           <t>1. Đã báo chi nhánh chưa: chưa báo
 2.KH gọi điện lên TĐ
@@ -6220,853 +6907,853 @@
 4.KH yêu cầu Kt kiểm tra lại pin và CN đưa ra phương án xử lý vấn đề thiệt hại kinh tế cho KH khi sử dụng điện NLMT không hiệu quả.</t>
         </is>
       </c>
-      <c r="S41" t="inlineStr">
+      <c r="S46" t="inlineStr">
         <is>
           <t>15:09 03/03/2026</t>
         </is>
       </c>
-      <c r="T41" t="inlineStr">
+      <c r="T46" t="inlineStr">
         <is>
           <t>12:55 15/03/2026</t>
         </is>
       </c>
-      <c r="U41" t="inlineStr">
+      <c r="U46" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V41" t="inlineStr">
+      <c r="V46" t="inlineStr">
         <is>
           <t>Trong hạn</t>
         </is>
       </c>
-      <c r="W41" t="inlineStr">
+      <c r="W46" t="inlineStr">
         <is>
           <t>Lê Đức Cảnh</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr">
+      <c r="X46" t="inlineStr">
         <is>
           <t>291002</t>
         </is>
       </c>
-      <c r="Y41" s="2">
+      <c r="Y46" s="2">
         <v>46084</v>
       </c>
-      <c r="Z41">
-        <v>29</v>
-      </c>
-      <c r="AA41" t="inlineStr">
+      <c r="Z46">
+        <v>30</v>
+      </c>
+      <c r="AA46" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
+    <row r="47">
+      <c r="A47" t="inlineStr">
         <is>
           <t>KV1</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B47" t="inlineStr">
         <is>
           <t>NAN</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C47" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="D47" t="inlineStr">
         <is>
           <t>CNTT</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="E47" t="inlineStr">
         <is>
           <t>Camera</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="F47" t="inlineStr">
         <is>
           <t>081101/HĐMBLĐ-2024/THQUYNHHUNG-NAN</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="G47" t="inlineStr">
         <is>
           <t>B2B</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
+      <c r="I47" t="inlineStr">
         <is>
           <t>Khách hàng doanh nghiệp</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr">
+      <c r="J47" t="inlineStr">
         <is>
           <t>Trường Tiểu Học Quỳnh Hưng</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr">
+      <c r="K47" t="inlineStr">
         <is>
           <t>0963785576</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr">
+      <c r="L47" t="inlineStr">
         <is>
           <t>Xóm 6,Xã Quỳnh Hưng,Huyện Quỳnh Lưu,Tỉnh Nghệ An</t>
         </is>
       </c>
-      <c r="M42" t="inlineStr">
+      <c r="M47" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N42" t="inlineStr">
+      <c r="N47" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O42" t="inlineStr">
+      <c r="O47" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P42" t="inlineStr">
+      <c r="P47" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q42" t="inlineStr">
+      <c r="Q47" t="inlineStr">
         <is>
           <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
-      <c r="R42" t="inlineStr">
+      <c r="R47" t="inlineStr">
         <is>
           <t>1. Kh chưa báo cn
 2. Kh phản ánh: Hiện tại ko có mắt cam nào xem đc, mạng thì vẫn bình thường
 3. Kh yc: Yc cn hỗ trợ</t>
         </is>
       </c>
-      <c r="S42" t="inlineStr">
+      <c r="S47" t="inlineStr">
         <is>
           <t>16:54 26/02/2026</t>
         </is>
       </c>
-      <c r="T42" t="inlineStr">
+      <c r="T47" t="inlineStr">
         <is>
           <t>18:30 04/04/2026</t>
         </is>
       </c>
-      <c r="U42" t="inlineStr">
+      <c r="U47" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V42" t="inlineStr">
+      <c r="V47" t="inlineStr">
         <is>
           <t>Sắp quá hạn</t>
         </is>
       </c>
-      <c r="W42" t="inlineStr">
+      <c r="W47" t="inlineStr">
         <is>
           <t>Lê Văn Toán</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr">
+      <c r="X47" t="inlineStr">
         <is>
           <t>119464</t>
         </is>
       </c>
-      <c r="Y42" s="2">
+      <c r="Y47" s="2">
         <v>46079</v>
       </c>
-      <c r="Z42">
-        <v>34</v>
-      </c>
-      <c r="AA42" t="inlineStr">
+      <c r="Z47">
+        <v>35</v>
+      </c>
+      <c r="AA47" t="inlineStr">
         <is>
           <t>IOC</t>
         </is>
       </c>
-      <c r="AB42" t="inlineStr">
+      <c r="AB47" t="inlineStr">
         <is>
           <t>P.Triển khai</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
+      <c r="AC47" t="inlineStr">
         <is>
           <t>tietvt16</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
+    <row r="48">
+      <c r="A48" t="inlineStr">
         <is>
           <t>KV3</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B48" t="inlineStr">
         <is>
           <t>DNI</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C48" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="D48" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="E48" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="F48" t="inlineStr">
         <is>
           <t>KHDN_TT.GPTH_DNI_1659133</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="G48" t="inlineStr">
         <is>
           <t>B2B</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
+      <c r="H48" t="inlineStr">
         <is>
           <t>Diamond</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
+      <c r="I48" t="inlineStr">
         <is>
           <t>Khách hàng doanh nghiệp</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr">
+      <c r="J48" t="inlineStr">
         <is>
           <t>CÔNG TY TNHH KHOA HỌC KỸ THUẬT TOÀN CẦU</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
+      <c r="K48" t="inlineStr">
         <is>
           <t>0907002673</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr">
+      <c r="L48" t="inlineStr">
         <is>
           <t>Lầu 19, Khu A, Số 4 Nguyễn Đình Chiểu, Phường Tân Định, Thành phố Hồ Chí Minh</t>
         </is>
       </c>
-      <c r="M43" t="inlineStr">
+      <c r="M48" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N43" t="inlineStr">
+      <c r="N48" t="inlineStr">
         <is>
           <t>Hot</t>
         </is>
       </c>
-      <c r="O43" t="inlineStr">
+      <c r="O48" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P43" t="inlineStr">
+      <c r="P48" t="inlineStr">
         <is>
           <t>Bảo hành</t>
         </is>
       </c>
-      <c r="Q43" t="inlineStr">
+      <c r="Q48" t="inlineStr">
         <is>
           <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
-      <c r="R43" t="inlineStr">
+      <c r="R48" t="inlineStr">
         <is>
           <t>1. Kh đã báo cn
 2. Kh phản ánh: Hệ của kh dạo này sd có hiện tượng liên tục bị sập. Kh đã báo kt và kt phản hồi do kh sd quá tải nhưng từ khi lắp đến nay kh báo chỉ dùng bằng đó thiết bị chứ ko hơn
 3. kh yc: YC cn hỗ trợ sớm</t>
         </is>
       </c>
-      <c r="S43" t="inlineStr">
+      <c r="S48" t="inlineStr">
         <is>
           <t>13:30 23/02/2026</t>
         </is>
       </c>
-      <c r="T43" t="inlineStr">
+      <c r="T48" t="inlineStr">
         <is>
           <t>17:45 29/03/2026</t>
         </is>
       </c>
-      <c r="U43" t="inlineStr">
+      <c r="U48" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V43" t="inlineStr">
+      <c r="V48" t="inlineStr">
         <is>
           <t>Trong hạn</t>
         </is>
       </c>
-      <c r="W43" t="inlineStr">
+      <c r="W48" t="inlineStr">
         <is>
           <t>Nguyễn Hữu Tâm Định</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr">
+      <c r="X48" t="inlineStr">
         <is>
           <t>450471</t>
         </is>
       </c>
-      <c r="Y43" s="2">
+      <c r="Y48" s="2">
         <v>46076</v>
       </c>
-      <c r="Z43">
-        <v>37</v>
-      </c>
-      <c r="AA43" t="inlineStr">
+      <c r="Z48">
+        <v>38</v>
+      </c>
+      <c r="AA48" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
+    <row r="49">
+      <c r="A49" t="inlineStr">
         <is>
           <t>KV1</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B49" t="inlineStr">
         <is>
           <t>NAN</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="C49" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="D49" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="E49" t="inlineStr">
         <is>
           <t>Inverter</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="F49" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_NAN_1364237</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="G49" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
+      <c r="H49" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
+      <c r="I49" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr">
+      <c r="J49" t="inlineStr">
         <is>
           <t>Trương Công An</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr">
+      <c r="K49" t="inlineStr">
         <is>
           <t>0914531694</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr">
+      <c r="L49" t="inlineStr">
         <is>
           <t>khối 2</t>
         </is>
       </c>
-      <c r="M44" t="inlineStr">
+      <c r="M49" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N44" t="inlineStr">
+      <c r="N49" t="inlineStr">
         <is>
           <t>Hot</t>
         </is>
       </c>
-      <c r="O44" t="inlineStr">
+      <c r="O49" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P44" t="inlineStr">
+      <c r="P49" t="inlineStr">
         <is>
           <t>Bảo hành</t>
         </is>
       </c>
-      <c r="Q44" t="inlineStr">
+      <c r="Q49" t="inlineStr">
         <is>
           <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
-      <c r="R44" t="inlineStr">
+      <c r="R49" t="inlineStr">
         <is>
           <t>- KH phản ánh nhân sự Lê Văn Anh mang thiết bị ivt đi bảo hành từ 8/12/2025  tới nay 16/1/2026 vẫn chưa có ivt gửi về cho KH. Đã rất lâu và thiệt hại rất nhiều, trước đấy có mang ắc quy đi BH cũng k được giờ mang ivt đi hơn tháng chưa thấy phản hồi 
 - KH Yc ktra lại và phản hồi mang thiết bị về lắp đặt  lại cho KH</t>
         </is>
       </c>
-      <c r="S44" t="inlineStr">
+      <c r="S49" t="inlineStr">
         <is>
           <t>08:00 19/01/2026</t>
         </is>
       </c>
-      <c r="T44" t="inlineStr">
+      <c r="T49" t="inlineStr">
         <is>
           <t>22:00 17/04/2026</t>
         </is>
       </c>
-      <c r="U44" t="inlineStr">
+      <c r="U49" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V44" t="inlineStr">
+      <c r="V49" t="inlineStr">
         <is>
           <t>Trong hạn</t>
         </is>
       </c>
-      <c r="W44" t="inlineStr">
+      <c r="W49" t="inlineStr">
         <is>
           <t>Lê Văn Anh</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr">
+      <c r="X49" t="inlineStr">
         <is>
           <t>069170</t>
         </is>
       </c>
-      <c r="Y44" s="2">
+      <c r="Y49" s="2">
         <v>46041</v>
       </c>
-      <c r="Z44">
-        <v>72</v>
-      </c>
-      <c r="AA44" t="inlineStr">
+      <c r="Z49">
+        <v>73</v>
+      </c>
+      <c r="AA49" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
+    <row r="50">
+      <c r="A50" t="inlineStr">
         <is>
           <t>KV1</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B50" t="inlineStr">
         <is>
           <t>TNN</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C50" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="D50" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="E50" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="F50" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_TNN_0885867</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="G50" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
+      <c r="I50" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr">
+      <c r="J50" t="inlineStr">
         <is>
           <t>Nguyễn Đức Hùng</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr">
+      <c r="K50" t="inlineStr">
         <is>
           <t>0396264028</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr">
+      <c r="L50" t="inlineStr">
         <is>
           <t>Xóm Ấp Chè, Xã Văn Hán, Huyện Đồng Hỷ, Tỉnh Thái Nguyên</t>
         </is>
       </c>
-      <c r="M45" t="inlineStr">
+      <c r="M50" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N45" t="inlineStr">
+      <c r="N50" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O45" t="inlineStr">
+      <c r="O50" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P45" t="inlineStr">
+      <c r="P50" t="inlineStr">
         <is>
           <t>Bảo hành</t>
         </is>
       </c>
-      <c r="Q45" t="inlineStr">
+      <c r="Q50" t="inlineStr">
         <is>
           <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
-      <c r="R45" t="inlineStr">
+      <c r="R50" t="inlineStr">
         <is>
           <t>1. Đã báo CN: Chưa báo
 2. KH báo sự cố: 1 cục pin lưu trữ không vào điện và khi mất điện lưới hệ không tải điện vào để sử dụng.
 3. Kh yêu cầu: KT qua kiểm tra cho Kh</t>
         </is>
       </c>
-      <c r="S45" t="inlineStr">
+      <c r="S50" t="inlineStr">
         <is>
           <t>08:00 14/01/2026</t>
         </is>
       </c>
-      <c r="T45" t="inlineStr">
+      <c r="T50" t="inlineStr">
         <is>
           <t>17:00 25/02/2026</t>
         </is>
       </c>
-      <c r="U45" t="inlineStr">
+      <c r="U50" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V45" t="inlineStr">
+      <c r="V50" t="inlineStr">
         <is>
           <t>Trong hạn</t>
         </is>
       </c>
-      <c r="W45" t="inlineStr">
+      <c r="W50" t="inlineStr">
         <is>
           <t>Trần Xuân Kương</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr">
+      <c r="X50" t="inlineStr">
         <is>
           <t>289759</t>
         </is>
       </c>
-      <c r="Y45" s="2">
+      <c r="Y50" s="2">
         <v>46036</v>
       </c>
-      <c r="Z45">
-        <v>77</v>
-      </c>
-      <c r="AA45" t="inlineStr">
+      <c r="Z50">
+        <v>78</v>
+      </c>
+      <c r="AA50" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
+    <row r="51">
+      <c r="A51" t="inlineStr">
         <is>
           <t>KV1</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B51" t="inlineStr">
         <is>
           <t>BNH</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C51" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="D51" t="inlineStr">
         <is>
           <t>M&amp;E</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="E51" t="inlineStr">
         <is>
           <t>Bếp từ</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="F51" t="inlineStr">
         <is>
           <t>KHDN_TT.GPTH_HNI_2402026_CDV</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="G51" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
+      <c r="H51" t="inlineStr">
         <is>
           <t>Silver</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
+      <c r="I51" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr">
+      <c r="J51" t="inlineStr">
         <is>
           <t>Nguyễn Quang Vũ</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr">
+      <c r="K51" t="inlineStr">
         <is>
           <t>0983034568</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr">
+      <c r="L51" t="inlineStr">
         <is>
           <t>CNCT Viettel Bắc Ninh</t>
         </is>
       </c>
-      <c r="M46" t="inlineStr">
+      <c r="M51" t="inlineStr">
         <is>
           <t>Nhân viên nội bộ VCC</t>
         </is>
       </c>
-      <c r="N46" t="inlineStr">
+      <c r="N51" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O46" t="inlineStr">
+      <c r="O51" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P46" t="inlineStr">
+      <c r="P51" t="inlineStr">
         <is>
           <t>Bảo hành</t>
         </is>
       </c>
-      <c r="Q46" t="inlineStr">
+      <c r="Q51" t="inlineStr">
         <is>
           <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
-      <c r="R46" t="inlineStr">
+      <c r="R51" t="inlineStr">
         <is>
           <t>KH nội bộ VCC T12/2025 quay số trúng thưởng bếp từ đơn AIO, bếp không hoạt động. Yêu cầu Kt qua bảo hành gấp. 
 Quà tặng trúng thưởng nên không có thông tin mã HĐ.</t>
         </is>
       </c>
-      <c r="S46" t="inlineStr">
+      <c r="S51" t="inlineStr">
         <is>
           <t>08:00 05/01/2026</t>
         </is>
       </c>
-      <c r="T46" t="inlineStr">
+      <c r="T51" t="inlineStr">
         <is>
           <t>10:25 03/04/2026</t>
         </is>
       </c>
-      <c r="U46" t="inlineStr">
+      <c r="U51" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V46" t="inlineStr">
+      <c r="V51" t="inlineStr">
         <is>
           <t>Trong hạn</t>
         </is>
       </c>
-      <c r="W46" t="inlineStr">
+      <c r="W51" t="inlineStr">
         <is>
           <t>Đinh Thị Ngọc</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr">
+      <c r="X51" t="inlineStr">
         <is>
           <t>205029</t>
         </is>
       </c>
-      <c r="Y46" s="2">
+      <c r="Y51" s="2">
         <v>46027</v>
       </c>
-      <c r="Z46">
-        <v>86</v>
-      </c>
-      <c r="AA46" t="inlineStr">
+      <c r="Z51">
+        <v>87</v>
+      </c>
+      <c r="AA51" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB46" t="inlineStr">
+      <c r="AB51" t="inlineStr">
         <is>
           <t>P.Triển khai</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr">
+      <c r="AC51" t="inlineStr">
         <is>
           <t>Anhnt631</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
+    <row r="52">
+      <c r="A52" t="inlineStr">
         <is>
           <t>KV1</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B52" t="inlineStr">
         <is>
           <t>QNH</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C52" t="inlineStr">
         <is>
           <t>DVKT</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="D52" t="inlineStr">
         <is>
           <t>Home Service</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="E52" t="inlineStr">
         <is>
           <t>Dịch vụ khác</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="F52" t="inlineStr">
         <is>
           <t>23092025/HĐTP-SPT-VIETTEL</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="G52" t="inlineStr">
         <is>
           <t>B2B</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
+      <c r="I52" t="inlineStr">
         <is>
           <t>Khách hàng doanh nghiệp</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr">
+      <c r="J52" t="inlineStr">
         <is>
           <t>CÔNG TY CỔ PHẦN SPT VIỆT NAM</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr">
+      <c r="K52" t="inlineStr">
         <is>
           <t>0962892720</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr">
+      <c r="L52" t="inlineStr">
         <is>
           <t>...</t>
         </is>
       </c>
-      <c r="M47" t="inlineStr">
+      <c r="M52" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N47" t="inlineStr">
+      <c r="N52" t="inlineStr">
         <is>
           <t>Hot</t>
         </is>
       </c>
-      <c r="O47" t="inlineStr">
+      <c r="O52" t="inlineStr">
         <is>
           <t>Trong bán</t>
         </is>
       </c>
-      <c r="P47" t="inlineStr">
+      <c r="P52" t="inlineStr">
         <is>
           <t>Khiếu nại</t>
         </is>
       </c>
-      <c r="Q47" t="inlineStr">
+      <c r="Q52" t="inlineStr">
         <is>
           <t>Tiến độ triển khai chậm</t>
         </is>
       </c>
-      <c r="R47" t="inlineStr">
+      <c r="R52" t="inlineStr">
         <is>
           <t>- Đối tác Công ty cổ phần SPT Việt Nam (sdt phản ánh 0975014010) tiếp tục gọi tđ phản ánh về vấn đề chậm trễ tiến độ và thiếu nhân lực thi công cho dự án Thi công lắp đặt hệ thống Chiller. 
 - Kh báo hiện tại vẫn chậm tiến độ, cn ko thay đổi hay tiến triển thêm gì
@@ -7074,53 +7761,53 @@
 - Kh yc: Yc TCT có biện pháp xử lý rõ ràng cho kh</t>
         </is>
       </c>
-      <c r="S47" t="inlineStr">
+      <c r="S52" t="inlineStr">
         <is>
           <t>08:00 10/12/2025</t>
         </is>
       </c>
-      <c r="T47" t="inlineStr">
+      <c r="T52" t="inlineStr">
         <is>
           <t>15:00 16/12/2025</t>
         </is>
       </c>
-      <c r="U47" t="inlineStr">
+      <c r="U52" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V47" t="inlineStr">
+      <c r="V52" t="inlineStr">
         <is>
           <t>Trong hạn</t>
         </is>
       </c>
-      <c r="W47" t="inlineStr">
+      <c r="W52" t="inlineStr">
         <is>
           <t>Đặng Việt Phú</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr">
+      <c r="X52" t="inlineStr">
         <is>
           <t>062146</t>
         </is>
       </c>
-      <c r="Y47" s="2">
+      <c r="Y52" s="2">
         <v>46001</v>
       </c>
-      <c r="Z47">
-        <v>112</v>
-      </c>
-      <c r="AA47" t="inlineStr">
+      <c r="Z52">
+        <v>113</v>
+      </c>
+      <c r="AA52" t="inlineStr">
         <is>
           <t>IOC</t>
         </is>
       </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
